--- a/output/bases_limpias/Grupo_03_MODULOS/df_ugrd_me.xlsx
+++ b/output/bases_limpias/Grupo_03_MODULOS/df_ugrd_me.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O518"/>
+  <dimension ref="A1:Q518"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -492,6 +492,16 @@
           <t>ubigeo</t>
         </is>
       </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>dre</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>ugel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -561,6 +571,16 @@
           <t>131201</t>
         </is>
       </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>UGEL VIRÚ</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -630,6 +650,16 @@
           <t>131202</t>
         </is>
       </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>UGEL VIRÚ</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -699,6 +729,16 @@
           <t>131202</t>
         </is>
       </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>UGEL VIRÚ</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -768,6 +808,16 @@
           <t>130102</t>
         </is>
       </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>UGEL 01 - EL PORVENIR</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -837,6 +887,16 @@
           <t>130101</t>
         </is>
       </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>UGEL 03 - TRUJILLO NOR OESTE</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -906,6 +966,16 @@
           <t>140205</t>
         </is>
       </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>UGEL FERREÑAFE</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -975,6 +1045,16 @@
           <t>140205</t>
         </is>
       </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>UGEL FERREÑAFE</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1044,6 +1124,16 @@
           <t>130102</t>
         </is>
       </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>UGEL 01 - EL PORVENIR</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1113,6 +1203,16 @@
           <t>130106</t>
         </is>
       </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>UGEL 01 - EL PORVENIR</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1182,6 +1282,16 @@
           <t>130705</t>
         </is>
       </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>UGEL PACASMAYO</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1251,6 +1361,16 @@
           <t>140108</t>
         </is>
       </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>UGEL CHICLAYO</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1320,6 +1440,16 @@
           <t>140203</t>
         </is>
       </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>UGEL FERREÑAFE</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1389,6 +1519,16 @@
           <t>140203</t>
         </is>
       </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>UGEL FERREÑAFE</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1458,6 +1598,16 @@
           <t>140203</t>
         </is>
       </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>UGEL FERREÑAFE</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1527,6 +1677,16 @@
           <t>090401</t>
         </is>
       </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>UGEL CASTROVIRREYNA</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1596,6 +1756,16 @@
           <t>090401</t>
         </is>
       </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>UGEL CASTROVIRREYNA</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1665,6 +1835,16 @@
           <t>090407</t>
         </is>
       </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>UGEL CASTROVIRREYNA</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1734,6 +1914,16 @@
           <t>090407</t>
         </is>
       </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>UGEL CASTROVIRREYNA</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1803,6 +1993,16 @@
           <t>090502</t>
         </is>
       </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>UGEL CHURCAMPA</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1872,6 +2072,16 @@
           <t>090502</t>
         </is>
       </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>UGEL CHURCAMPA</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1941,6 +2151,16 @@
           <t>090507</t>
         </is>
       </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>UGEL CHURCAMPA</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2010,6 +2230,16 @@
           <t>090507</t>
         </is>
       </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>UGEL CHURCAMPA</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2079,6 +2309,16 @@
           <t>090310</t>
         </is>
       </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>UGEL ANGARAES</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2148,6 +2388,16 @@
           <t>090310</t>
         </is>
       </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>UGEL ANGARAES</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2217,6 +2467,16 @@
           <t>090310</t>
         </is>
       </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>UGEL ANGARAES</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2286,6 +2546,16 @@
           <t>090310</t>
         </is>
       </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>UGEL ANGARAES</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2355,6 +2625,16 @@
           <t>090609</t>
         </is>
       </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>UGEL HUAYTARÁ</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2424,6 +2704,16 @@
           <t>090609</t>
         </is>
       </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>UGEL HUAYTARÁ</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2493,6 +2783,16 @@
           <t>130601</t>
         </is>
       </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>UGEL OTUZCO</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2562,6 +2862,16 @@
           <t>130601</t>
         </is>
       </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>UGEL OTUZCO</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2631,6 +2941,16 @@
           <t>131203</t>
         </is>
       </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>UGEL VIRÚ</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2700,6 +3020,16 @@
           <t>131101</t>
         </is>
       </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>UGEL GRAN CHIMÚ</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2769,6 +3099,16 @@
           <t>131101</t>
         </is>
       </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>UGEL GRAN CHIMÚ</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2838,6 +3178,16 @@
           <t>130201</t>
         </is>
       </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>UGEL ASCOPE</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2907,6 +3257,16 @@
           <t>130104</t>
         </is>
       </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>UGEL 03 - TRUJILLO NOR OESTE</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2974,6 +3334,16 @@
       <c r="O37" t="inlineStr">
         <is>
           <t>131201</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>UGEL VIRÚ</t>
         </is>
       </c>
     </row>
@@ -3025,6 +3395,8 @@
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -3094,6 +3466,16 @@
           <t>130701</t>
         </is>
       </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>UGEL PACASMAYO</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -3163,6 +3545,16 @@
           <t>130108</t>
         </is>
       </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>UGEL 01 - EL PORVENIR</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -3232,6 +3624,16 @@
           <t>131201</t>
         </is>
       </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>UGEL VIRÚ</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -3301,6 +3703,16 @@
           <t>131202</t>
         </is>
       </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>UGEL VIRÚ</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -3370,6 +3782,16 @@
           <t>130401</t>
         </is>
       </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>UGEL CHEPEN</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -3439,6 +3861,16 @@
           <t>130104</t>
         </is>
       </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>UGEL 02 - LA ESPERANZA</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -3508,6 +3940,16 @@
           <t>131101</t>
         </is>
       </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>UGEL GRAN CHIMÚ</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -3577,6 +4019,16 @@
           <t>130208</t>
         </is>
       </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>UGEL ASCOPE</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -3646,6 +4098,16 @@
           <t>130205</t>
         </is>
       </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>UGEL ASCOPE</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -3715,6 +4177,16 @@
           <t>130207</t>
         </is>
       </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>UGEL ASCOPE</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -3784,6 +4256,16 @@
           <t>131101</t>
         </is>
       </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>UGEL GRAN CHIMÚ</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -3853,6 +4335,16 @@
           <t>131101</t>
         </is>
       </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>UGEL GRAN CHIMÚ</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -3922,6 +4414,16 @@
           <t>130601</t>
         </is>
       </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>UGEL OTUZCO</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -3989,6 +4491,16 @@
       <c r="O52" t="inlineStr">
         <is>
           <t>130601</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>UGEL OTUZCO</t>
         </is>
       </c>
     </row>
@@ -4040,6 +4552,8 @@
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -4109,6 +4623,16 @@
           <t>131101</t>
         </is>
       </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>UGEL GRAN CHIMÚ</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -4178,6 +4702,16 @@
           <t>131101</t>
         </is>
       </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>UGEL GRAN CHIMÚ</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -4247,6 +4781,16 @@
           <t>130105</t>
         </is>
       </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>UGEL 02 - LA ESPERANZA</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -4316,6 +4860,16 @@
           <t>131202</t>
         </is>
       </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>UGEL VIRÚ</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -4385,6 +4939,16 @@
           <t>131201</t>
         </is>
       </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>UGEL VIRÚ</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -4454,6 +5018,16 @@
           <t>131201</t>
         </is>
       </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>UGEL VIRÚ</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -4523,6 +5097,16 @@
           <t>140310</t>
         </is>
       </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>UGEL LAMBAYEQUE</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -4592,6 +5176,16 @@
           <t>140204</t>
         </is>
       </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>UGEL FERREÑAFE</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -4661,6 +5255,16 @@
           <t>140205</t>
         </is>
       </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>UGEL FERREÑAFE</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -4730,6 +5334,16 @@
           <t>140205</t>
         </is>
       </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>UGEL FERREÑAFE</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -4799,6 +5413,16 @@
           <t>140203</t>
         </is>
       </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>UGEL FERREÑAFE</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -4868,6 +5492,16 @@
           <t>140203</t>
         </is>
       </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>UGEL FERREÑAFE</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -4937,6 +5571,16 @@
           <t>140205</t>
         </is>
       </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>UGEL FERREÑAFE</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -5006,6 +5650,16 @@
           <t>140312</t>
         </is>
       </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>UGEL LAMBAYEQUE</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -5075,6 +5729,16 @@
           <t>140305</t>
         </is>
       </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>UGEL LAMBAYEQUE</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -5144,6 +5808,16 @@
           <t>140305</t>
         </is>
       </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>UGEL LAMBAYEQUE</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -5213,6 +5887,16 @@
           <t>020201</t>
         </is>
       </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>UGEL AIJA</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -5282,6 +5966,16 @@
           <t>020204</t>
         </is>
       </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>UGEL AIJA</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -5351,6 +6045,16 @@
           <t>020201</t>
         </is>
       </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>UGEL AIJA</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -5420,6 +6124,16 @@
           <t>020201</t>
         </is>
       </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>UGEL AIJA</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -5489,6 +6203,16 @@
           <t>020104</t>
         </is>
       </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>UGEL HUARMEY</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -5558,6 +6282,16 @@
           <t>020801</t>
         </is>
       </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>UGEL CASMA</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -5627,6 +6361,16 @@
           <t>020801</t>
         </is>
       </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>UGEL CASMA</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -5696,6 +6440,16 @@
           <t>020804</t>
         </is>
       </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>UGEL CASMA</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -5765,6 +6519,16 @@
           <t>021104</t>
         </is>
       </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>UGEL HUARMEY</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -5834,6 +6598,16 @@
           <t>020804</t>
         </is>
       </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>UGEL CASMA</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -5903,6 +6677,16 @@
           <t>021101</t>
         </is>
       </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>UGEL HUARMEY</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -5972,6 +6756,16 @@
           <t>020906</t>
         </is>
       </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>UGEL CORONGO</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -6041,6 +6835,16 @@
           <t>020511</t>
         </is>
       </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>UGEL BOLOGNESI</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -6110,6 +6914,16 @@
           <t>020511</t>
         </is>
       </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>UGEL BOLOGNESI</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -6179,6 +6993,16 @@
           <t>020506</t>
         </is>
       </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>UGEL BOLOGNESI</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -6248,6 +7072,16 @@
           <t>020606</t>
         </is>
       </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>UGEL CARHUÁZ</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -6317,6 +7151,16 @@
           <t>020606</t>
         </is>
       </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>UGEL CARHUÁZ</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -6386,6 +7230,16 @@
           <t>021016</t>
         </is>
       </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>UGEL HUARI</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -6455,6 +7309,16 @@
           <t>021016</t>
         </is>
       </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>UGEL HUARI</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -6524,6 +7388,16 @@
           <t>021009</t>
         </is>
       </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>UGEL HUARI</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -6593,6 +7467,16 @@
           <t>021009</t>
         </is>
       </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>UGEL HUARI</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -6662,6 +7546,16 @@
           <t>020801</t>
         </is>
       </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>UGEL CASMA</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -6731,6 +7625,16 @@
           <t>020109</t>
         </is>
       </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>UGEL HUARAZ</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -6800,6 +7704,16 @@
           <t>020109</t>
         </is>
       </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>UGEL HUARAZ</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -6869,6 +7783,16 @@
           <t>020801</t>
         </is>
       </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>UGEL CASMA</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -6938,6 +7862,16 @@
           <t>020205</t>
         </is>
       </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>UGEL AIJA</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -7007,6 +7941,16 @@
           <t>020205</t>
         </is>
       </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>UGEL AIJA</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -7076,6 +8020,16 @@
           <t>020801</t>
         </is>
       </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>UGEL CASMA</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -7145,6 +8099,16 @@
           <t>020202</t>
         </is>
       </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>UGEL AIJA</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -7214,6 +8178,16 @@
           <t>020104</t>
         </is>
       </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>UGEL HUARMEY</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -7283,6 +8257,16 @@
           <t>020104</t>
         </is>
       </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>UGEL HUARMEY</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -7352,6 +8336,16 @@
           <t>020804</t>
         </is>
       </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>UGEL CASMA</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -7421,6 +8415,16 @@
           <t>020801</t>
         </is>
       </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>UGEL CASMA</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -7490,6 +8494,16 @@
           <t>020801</t>
         </is>
       </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>UGEL CASMA</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -7559,6 +8573,16 @@
           <t>020702</t>
         </is>
       </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>UGEL CARLOS FERMIN FITZCARRALD</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -7628,6 +8652,16 @@
           <t>020702</t>
         </is>
       </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>UGEL CARLOS FERMIN FITZCARRALD</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -7697,6 +8731,16 @@
           <t>020701</t>
         </is>
       </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>UGEL CARLOS FERMIN FITZCARRALD</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -7766,6 +8810,16 @@
           <t>020701</t>
         </is>
       </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>UGEL CARLOS FERMIN FITZCARRALD</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -7835,6 +8889,16 @@
           <t>020109</t>
         </is>
       </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>UGEL HUARAZ</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -7904,6 +8968,16 @@
           <t>020109</t>
         </is>
       </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>UGEL HUARAZ</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -7973,6 +9047,16 @@
           <t>020203</t>
         </is>
       </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>UGEL AIJA</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -8042,6 +9126,16 @@
           <t>020104</t>
         </is>
       </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>UGEL HUARMEY</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -8111,6 +9205,16 @@
           <t>021102</t>
         </is>
       </c>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>UGEL HUARMEY</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -8180,6 +9284,16 @@
           <t>021103</t>
         </is>
       </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>UGEL HUARMEY</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -8249,6 +9363,16 @@
           <t>020202</t>
         </is>
       </c>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>UGEL AIJA</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -8318,6 +9442,16 @@
           <t>020203</t>
         </is>
       </c>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q115" t="inlineStr">
+        <is>
+          <t>UGEL AIJA</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -8387,6 +9521,16 @@
           <t>020203</t>
         </is>
       </c>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <t>UGEL AIJA</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -8456,6 +9600,16 @@
           <t>020204</t>
         </is>
       </c>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q117" t="inlineStr">
+        <is>
+          <t>UGEL AIJA</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -8525,6 +9679,16 @@
           <t>020204</t>
         </is>
       </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>UGEL AIJA</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -8594,6 +9758,16 @@
           <t>020204</t>
         </is>
       </c>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>UGEL AIJA</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -8663,6 +9837,16 @@
           <t>020204</t>
         </is>
       </c>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>UGEL AIJA</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -8732,6 +9916,16 @@
           <t>020802</t>
         </is>
       </c>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q121" t="inlineStr">
+        <is>
+          <t>UGEL CASMA</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -8801,6 +9995,16 @@
           <t>021010</t>
         </is>
       </c>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q122" t="inlineStr">
+        <is>
+          <t>UGEL HUARI</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -8870,6 +10074,16 @@
           <t>021010</t>
         </is>
       </c>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q123" t="inlineStr">
+        <is>
+          <t>UGEL HUARI</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -8939,6 +10153,16 @@
           <t>021103</t>
         </is>
       </c>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q124" t="inlineStr">
+        <is>
+          <t>UGEL HUARMEY</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -9008,6 +10232,16 @@
           <t>021101</t>
         </is>
       </c>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q125" t="inlineStr">
+        <is>
+          <t>UGEL HUARMEY</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -9077,6 +10311,16 @@
           <t>021105</t>
         </is>
       </c>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q126" t="inlineStr">
+        <is>
+          <t>UGEL HUARMEY</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -9146,6 +10390,16 @@
           <t>020201</t>
         </is>
       </c>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q127" t="inlineStr">
+        <is>
+          <t>UGEL AIJA</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -9215,6 +10469,16 @@
           <t>020201</t>
         </is>
       </c>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q128" t="inlineStr">
+        <is>
+          <t>UGEL AIJA</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -9284,6 +10548,16 @@
           <t>020202</t>
         </is>
       </c>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q129" t="inlineStr">
+        <is>
+          <t>UGEL AIJA</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -9353,6 +10627,16 @@
           <t>020202</t>
         </is>
       </c>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q130" t="inlineStr">
+        <is>
+          <t>UGEL AIJA</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -9422,6 +10706,16 @@
           <t>020305</t>
         </is>
       </c>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q131" t="inlineStr">
+        <is>
+          <t>UGEL ANTONIO RAYMONDI</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -9491,6 +10785,16 @@
           <t>020305</t>
         </is>
       </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q132" t="inlineStr">
+        <is>
+          <t>UGEL ANTONIO RAYMONDI</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -9560,6 +10864,16 @@
           <t>020604</t>
         </is>
       </c>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q133" t="inlineStr">
+        <is>
+          <t>UGEL CARHUÁZ</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -9629,6 +10943,16 @@
           <t>020604</t>
         </is>
       </c>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q134" t="inlineStr">
+        <is>
+          <t>UGEL CARHUÁZ</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -9698,6 +11022,16 @@
           <t>020804</t>
         </is>
       </c>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q135" t="inlineStr">
+        <is>
+          <t>UGEL CASMA</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -9767,6 +11101,16 @@
           <t>021102</t>
         </is>
       </c>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q136" t="inlineStr">
+        <is>
+          <t>UGEL HUARMEY</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -9836,6 +11180,16 @@
           <t>021102</t>
         </is>
       </c>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q137" t="inlineStr">
+        <is>
+          <t>UGEL HUARMEY</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -9905,6 +11259,16 @@
           <t>060202</t>
         </is>
       </c>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="Q138" t="inlineStr">
+        <is>
+          <t>UGEL CAJABAMBA</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -9974,6 +11338,16 @@
           <t>060202</t>
         </is>
       </c>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="Q139" t="inlineStr">
+        <is>
+          <t>UGEL CAJABAMBA</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -10043,6 +11417,16 @@
           <t>200701</t>
         </is>
       </c>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q140" t="inlineStr">
+        <is>
+          <t>UGEL TALARA</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -10112,6 +11496,16 @@
           <t>200114</t>
         </is>
       </c>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q141" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOGRANDE</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -10181,6 +11575,16 @@
           <t>200101</t>
         </is>
       </c>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q142" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -10250,6 +11654,16 @@
           <t>200114</t>
         </is>
       </c>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q143" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOGRANDE</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -10317,6 +11731,16 @@
       <c r="O144" t="inlineStr">
         <is>
           <t>200603</t>
+        </is>
+      </c>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q144" t="inlineStr">
+        <is>
+          <t>UGEL SULLANA</t>
         </is>
       </c>
     </row>
@@ -10368,6 +11792,8 @@
       <c r="M145" t="inlineStr"/>
       <c r="N145" t="inlineStr"/>
       <c r="O145" t="inlineStr"/>
+      <c r="P145" t="inlineStr"/>
+      <c r="Q145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -10437,6 +11863,16 @@
           <t>150305</t>
         </is>
       </c>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="Q146" t="inlineStr">
+        <is>
+          <t>UGEL 11 CAJATAMBO</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -10506,6 +11942,16 @@
           <t>151003</t>
         </is>
       </c>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="Q147" t="inlineStr">
+        <is>
+          <t>UGEL 13 YAUYOS</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -10575,6 +12021,16 @@
           <t>151003</t>
         </is>
       </c>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="Q148" t="inlineStr">
+        <is>
+          <t>UGEL 13 YAUYOS</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -10644,6 +12100,16 @@
           <t>150702</t>
         </is>
       </c>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="Q149" t="inlineStr">
+        <is>
+          <t>UGEL 15 HUAROCHIRÍ</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -10713,6 +12179,16 @@
           <t>150807</t>
         </is>
       </c>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="Q150" t="inlineStr">
+        <is>
+          <t>UGEL 09 HUAURA</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -10782,6 +12258,16 @@
           <t>150807</t>
         </is>
       </c>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="Q151" t="inlineStr">
+        <is>
+          <t>UGEL 09 HUAURA</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -10851,6 +12337,16 @@
           <t>150407</t>
         </is>
       </c>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="Q152" t="inlineStr">
+        <is>
+          <t>UGEL 12 CANTA</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -10920,6 +12416,16 @@
           <t>151027</t>
         </is>
       </c>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="Q153" t="inlineStr">
+        <is>
+          <t>UGEL 13 YAUYOS</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -10989,6 +12495,16 @@
           <t>200114</t>
         </is>
       </c>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q154" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOGRANDE</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -11058,6 +12574,16 @@
           <t>200114</t>
         </is>
       </c>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q155" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOGRANDE</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -11127,6 +12653,16 @@
           <t>200801</t>
         </is>
       </c>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q156" t="inlineStr">
+        <is>
+          <t>UGEL SECHURA</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -11196,6 +12732,16 @@
           <t>240202</t>
         </is>
       </c>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>DRE TUMBES</t>
+        </is>
+      </c>
+      <c r="Q157" t="inlineStr">
+        <is>
+          <t>UGEL CONTRALMIRANTE VILLAR</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -11265,6 +12811,16 @@
           <t>050407</t>
         </is>
       </c>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="Q158" t="inlineStr">
+        <is>
+          <t>UGEL HUANTA</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -11334,6 +12890,16 @@
           <t>050407</t>
         </is>
       </c>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="Q159" t="inlineStr">
+        <is>
+          <t>UGEL HUANTA</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -11403,6 +12969,16 @@
           <t>060112</t>
         </is>
       </c>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="Q160" t="inlineStr">
+        <is>
+          <t>UGEL CAJAMARCA</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -11472,6 +13048,16 @@
           <t>060112</t>
         </is>
       </c>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="Q161" t="inlineStr">
+        <is>
+          <t>UGEL CAJAMARCA</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -11541,6 +13127,16 @@
           <t>060308</t>
         </is>
       </c>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="Q162" t="inlineStr">
+        <is>
+          <t>UGEL CELENDÍN</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -11610,6 +13206,16 @@
           <t>060308</t>
         </is>
       </c>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="Q163" t="inlineStr">
+        <is>
+          <t>UGEL CELENDÍN</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -11679,6 +13285,16 @@
           <t>060612</t>
         </is>
       </c>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="Q164" t="inlineStr">
+        <is>
+          <t>UGEL CUTERVO</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -11748,6 +13364,16 @@
           <t>060612</t>
         </is>
       </c>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="Q165" t="inlineStr">
+        <is>
+          <t>UGEL CUTERVO</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -11817,6 +13443,16 @@
           <t>151003</t>
         </is>
       </c>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="Q166" t="inlineStr">
+        <is>
+          <t>UGEL 13 YAUYOS</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -11886,6 +13522,16 @@
           <t>150304</t>
         </is>
       </c>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="Q167" t="inlineStr">
+        <is>
+          <t>UGEL 11 CAJATAMBO</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -11955,6 +13601,16 @@
           <t>150304</t>
         </is>
       </c>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="Q168" t="inlineStr">
+        <is>
+          <t>UGEL 11 CAJATAMBO</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -12024,6 +13680,16 @@
           <t>150728</t>
         </is>
       </c>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="Q169" t="inlineStr">
+        <is>
+          <t>UGEL 15 HUAROCHIRÍ</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -12093,6 +13759,16 @@
           <t>150715</t>
         </is>
       </c>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="Q170" t="inlineStr">
+        <is>
+          <t>UGEL 15 HUAROCHIRÍ</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -12162,6 +13838,16 @@
           <t>150715</t>
         </is>
       </c>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="Q171" t="inlineStr">
+        <is>
+          <t>UGEL 15 HUAROCHIRÍ</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -12231,6 +13917,16 @@
           <t>150726</t>
         </is>
       </c>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="Q172" t="inlineStr">
+        <is>
+          <t>UGEL 15 HUAROCHIRÍ</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -12300,6 +13996,16 @@
           <t>151022</t>
         </is>
       </c>
+      <c r="P173" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="Q173" t="inlineStr">
+        <is>
+          <t>UGEL 13 YAUYOS</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -12369,6 +14075,16 @@
           <t>150606</t>
         </is>
       </c>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="Q174" t="inlineStr">
+        <is>
+          <t>UGEL 10 HUARAL</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -12438,6 +14154,16 @@
           <t>150606</t>
         </is>
       </c>
+      <c r="P175" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="Q175" t="inlineStr">
+        <is>
+          <t>UGEL 10 HUARAL</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -12507,6 +14233,16 @@
           <t>200801</t>
         </is>
       </c>
+      <c r="P176" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q176" t="inlineStr">
+        <is>
+          <t>UGEL SECHURA</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -12576,6 +14312,16 @@
           <t>200801</t>
         </is>
       </c>
+      <c r="P177" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q177" t="inlineStr">
+        <is>
+          <t>UGEL SECHURA</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -12645,6 +14391,16 @@
           <t>200601</t>
         </is>
       </c>
+      <c r="P178" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q178" t="inlineStr">
+        <is>
+          <t>UGEL SULLANA</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -12714,6 +14470,16 @@
           <t>200701</t>
         </is>
       </c>
+      <c r="P179" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q179" t="inlineStr">
+        <is>
+          <t>UGEL TALARA</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -12783,6 +14549,16 @@
           <t>200108</t>
         </is>
       </c>
+      <c r="P180" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q180" t="inlineStr">
+        <is>
+          <t>UGEL LA UNIÓN</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -12852,6 +14628,16 @@
           <t>200111</t>
         </is>
       </c>
+      <c r="P181" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q181" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOGRANDE</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -12921,6 +14707,16 @@
           <t>200101</t>
         </is>
       </c>
+      <c r="P182" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q182" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -12990,6 +14786,16 @@
           <t>200105</t>
         </is>
       </c>
+      <c r="P183" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q183" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -13059,6 +14865,16 @@
           <t>200108</t>
         </is>
       </c>
+      <c r="P184" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q184" t="inlineStr">
+        <is>
+          <t>UGEL LA UNIÓN</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -13128,6 +14944,16 @@
           <t>200110</t>
         </is>
       </c>
+      <c r="P185" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q185" t="inlineStr">
+        <is>
+          <t>UGEL LA UNIÓN</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -13197,6 +15023,16 @@
           <t>200101</t>
         </is>
       </c>
+      <c r="P186" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q186" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -13266,6 +15102,16 @@
           <t>200101</t>
         </is>
       </c>
+      <c r="P187" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q187" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -13335,6 +15181,16 @@
           <t>200114</t>
         </is>
       </c>
+      <c r="P188" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q188" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOGRANDE</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -13404,6 +15260,16 @@
           <t>200114</t>
         </is>
       </c>
+      <c r="P189" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q189" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOGRANDE</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -13473,6 +15339,16 @@
           <t>200105</t>
         </is>
       </c>
+      <c r="P190" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q190" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -13542,6 +15418,16 @@
           <t>200110</t>
         </is>
       </c>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q191" t="inlineStr">
+        <is>
+          <t>UGEL LA UNIÓN</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -13611,6 +15497,16 @@
           <t>200101</t>
         </is>
       </c>
+      <c r="P192" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q192" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -13680,6 +15576,16 @@
           <t>200114</t>
         </is>
       </c>
+      <c r="P193" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q193" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOGRANDE</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -13749,6 +15655,16 @@
           <t>200101</t>
         </is>
       </c>
+      <c r="P194" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q194" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -13818,6 +15734,16 @@
           <t>200101</t>
         </is>
       </c>
+      <c r="P195" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q195" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -13887,6 +15813,16 @@
           <t>200101</t>
         </is>
       </c>
+      <c r="P196" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q196" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -13956,6 +15892,16 @@
           <t>240203</t>
         </is>
       </c>
+      <c r="P197" t="inlineStr">
+        <is>
+          <t>DRE TUMBES</t>
+        </is>
+      </c>
+      <c r="Q197" t="inlineStr">
+        <is>
+          <t>UGEL CONTRALMIRANTE VILLAR</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -14025,6 +15971,16 @@
           <t>240202</t>
         </is>
       </c>
+      <c r="P198" t="inlineStr">
+        <is>
+          <t>DRE TUMBES</t>
+        </is>
+      </c>
+      <c r="Q198" t="inlineStr">
+        <is>
+          <t>UGEL CONTRALMIRANTE VILLAR</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -14094,6 +16050,16 @@
           <t>240203</t>
         </is>
       </c>
+      <c r="P199" t="inlineStr">
+        <is>
+          <t>DRE TUMBES</t>
+        </is>
+      </c>
+      <c r="Q199" t="inlineStr">
+        <is>
+          <t>UGEL CONTRALMIRANTE VILLAR</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -14163,6 +16129,16 @@
           <t>240202</t>
         </is>
       </c>
+      <c r="P200" t="inlineStr">
+        <is>
+          <t>DRE TUMBES</t>
+        </is>
+      </c>
+      <c r="Q200" t="inlineStr">
+        <is>
+          <t>UGEL CONTRALMIRANTE VILLAR</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -14232,6 +16208,16 @@
           <t>240202</t>
         </is>
       </c>
+      <c r="P201" t="inlineStr">
+        <is>
+          <t>DRE TUMBES</t>
+        </is>
+      </c>
+      <c r="Q201" t="inlineStr">
+        <is>
+          <t>UGEL CONTRALMIRANTE VILLAR</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -14301,6 +16287,16 @@
           <t>240202</t>
         </is>
       </c>
+      <c r="P202" t="inlineStr">
+        <is>
+          <t>DRE TUMBES</t>
+        </is>
+      </c>
+      <c r="Q202" t="inlineStr">
+        <is>
+          <t>UGEL CONTRALMIRANTE VILLAR</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -14370,6 +16366,16 @@
           <t>240104</t>
         </is>
       </c>
+      <c r="P203" t="inlineStr">
+        <is>
+          <t>DRE TUMBES</t>
+        </is>
+      </c>
+      <c r="Q203" t="inlineStr">
+        <is>
+          <t>UGEL TUMBES</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -14439,6 +16445,16 @@
           <t>240202</t>
         </is>
       </c>
+      <c r="P204" t="inlineStr">
+        <is>
+          <t>DRE TUMBES</t>
+        </is>
+      </c>
+      <c r="Q204" t="inlineStr">
+        <is>
+          <t>UGEL CONTRALMIRANTE VILLAR</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -14508,6 +16524,16 @@
           <t>240105</t>
         </is>
       </c>
+      <c r="P205" t="inlineStr">
+        <is>
+          <t>DRE TUMBES</t>
+        </is>
+      </c>
+      <c r="Q205" t="inlineStr">
+        <is>
+          <t>UGEL TUMBES</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -14577,6 +16603,16 @@
           <t>240303</t>
         </is>
       </c>
+      <c r="P206" t="inlineStr">
+        <is>
+          <t>DRE TUMBES</t>
+        </is>
+      </c>
+      <c r="Q206" t="inlineStr">
+        <is>
+          <t>UGEL ZARUMILLA</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -14646,6 +16682,16 @@
           <t>061102</t>
         </is>
       </c>
+      <c r="P207" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="Q207" t="inlineStr">
+        <is>
+          <t>UGEL SAN MIGUEL</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -14715,6 +16761,16 @@
           <t>061102</t>
         </is>
       </c>
+      <c r="P208" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="Q208" t="inlineStr">
+        <is>
+          <t>UGEL SAN MIGUEL</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -14784,6 +16840,16 @@
           <t>060606</t>
         </is>
       </c>
+      <c r="P209" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="Q209" t="inlineStr">
+        <is>
+          <t>UGEL CUTERVO</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -14853,6 +16919,16 @@
           <t>060202</t>
         </is>
       </c>
+      <c r="P210" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="Q210" t="inlineStr">
+        <is>
+          <t>UGEL CAJABAMBA</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -14922,6 +16998,16 @@
           <t>060202</t>
         </is>
       </c>
+      <c r="P211" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="Q211" t="inlineStr">
+        <is>
+          <t>UGEL CAJABAMBA</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -14991,6 +17077,16 @@
           <t>120608</t>
         </is>
       </c>
+      <c r="P212" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="Q212" t="inlineStr">
+        <is>
+          <t>UGEL RIO TAMBO</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -15060,6 +17156,16 @@
           <t>200303</t>
         </is>
       </c>
+      <c r="P213" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q213" t="inlineStr">
+        <is>
+          <t>UGEL HUANCABAMBA</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -15129,6 +17235,16 @@
           <t>200303</t>
         </is>
       </c>
+      <c r="P214" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q214" t="inlineStr">
+        <is>
+          <t>UGEL HUANCABAMBA</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -15198,6 +17314,16 @@
           <t>200201</t>
         </is>
       </c>
+      <c r="P215" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q215" t="inlineStr">
+        <is>
+          <t>UGEL AYABACA</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -15267,6 +17393,16 @@
           <t>200201</t>
         </is>
       </c>
+      <c r="P216" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q216" t="inlineStr">
+        <is>
+          <t>UGEL AYABACA</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -15336,6 +17472,16 @@
           <t>200201</t>
         </is>
       </c>
+      <c r="P217" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q217" t="inlineStr">
+        <is>
+          <t>UGEL AYABACA</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -15405,6 +17551,16 @@
           <t>200201</t>
         </is>
       </c>
+      <c r="P218" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q218" t="inlineStr">
+        <is>
+          <t>UGEL AYABACA</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -15474,6 +17630,16 @@
           <t>021302</t>
         </is>
       </c>
+      <c r="P219" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q219" t="inlineStr">
+        <is>
+          <t>UGEL MARISCAL LUZURIAGA</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -15543,6 +17709,16 @@
           <t>021302</t>
         </is>
       </c>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q220" t="inlineStr">
+        <is>
+          <t>UGEL MARISCAL LUZURIAGA</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -15612,6 +17788,16 @@
           <t>200402</t>
         </is>
       </c>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q221" t="inlineStr">
+        <is>
+          <t>UGEL MORROPÓN</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -15681,6 +17867,16 @@
           <t>200406</t>
         </is>
       </c>
+      <c r="P222" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q222" t="inlineStr">
+        <is>
+          <t>UGEL MORROPÓN</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -15750,6 +17946,16 @@
           <t>200401</t>
         </is>
       </c>
+      <c r="P223" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q223" t="inlineStr">
+        <is>
+          <t>UGEL CHULUCANAS</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -15819,6 +18025,16 @@
           <t>200401</t>
         </is>
       </c>
+      <c r="P224" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q224" t="inlineStr">
+        <is>
+          <t>UGEL CHULUCANAS</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -15888,6 +18104,16 @@
           <t>200401</t>
         </is>
       </c>
+      <c r="P225" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q225" t="inlineStr">
+        <is>
+          <t>UGEL CHULUCANAS</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -15957,6 +18183,16 @@
           <t>200402</t>
         </is>
       </c>
+      <c r="P226" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q226" t="inlineStr">
+        <is>
+          <t>UGEL MORROPÓN</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -16026,6 +18262,16 @@
           <t>021701</t>
         </is>
       </c>
+      <c r="P227" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q227" t="inlineStr">
+        <is>
+          <t>UGEL RECUAY</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -16095,6 +18341,16 @@
           <t>021701</t>
         </is>
       </c>
+      <c r="P228" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q228" t="inlineStr">
+        <is>
+          <t>UGEL RECUAY</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -16164,6 +18420,16 @@
           <t>021701</t>
         </is>
       </c>
+      <c r="P229" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q229" t="inlineStr">
+        <is>
+          <t>UGEL RECUAY</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -16233,6 +18499,16 @@
           <t>021701</t>
         </is>
       </c>
+      <c r="P230" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q230" t="inlineStr">
+        <is>
+          <t>UGEL RECUAY</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -16302,6 +18578,16 @@
           <t>021705</t>
         </is>
       </c>
+      <c r="P231" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q231" t="inlineStr">
+        <is>
+          <t>UGEL RECUAY</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -16371,6 +18657,16 @@
           <t>021705</t>
         </is>
       </c>
+      <c r="P232" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q232" t="inlineStr">
+        <is>
+          <t>UGEL RECUAY</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -16440,6 +18736,16 @@
           <t>021702</t>
         </is>
       </c>
+      <c r="P233" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q233" t="inlineStr">
+        <is>
+          <t>UGEL RECUAY</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -16509,6 +18815,16 @@
           <t>021702</t>
         </is>
       </c>
+      <c r="P234" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q234" t="inlineStr">
+        <is>
+          <t>UGEL RECUAY</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -16578,6 +18894,16 @@
           <t>021809</t>
         </is>
       </c>
+      <c r="P235" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q235" t="inlineStr">
+        <is>
+          <t>UGEL SANTA</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -16647,6 +18973,16 @@
           <t>021802</t>
         </is>
       </c>
+      <c r="P236" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q236" t="inlineStr">
+        <is>
+          <t>UGEL SANTA</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -16716,6 +19052,16 @@
           <t>021802</t>
         </is>
       </c>
+      <c r="P237" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q237" t="inlineStr">
+        <is>
+          <t>UGEL SANTA</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -16785,6 +19131,16 @@
           <t>022001</t>
         </is>
       </c>
+      <c r="P238" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q238" t="inlineStr">
+        <is>
+          <t>UGEL YUNGAY</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -16854,6 +19210,16 @@
           <t>022001</t>
         </is>
       </c>
+      <c r="P239" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q239" t="inlineStr">
+        <is>
+          <t>UGEL YUNGAY</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -16923,6 +19289,16 @@
           <t>200407</t>
         </is>
       </c>
+      <c r="P240" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q240" t="inlineStr">
+        <is>
+          <t>UGEL MORROPÓN</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -16992,6 +19368,16 @@
           <t>021410</t>
         </is>
       </c>
+      <c r="P241" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q241" t="inlineStr">
+        <is>
+          <t>UGEL OCROS</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -17061,6 +19447,16 @@
           <t>021410</t>
         </is>
       </c>
+      <c r="P242" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q242" t="inlineStr">
+        <is>
+          <t>UGEL OCROS</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -17130,6 +19526,16 @@
           <t>200305</t>
         </is>
       </c>
+      <c r="P243" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q243" t="inlineStr">
+        <is>
+          <t>UGEL MORROPÓN</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -17199,6 +19605,16 @@
           <t>200305</t>
         </is>
       </c>
+      <c r="P244" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q244" t="inlineStr">
+        <is>
+          <t>UGEL MORROPÓN</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -17268,6 +19684,16 @@
           <t>200304</t>
         </is>
       </c>
+      <c r="P245" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q245" t="inlineStr">
+        <is>
+          <t>UGEL HUARMACA</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -17337,6 +19763,16 @@
           <t>021410</t>
         </is>
       </c>
+      <c r="P246" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q246" t="inlineStr">
+        <is>
+          <t>UGEL OCROS</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -17406,6 +19842,16 @@
           <t>021708</t>
         </is>
       </c>
+      <c r="P247" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q247" t="inlineStr">
+        <is>
+          <t>UGEL RECUAY</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -17475,6 +19921,16 @@
           <t>021202</t>
         </is>
       </c>
+      <c r="P248" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q248" t="inlineStr">
+        <is>
+          <t>UGEL HUAYLAS</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -17544,6 +20000,16 @@
           <t>021204</t>
         </is>
       </c>
+      <c r="P249" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q249" t="inlineStr">
+        <is>
+          <t>UGEL HUAYLAS</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -17613,6 +20079,16 @@
           <t>021204</t>
         </is>
       </c>
+      <c r="P250" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q250" t="inlineStr">
+        <is>
+          <t>UGEL HUAYLAS</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -17682,6 +20158,16 @@
           <t>021206</t>
         </is>
       </c>
+      <c r="P251" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q251" t="inlineStr">
+        <is>
+          <t>UGEL HUAYLAS</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -17751,6 +20237,16 @@
           <t>021206</t>
         </is>
       </c>
+      <c r="P252" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q252" t="inlineStr">
+        <is>
+          <t>UGEL HUAYLAS</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -17820,6 +20316,16 @@
           <t>021404</t>
         </is>
       </c>
+      <c r="P253" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q253" t="inlineStr">
+        <is>
+          <t>UGEL OCROS</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -17889,6 +20395,16 @@
           <t>021404</t>
         </is>
       </c>
+      <c r="P254" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q254" t="inlineStr">
+        <is>
+          <t>UGEL OCROS</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -17958,6 +20474,16 @@
           <t>021707</t>
         </is>
       </c>
+      <c r="P255" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q255" t="inlineStr">
+        <is>
+          <t>UGEL RECUAY</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -18027,6 +20553,16 @@
           <t>021906</t>
         </is>
       </c>
+      <c r="P256" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q256" t="inlineStr">
+        <is>
+          <t>UGEL SIHUAS</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -18096,6 +20632,16 @@
           <t>021906</t>
         </is>
       </c>
+      <c r="P257" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q257" t="inlineStr">
+        <is>
+          <t>UGEL SIHUAS</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -18165,6 +20711,16 @@
           <t>021801</t>
         </is>
       </c>
+      <c r="P258" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q258" t="inlineStr">
+        <is>
+          <t>UGEL SANTA</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -18234,6 +20790,16 @@
           <t>022005</t>
         </is>
       </c>
+      <c r="P259" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q259" t="inlineStr">
+        <is>
+          <t>UGEL YUNGAY</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -18303,6 +20869,16 @@
           <t>022005</t>
         </is>
       </c>
+      <c r="P260" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q260" t="inlineStr">
+        <is>
+          <t>UGEL YUNGAY</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -18372,6 +20948,16 @@
           <t>022008</t>
         </is>
       </c>
+      <c r="P261" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q261" t="inlineStr">
+        <is>
+          <t>UGEL YUNGAY</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -18441,6 +21027,16 @@
           <t>022008</t>
         </is>
       </c>
+      <c r="P262" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q262" t="inlineStr">
+        <is>
+          <t>UGEL YUNGAY</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -18510,6 +21106,16 @@
           <t>021809</t>
         </is>
       </c>
+      <c r="P263" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q263" t="inlineStr">
+        <is>
+          <t>UGEL SANTA</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -18579,6 +21185,16 @@
           <t>021409</t>
         </is>
       </c>
+      <c r="P264" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q264" t="inlineStr">
+        <is>
+          <t>UGEL OCROS</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -18648,6 +21264,16 @@
           <t>022001</t>
         </is>
       </c>
+      <c r="P265" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q265" t="inlineStr">
+        <is>
+          <t>UGEL YUNGAY</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -18715,6 +21341,16 @@
       <c r="O266" t="inlineStr">
         <is>
           <t>022001</t>
+        </is>
+      </c>
+      <c r="P266" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q266" t="inlineStr">
+        <is>
+          <t>UGEL YUNGAY</t>
         </is>
       </c>
     </row>
@@ -18766,6 +21402,8 @@
       <c r="M267" t="inlineStr"/>
       <c r="N267" t="inlineStr"/>
       <c r="O267" t="inlineStr"/>
+      <c r="P267" t="inlineStr"/>
+      <c r="Q267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -18815,6 +21453,8 @@
       <c r="M268" t="inlineStr"/>
       <c r="N268" t="inlineStr"/>
       <c r="O268" t="inlineStr"/>
+      <c r="P268" t="inlineStr"/>
+      <c r="Q268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -18884,6 +21524,16 @@
           <t>021708</t>
         </is>
       </c>
+      <c r="P269" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q269" t="inlineStr">
+        <is>
+          <t>UGEL RECUAY</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -18953,6 +21603,16 @@
           <t>021701</t>
         </is>
       </c>
+      <c r="P270" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q270" t="inlineStr">
+        <is>
+          <t>UGEL RECUAY</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -19022,6 +21682,16 @@
           <t>021701</t>
         </is>
       </c>
+      <c r="P271" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q271" t="inlineStr">
+        <is>
+          <t>UGEL RECUAY</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -19091,6 +21761,16 @@
           <t>021710</t>
         </is>
       </c>
+      <c r="P272" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q272" t="inlineStr">
+        <is>
+          <t>UGEL RECUAY</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -19160,6 +21840,16 @@
           <t>021710</t>
         </is>
       </c>
+      <c r="P273" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q273" t="inlineStr">
+        <is>
+          <t>UGEL RECUAY</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -19229,6 +21919,16 @@
           <t>021806</t>
         </is>
       </c>
+      <c r="P274" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q274" t="inlineStr">
+        <is>
+          <t>UGEL SANTA</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -19298,6 +21998,16 @@
           <t>022005</t>
         </is>
       </c>
+      <c r="P275" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q275" t="inlineStr">
+        <is>
+          <t>UGEL YUNGAY</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -19367,6 +22077,16 @@
           <t>022005</t>
         </is>
       </c>
+      <c r="P276" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q276" t="inlineStr">
+        <is>
+          <t>UGEL YUNGAY</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -19436,6 +22156,16 @@
           <t>021809</t>
         </is>
       </c>
+      <c r="P277" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q277" t="inlineStr">
+        <is>
+          <t>UGEL SANTA</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -19505,6 +22235,16 @@
           <t>022005</t>
         </is>
       </c>
+      <c r="P278" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q278" t="inlineStr">
+        <is>
+          <t>UGEL YUNGAY</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -19574,6 +22314,16 @@
           <t>022008</t>
         </is>
       </c>
+      <c r="P279" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q279" t="inlineStr">
+        <is>
+          <t>UGEL YUNGAY</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -19643,6 +22393,16 @@
           <t>022008</t>
         </is>
       </c>
+      <c r="P280" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q280" t="inlineStr">
+        <is>
+          <t>UGEL YUNGAY</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -19712,6 +22472,16 @@
           <t>040406</t>
         </is>
       </c>
+      <c r="P281" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="Q281" t="inlineStr">
+        <is>
+          <t>UGEL CAYLLOMA</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -19781,6 +22551,16 @@
           <t>040406</t>
         </is>
       </c>
+      <c r="P282" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="Q282" t="inlineStr">
+        <is>
+          <t>UGEL CAYLLOMA</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -19850,6 +22630,16 @@
           <t>200404</t>
         </is>
       </c>
+      <c r="P283" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q283" t="inlineStr">
+        <is>
+          <t>UGEL CHULUCANAS</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -19919,6 +22709,16 @@
           <t>200402</t>
         </is>
       </c>
+      <c r="P284" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q284" t="inlineStr">
+        <is>
+          <t>UGEL MORROPÓN</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -19988,6 +22788,16 @@
           <t>200404</t>
         </is>
       </c>
+      <c r="P285" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q285" t="inlineStr">
+        <is>
+          <t>UGEL CHULUCANAS</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -20057,6 +22867,16 @@
           <t>200201</t>
         </is>
       </c>
+      <c r="P286" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q286" t="inlineStr">
+        <is>
+          <t>UGEL AYABACA</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -20126,6 +22946,16 @@
           <t>200201</t>
         </is>
       </c>
+      <c r="P287" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q287" t="inlineStr">
+        <is>
+          <t>UGEL AYABACA</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -20195,6 +23025,16 @@
           <t>200201</t>
         </is>
       </c>
+      <c r="P288" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q288" t="inlineStr">
+        <is>
+          <t>UGEL AYABACA</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -20264,6 +23104,16 @@
           <t>200201</t>
         </is>
       </c>
+      <c r="P289" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q289" t="inlineStr">
+        <is>
+          <t>UGEL AYABACA</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -20333,6 +23183,16 @@
           <t>200201</t>
         </is>
       </c>
+      <c r="P290" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q290" t="inlineStr">
+        <is>
+          <t>UGEL AYABACA</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -20402,6 +23262,16 @@
           <t>200201</t>
         </is>
       </c>
+      <c r="P291" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q291" t="inlineStr">
+        <is>
+          <t>UGEL AYABACA</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -20471,6 +23341,16 @@
           <t>200202</t>
         </is>
       </c>
+      <c r="P292" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q292" t="inlineStr">
+        <is>
+          <t>UGEL CHULUCANAS</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -20540,6 +23420,16 @@
           <t>200202</t>
         </is>
       </c>
+      <c r="P293" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q293" t="inlineStr">
+        <is>
+          <t>UGEL CHULUCANAS</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -20609,6 +23499,16 @@
           <t>200305</t>
         </is>
       </c>
+      <c r="P294" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q294" t="inlineStr">
+        <is>
+          <t>UGEL MORROPÓN</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -20678,6 +23578,16 @@
           <t>200305</t>
         </is>
       </c>
+      <c r="P295" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q295" t="inlineStr">
+        <is>
+          <t>UGEL MORROPÓN</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -20747,6 +23657,16 @@
           <t>200401</t>
         </is>
       </c>
+      <c r="P296" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q296" t="inlineStr">
+        <is>
+          <t>UGEL CHULUCANAS</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -20816,6 +23736,16 @@
           <t>200405</t>
         </is>
       </c>
+      <c r="P297" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q297" t="inlineStr">
+        <is>
+          <t>UGEL MORROPÓN</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -20885,6 +23815,16 @@
           <t>200404</t>
         </is>
       </c>
+      <c r="P298" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q298" t="inlineStr">
+        <is>
+          <t>UGEL CHULUCANAS</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -20954,6 +23894,16 @@
           <t>200201</t>
         </is>
       </c>
+      <c r="P299" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q299" t="inlineStr">
+        <is>
+          <t>UGEL AYABACA</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -21023,6 +23973,16 @@
           <t>200201</t>
         </is>
       </c>
+      <c r="P300" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q300" t="inlineStr">
+        <is>
+          <t>UGEL AYABACA</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -21092,6 +24052,16 @@
           <t>200201</t>
         </is>
       </c>
+      <c r="P301" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q301" t="inlineStr">
+        <is>
+          <t>UGEL AYABACA</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -21161,6 +24131,16 @@
           <t>200201</t>
         </is>
       </c>
+      <c r="P302" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q302" t="inlineStr">
+        <is>
+          <t>UGEL AYABACA</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -21230,6 +24210,16 @@
           <t>200302</t>
         </is>
       </c>
+      <c r="P303" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q303" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -21299,6 +24289,16 @@
           <t>200202</t>
         </is>
       </c>
+      <c r="P304" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q304" t="inlineStr">
+        <is>
+          <t>UGEL CHULUCANAS</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -21368,6 +24368,16 @@
           <t>200202</t>
         </is>
       </c>
+      <c r="P305" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q305" t="inlineStr">
+        <is>
+          <t>UGEL CHULUCANAS</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -21437,6 +24447,16 @@
           <t>200305</t>
         </is>
       </c>
+      <c r="P306" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q306" t="inlineStr">
+        <is>
+          <t>UGEL MORROPÓN</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -21506,6 +24526,16 @@
           <t>200305</t>
         </is>
       </c>
+      <c r="P307" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q307" t="inlineStr">
+        <is>
+          <t>UGEL MORROPÓN</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -21575,6 +24605,16 @@
           <t>200306</t>
         </is>
       </c>
+      <c r="P308" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q308" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -21644,6 +24684,16 @@
           <t>021511</t>
         </is>
       </c>
+      <c r="P309" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q309" t="inlineStr">
+        <is>
+          <t>UGEL PALLASCA</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -21713,6 +24763,16 @@
           <t>021511</t>
         </is>
       </c>
+      <c r="P310" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q310" t="inlineStr">
+        <is>
+          <t>UGEL PALLASCA</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -21782,6 +24842,16 @@
           <t>021302</t>
         </is>
       </c>
+      <c r="P311" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q311" t="inlineStr">
+        <is>
+          <t>UGEL MARISCAL LUZURIAGA</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -21851,6 +24921,16 @@
           <t>021302</t>
         </is>
       </c>
+      <c r="P312" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q312" t="inlineStr">
+        <is>
+          <t>UGEL MARISCAL LUZURIAGA</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -21920,6 +25000,16 @@
           <t>200201</t>
         </is>
       </c>
+      <c r="P313" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q313" t="inlineStr">
+        <is>
+          <t>UGEL AYABACA</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -21989,6 +25079,16 @@
           <t>200201</t>
         </is>
       </c>
+      <c r="P314" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q314" t="inlineStr">
+        <is>
+          <t>UGEL AYABACA</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -22058,6 +25158,16 @@
           <t>200201</t>
         </is>
       </c>
+      <c r="P315" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q315" t="inlineStr">
+        <is>
+          <t>UGEL AYABACA</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -22127,6 +25237,16 @@
           <t>200201</t>
         </is>
       </c>
+      <c r="P316" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q316" t="inlineStr">
+        <is>
+          <t>UGEL AYABACA</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -22196,6 +25316,16 @@
           <t>200306</t>
         </is>
       </c>
+      <c r="P317" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q317" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -22265,6 +25395,16 @@
           <t>200205</t>
         </is>
       </c>
+      <c r="P318" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q318" t="inlineStr">
+        <is>
+          <t>UGEL AYABACA</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -22334,6 +25474,16 @@
           <t>200205</t>
         </is>
       </c>
+      <c r="P319" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q319" t="inlineStr">
+        <is>
+          <t>UGEL AYABACA</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -22403,6 +25553,16 @@
           <t>131201</t>
         </is>
       </c>
+      <c r="P320" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="Q320" t="inlineStr">
+        <is>
+          <t>UGEL VIRÚ</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
@@ -22472,6 +25632,16 @@
           <t>131201</t>
         </is>
       </c>
+      <c r="P321" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="Q321" t="inlineStr">
+        <is>
+          <t>UGEL VIRÚ</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -22541,6 +25711,16 @@
           <t>131202</t>
         </is>
       </c>
+      <c r="P322" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="Q322" t="inlineStr">
+        <is>
+          <t>UGEL VIRÚ</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -22610,6 +25790,16 @@
           <t>130401</t>
         </is>
       </c>
+      <c r="P323" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="Q323" t="inlineStr">
+        <is>
+          <t>UGEL CHEPEN</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
@@ -22679,6 +25869,16 @@
           <t>130401</t>
         </is>
       </c>
+      <c r="P324" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="Q324" t="inlineStr">
+        <is>
+          <t>UGEL CHEPEN</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
@@ -22748,6 +25948,16 @@
           <t>130102</t>
         </is>
       </c>
+      <c r="P325" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="Q325" t="inlineStr">
+        <is>
+          <t>UGEL 01 - EL PORVENIR</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
@@ -22817,6 +26027,16 @@
           <t>130101</t>
         </is>
       </c>
+      <c r="P326" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="Q326" t="inlineStr">
+        <is>
+          <t>UGEL 03 - TRUJILLO NOR OESTE</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
@@ -22886,6 +26106,16 @@
           <t>130101</t>
         </is>
       </c>
+      <c r="P327" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="Q327" t="inlineStr">
+        <is>
+          <t>UGEL 03 - TRUJILLO NOR OESTE</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -22955,6 +26185,16 @@
           <t>140205</t>
         </is>
       </c>
+      <c r="P328" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="Q328" t="inlineStr">
+        <is>
+          <t>UGEL FERREÑAFE</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
@@ -23024,6 +26264,16 @@
           <t>140205</t>
         </is>
       </c>
+      <c r="P329" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="Q329" t="inlineStr">
+        <is>
+          <t>UGEL FERREÑAFE</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
@@ -23093,6 +26343,16 @@
           <t>140308</t>
         </is>
       </c>
+      <c r="P330" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="Q330" t="inlineStr">
+        <is>
+          <t>UGEL LAMBAYEQUE</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -23162,6 +26422,16 @@
           <t>140205</t>
         </is>
       </c>
+      <c r="P331" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="Q331" t="inlineStr">
+        <is>
+          <t>UGEL FERREÑAFE</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
@@ -23231,6 +26501,16 @@
           <t>140205</t>
         </is>
       </c>
+      <c r="P332" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="Q332" t="inlineStr">
+        <is>
+          <t>UGEL FERREÑAFE</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
@@ -23300,6 +26580,16 @@
           <t>130403</t>
         </is>
       </c>
+      <c r="P333" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="Q333" t="inlineStr">
+        <is>
+          <t>UGEL CHEPEN</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -23369,6 +26659,16 @@
           <t>130102</t>
         </is>
       </c>
+      <c r="P334" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="Q334" t="inlineStr">
+        <is>
+          <t>UGEL 01 - EL PORVENIR</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
@@ -23438,6 +26738,16 @@
           <t>130102</t>
         </is>
       </c>
+      <c r="P335" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="Q335" t="inlineStr">
+        <is>
+          <t>UGEL 01 - EL PORVENIR</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
@@ -23507,6 +26817,16 @@
           <t>130403</t>
         </is>
       </c>
+      <c r="P336" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="Q336" t="inlineStr">
+        <is>
+          <t>UGEL CHEPEN</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
@@ -23576,6 +26896,16 @@
           <t>140108</t>
         </is>
       </c>
+      <c r="P337" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="Q337" t="inlineStr">
+        <is>
+          <t>UGEL CHICLAYO</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
@@ -23645,6 +26975,16 @@
           <t>130201</t>
         </is>
       </c>
+      <c r="P338" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="Q338" t="inlineStr">
+        <is>
+          <t>UGEL ASCOPE</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
@@ -23714,6 +27054,16 @@
           <t>130205</t>
         </is>
       </c>
+      <c r="P339" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="Q339" t="inlineStr">
+        <is>
+          <t>UGEL ASCOPE</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
@@ -23783,6 +27133,16 @@
           <t>140203</t>
         </is>
       </c>
+      <c r="P340" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="Q340" t="inlineStr">
+        <is>
+          <t>UGEL FERREÑAFE</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
@@ -23852,6 +27212,16 @@
           <t>140309</t>
         </is>
       </c>
+      <c r="P341" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="Q341" t="inlineStr">
+        <is>
+          <t>UGEL LAMBAYEQUE</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
@@ -23921,6 +27291,16 @@
           <t>090401</t>
         </is>
       </c>
+      <c r="P342" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="Q342" t="inlineStr">
+        <is>
+          <t>UGEL CASTROVIRREYNA</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
@@ -23990,6 +27370,16 @@
           <t>090507</t>
         </is>
       </c>
+      <c r="P343" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="Q343" t="inlineStr">
+        <is>
+          <t>UGEL CHURCAMPA</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
@@ -24059,6 +27449,16 @@
           <t>090610</t>
         </is>
       </c>
+      <c r="P344" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="Q344" t="inlineStr">
+        <is>
+          <t>UGEL HUAYTARÁ</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
@@ -24128,6 +27528,16 @@
           <t>090609</t>
         </is>
       </c>
+      <c r="P345" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="Q345" t="inlineStr">
+        <is>
+          <t>UGEL HUAYTARÁ</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
@@ -24197,6 +27607,16 @@
           <t>130403</t>
         </is>
       </c>
+      <c r="P346" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="Q346" t="inlineStr">
+        <is>
+          <t>UGEL CHEPEN</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
@@ -24266,6 +27686,16 @@
           <t>130104</t>
         </is>
       </c>
+      <c r="P347" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="Q347" t="inlineStr">
+        <is>
+          <t>UGEL 02 - LA ESPERANZA</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
@@ -24335,6 +27765,16 @@
           <t>131101</t>
         </is>
       </c>
+      <c r="P348" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="Q348" t="inlineStr">
+        <is>
+          <t>UGEL GRAN CHIMÚ</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
@@ -24404,6 +27844,16 @@
           <t>130205</t>
         </is>
       </c>
+      <c r="P349" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="Q349" t="inlineStr">
+        <is>
+          <t>UGEL ASCOPE</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
@@ -24473,6 +27923,16 @@
           <t>131101</t>
         </is>
       </c>
+      <c r="P350" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="Q350" t="inlineStr">
+        <is>
+          <t>UGEL GRAN CHIMÚ</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
@@ -24542,6 +28002,16 @@
           <t>131101</t>
         </is>
       </c>
+      <c r="P351" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="Q351" t="inlineStr">
+        <is>
+          <t>UGEL GRAN CHIMÚ</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
@@ -24611,6 +28081,16 @@
           <t>131101</t>
         </is>
       </c>
+      <c r="P352" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="Q352" t="inlineStr">
+        <is>
+          <t>UGEL GRAN CHIMÚ</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
@@ -24680,6 +28160,16 @@
           <t>131101</t>
         </is>
       </c>
+      <c r="P353" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="Q353" t="inlineStr">
+        <is>
+          <t>UGEL GRAN CHIMÚ</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
@@ -24749,6 +28239,16 @@
           <t>130105</t>
         </is>
       </c>
+      <c r="P354" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="Q354" t="inlineStr">
+        <is>
+          <t>UGEL 02 - LA ESPERANZA</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
@@ -24818,6 +28318,16 @@
           <t>130105</t>
         </is>
       </c>
+      <c r="P355" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="Q355" t="inlineStr">
+        <is>
+          <t>UGEL 02 - LA ESPERANZA</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
@@ -24887,6 +28397,16 @@
           <t>131202</t>
         </is>
       </c>
+      <c r="P356" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="Q356" t="inlineStr">
+        <is>
+          <t>UGEL VIRÚ</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
@@ -24956,6 +28476,16 @@
           <t>131201</t>
         </is>
       </c>
+      <c r="P357" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="Q357" t="inlineStr">
+        <is>
+          <t>UGEL VIRÚ</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
@@ -25025,6 +28555,16 @@
           <t>140310</t>
         </is>
       </c>
+      <c r="P358" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="Q358" t="inlineStr">
+        <is>
+          <t>UGEL LAMBAYEQUE</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
@@ -25094,6 +28634,16 @@
           <t>140205</t>
         </is>
       </c>
+      <c r="P359" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="Q359" t="inlineStr">
+        <is>
+          <t>UGEL FERREÑAFE</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
@@ -25163,6 +28713,16 @@
           <t>140205</t>
         </is>
       </c>
+      <c r="P360" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="Q360" t="inlineStr">
+        <is>
+          <t>UGEL FERREÑAFE</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
@@ -25232,6 +28792,16 @@
           <t>140205</t>
         </is>
       </c>
+      <c r="P361" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="Q361" t="inlineStr">
+        <is>
+          <t>UGEL FERREÑAFE</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
@@ -25301,6 +28871,16 @@
           <t>140205</t>
         </is>
       </c>
+      <c r="P362" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="Q362" t="inlineStr">
+        <is>
+          <t>UGEL FERREÑAFE</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
@@ -25370,6 +28950,16 @@
           <t>140205</t>
         </is>
       </c>
+      <c r="P363" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="Q363" t="inlineStr">
+        <is>
+          <t>UGEL FERREÑAFE</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
@@ -25439,6 +29029,16 @@
           <t>140312</t>
         </is>
       </c>
+      <c r="P364" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="Q364" t="inlineStr">
+        <is>
+          <t>UGEL LAMBAYEQUE</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
@@ -25508,6 +29108,16 @@
           <t>140312</t>
         </is>
       </c>
+      <c r="P365" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="Q365" t="inlineStr">
+        <is>
+          <t>UGEL LAMBAYEQUE</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
@@ -25577,6 +29187,16 @@
           <t>140305</t>
         </is>
       </c>
+      <c r="P366" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="Q366" t="inlineStr">
+        <is>
+          <t>UGEL LAMBAYEQUE</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
@@ -25646,6 +29266,16 @@
           <t>140305</t>
         </is>
       </c>
+      <c r="P367" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="Q367" t="inlineStr">
+        <is>
+          <t>UGEL LAMBAYEQUE</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
@@ -25715,6 +29345,16 @@
           <t>020510</t>
         </is>
       </c>
+      <c r="P368" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q368" t="inlineStr">
+        <is>
+          <t>UGEL BOLOGNESI</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="n">
@@ -25784,6 +29424,16 @@
           <t>020104</t>
         </is>
       </c>
+      <c r="P369" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q369" t="inlineStr">
+        <is>
+          <t>UGEL HUARMEY</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
@@ -25853,6 +29503,16 @@
           <t>021104</t>
         </is>
       </c>
+      <c r="P370" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q370" t="inlineStr">
+        <is>
+          <t>UGEL HUARMEY</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
@@ -25922,6 +29582,16 @@
           <t>021104</t>
         </is>
       </c>
+      <c r="P371" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q371" t="inlineStr">
+        <is>
+          <t>UGEL HUARMEY</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
@@ -25991,6 +29661,16 @@
           <t>020202</t>
         </is>
       </c>
+      <c r="P372" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q372" t="inlineStr">
+        <is>
+          <t>UGEL AIJA</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
@@ -26060,6 +29740,16 @@
           <t>020202</t>
         </is>
       </c>
+      <c r="P373" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q373" t="inlineStr">
+        <is>
+          <t>UGEL AIJA</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
@@ -26129,6 +29819,16 @@
           <t>021101</t>
         </is>
       </c>
+      <c r="P374" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q374" t="inlineStr">
+        <is>
+          <t>UGEL HUARMEY</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
@@ -26198,6 +29898,16 @@
           <t>020906</t>
         </is>
       </c>
+      <c r="P375" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q375" t="inlineStr">
+        <is>
+          <t>UGEL CORONGO</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
@@ -26267,6 +29977,16 @@
           <t>020513</t>
         </is>
       </c>
+      <c r="P376" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q376" t="inlineStr">
+        <is>
+          <t>UGEL BOLOGNESI</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
@@ -26336,6 +30056,16 @@
           <t>020513</t>
         </is>
       </c>
+      <c r="P377" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q377" t="inlineStr">
+        <is>
+          <t>UGEL BOLOGNESI</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
@@ -26405,6 +30135,16 @@
           <t>020511</t>
         </is>
       </c>
+      <c r="P378" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q378" t="inlineStr">
+        <is>
+          <t>UGEL BOLOGNESI</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
@@ -26474,6 +30214,16 @@
           <t>020606</t>
         </is>
       </c>
+      <c r="P379" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q379" t="inlineStr">
+        <is>
+          <t>UGEL CARHUÁZ</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="n">
@@ -26543,6 +30293,16 @@
           <t>020801</t>
         </is>
       </c>
+      <c r="P380" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q380" t="inlineStr">
+        <is>
+          <t>UGEL CASMA</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
@@ -26612,6 +30372,16 @@
           <t>020109</t>
         </is>
       </c>
+      <c r="P381" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q381" t="inlineStr">
+        <is>
+          <t>UGEL HUARAZ</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
@@ -26681,6 +30451,16 @@
           <t>020801</t>
         </is>
       </c>
+      <c r="P382" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q382" t="inlineStr">
+        <is>
+          <t>UGEL CASMA</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
@@ -26750,6 +30530,16 @@
           <t>020702</t>
         </is>
       </c>
+      <c r="P383" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q383" t="inlineStr">
+        <is>
+          <t>UGEL CARLOS FERMIN FITZCARRALD</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="n">
@@ -26819,6 +30609,16 @@
           <t>020702</t>
         </is>
       </c>
+      <c r="P384" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q384" t="inlineStr">
+        <is>
+          <t>UGEL CARLOS FERMIN FITZCARRALD</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="n">
@@ -26888,6 +30688,16 @@
           <t>020109</t>
         </is>
       </c>
+      <c r="P385" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q385" t="inlineStr">
+        <is>
+          <t>UGEL HUARAZ</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="n">
@@ -26957,6 +30767,16 @@
           <t>020203</t>
         </is>
       </c>
+      <c r="P386" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q386" t="inlineStr">
+        <is>
+          <t>UGEL AIJA</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="n">
@@ -27026,6 +30846,16 @@
           <t>020204</t>
         </is>
       </c>
+      <c r="P387" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q387" t="inlineStr">
+        <is>
+          <t>UGEL AIJA</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="n">
@@ -27095,6 +30925,16 @@
           <t>020204</t>
         </is>
       </c>
+      <c r="P388" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q388" t="inlineStr">
+        <is>
+          <t>UGEL AIJA</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
@@ -27164,6 +31004,16 @@
           <t>020205</t>
         </is>
       </c>
+      <c r="P389" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q389" t="inlineStr">
+        <is>
+          <t>UGEL AIJA</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="n">
@@ -27233,6 +31083,16 @@
           <t>020205</t>
         </is>
       </c>
+      <c r="P390" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q390" t="inlineStr">
+        <is>
+          <t>UGEL AIJA</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="n">
@@ -27302,6 +31162,16 @@
           <t>020201</t>
         </is>
       </c>
+      <c r="P391" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q391" t="inlineStr">
+        <is>
+          <t>UGEL AIJA</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
@@ -27371,6 +31241,16 @@
           <t>020201</t>
         </is>
       </c>
+      <c r="P392" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q392" t="inlineStr">
+        <is>
+          <t>UGEL AIJA</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="n">
@@ -27440,6 +31320,16 @@
           <t>020305</t>
         </is>
       </c>
+      <c r="P393" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q393" t="inlineStr">
+        <is>
+          <t>UGEL ANTONIO RAYMONDI</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="n">
@@ -27509,6 +31399,16 @@
           <t>020604</t>
         </is>
       </c>
+      <c r="P394" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q394" t="inlineStr">
+        <is>
+          <t>UGEL CARHUÁZ</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="n">
@@ -27578,6 +31478,16 @@
           <t>020604</t>
         </is>
       </c>
+      <c r="P395" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q395" t="inlineStr">
+        <is>
+          <t>UGEL CARHUÁZ</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="n">
@@ -27647,6 +31557,16 @@
           <t>020604</t>
         </is>
       </c>
+      <c r="P396" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q396" t="inlineStr">
+        <is>
+          <t>UGEL CARHUÁZ</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="n">
@@ -27716,6 +31636,16 @@
           <t>060202</t>
         </is>
       </c>
+      <c r="P397" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="Q397" t="inlineStr">
+        <is>
+          <t>UGEL CAJABAMBA</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="n">
@@ -27785,6 +31715,16 @@
           <t>060202</t>
         </is>
       </c>
+      <c r="P398" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="Q398" t="inlineStr">
+        <is>
+          <t>UGEL CAJABAMBA</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="n">
@@ -27854,6 +31794,16 @@
           <t>060202</t>
         </is>
       </c>
+      <c r="P399" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="Q399" t="inlineStr">
+        <is>
+          <t>UGEL CAJABAMBA</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="n">
@@ -27923,6 +31873,16 @@
           <t>200114</t>
         </is>
       </c>
+      <c r="P400" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q400" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOGRANDE</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="n">
@@ -27992,6 +31952,16 @@
           <t>200114</t>
         </is>
       </c>
+      <c r="P401" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q401" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOGRANDE</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="n">
@@ -28061,6 +32031,16 @@
           <t>200701</t>
         </is>
       </c>
+      <c r="P402" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q402" t="inlineStr">
+        <is>
+          <t>UGEL TALARA</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="n">
@@ -28130,6 +32110,16 @@
           <t>200101</t>
         </is>
       </c>
+      <c r="P403" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q403" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="n">
@@ -28199,6 +32189,16 @@
           <t>200603</t>
         </is>
       </c>
+      <c r="P404" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q404" t="inlineStr">
+        <is>
+          <t>UGEL SULLANA</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="n">
@@ -28268,6 +32268,16 @@
           <t>200603</t>
         </is>
       </c>
+      <c r="P405" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q405" t="inlineStr">
+        <is>
+          <t>UGEL SULLANA</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="n">
@@ -28335,6 +32345,16 @@
       <c r="O406" t="inlineStr">
         <is>
           <t>200603</t>
+        </is>
+      </c>
+      <c r="P406" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q406" t="inlineStr">
+        <is>
+          <t>UGEL SULLANA</t>
         </is>
       </c>
     </row>
@@ -28386,6 +32406,8 @@
       <c r="M407" t="inlineStr"/>
       <c r="N407" t="inlineStr"/>
       <c r="O407" t="inlineStr"/>
+      <c r="P407" t="inlineStr"/>
+      <c r="Q407" t="inlineStr"/>
     </row>
     <row r="408">
       <c r="A408" t="n">
@@ -28455,6 +32477,16 @@
           <t>150305</t>
         </is>
       </c>
+      <c r="P408" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="Q408" t="inlineStr">
+        <is>
+          <t>UGEL 11 CAJATAMBO</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="n">
@@ -28524,6 +32556,16 @@
           <t>150807</t>
         </is>
       </c>
+      <c r="P409" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="Q409" t="inlineStr">
+        <is>
+          <t>UGEL 09 HUAURA</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="n">
@@ -28593,6 +32635,16 @@
           <t>200107</t>
         </is>
       </c>
+      <c r="P410" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q410" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="n">
@@ -28662,6 +32714,16 @@
           <t>200114</t>
         </is>
       </c>
+      <c r="P411" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q411" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOGRANDE</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="n">
@@ -28731,6 +32793,16 @@
           <t>200114</t>
         </is>
       </c>
+      <c r="P412" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q412" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOGRANDE</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="n">
@@ -28800,6 +32872,16 @@
           <t>200114</t>
         </is>
       </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOGRANDE</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="n">
@@ -28869,6 +32951,16 @@
           <t>200114</t>
         </is>
       </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOGRANDE</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="n">
@@ -28938,6 +33030,16 @@
           <t>200107</t>
         </is>
       </c>
+      <c r="P415" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q415" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="n">
@@ -29007,6 +33109,16 @@
           <t>240202</t>
         </is>
       </c>
+      <c r="P416" t="inlineStr">
+        <is>
+          <t>DRE TUMBES</t>
+        </is>
+      </c>
+      <c r="Q416" t="inlineStr">
+        <is>
+          <t>UGEL CONTRALMIRANTE VILLAR</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="n">
@@ -29076,6 +33188,16 @@
           <t>060112</t>
         </is>
       </c>
+      <c r="P417" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="Q417" t="inlineStr">
+        <is>
+          <t>UGEL CAJAMARCA</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="n">
@@ -29145,6 +33267,16 @@
           <t>150728</t>
         </is>
       </c>
+      <c r="P418" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="Q418" t="inlineStr">
+        <is>
+          <t>UGEL 15 HUAROCHIRÍ</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="n">
@@ -29214,6 +33346,16 @@
           <t>150202</t>
         </is>
       </c>
+      <c r="P419" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="Q419" t="inlineStr">
+        <is>
+          <t>UGEL 16 BARRANCA</t>
+        </is>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="n">
@@ -29283,6 +33425,16 @@
           <t>150713</t>
         </is>
       </c>
+      <c r="P420" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="Q420" t="inlineStr">
+        <is>
+          <t>UGEL 15 HUAROCHIRÍ</t>
+        </is>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="n">
@@ -29352,6 +33504,16 @@
           <t>150606</t>
         </is>
       </c>
+      <c r="P421" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="Q421" t="inlineStr">
+        <is>
+          <t>UGEL 10 HUARAL</t>
+        </is>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="n">
@@ -29421,6 +33583,16 @@
           <t>200801</t>
         </is>
       </c>
+      <c r="P422" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q422" t="inlineStr">
+        <is>
+          <t>UGEL SECHURA</t>
+        </is>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="n">
@@ -29490,6 +33662,16 @@
           <t>200801</t>
         </is>
       </c>
+      <c r="P423" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q423" t="inlineStr">
+        <is>
+          <t>UGEL SECHURA</t>
+        </is>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="n">
@@ -29559,6 +33741,16 @@
           <t>200601</t>
         </is>
       </c>
+      <c r="P424" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q424" t="inlineStr">
+        <is>
+          <t>UGEL SULLANA</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="n">
@@ -29628,6 +33820,16 @@
           <t>200701</t>
         </is>
       </c>
+      <c r="P425" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q425" t="inlineStr">
+        <is>
+          <t>UGEL TALARA</t>
+        </is>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="n">
@@ -29697,6 +33899,16 @@
           <t>200111</t>
         </is>
       </c>
+      <c r="P426" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q426" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOGRANDE</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="n">
@@ -29766,6 +33978,16 @@
           <t>200107</t>
         </is>
       </c>
+      <c r="P427" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q427" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="n">
@@ -29835,6 +34057,16 @@
           <t>200107</t>
         </is>
       </c>
+      <c r="P428" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q428" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="n">
@@ -29904,6 +34136,16 @@
           <t>200110</t>
         </is>
       </c>
+      <c r="P429" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q429" t="inlineStr">
+        <is>
+          <t>UGEL LA UNIÓN</t>
+        </is>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="n">
@@ -29973,6 +34215,16 @@
           <t>200101</t>
         </is>
       </c>
+      <c r="P430" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q430" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="n">
@@ -30042,6 +34294,16 @@
           <t>200101</t>
         </is>
       </c>
+      <c r="P431" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q431" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="n">
@@ -30111,6 +34373,16 @@
           <t>200101</t>
         </is>
       </c>
+      <c r="P432" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q432" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="n">
@@ -30180,6 +34452,16 @@
           <t>200114</t>
         </is>
       </c>
+      <c r="P433" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q433" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOGRANDE</t>
+        </is>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="n">
@@ -30249,6 +34531,16 @@
           <t>200114</t>
         </is>
       </c>
+      <c r="P434" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q434" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOGRANDE</t>
+        </is>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="n">
@@ -30318,6 +34610,16 @@
           <t>200114</t>
         </is>
       </c>
+      <c r="P435" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q435" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOGRANDE</t>
+        </is>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="n">
@@ -30387,6 +34689,16 @@
           <t>200114</t>
         </is>
       </c>
+      <c r="P436" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q436" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOGRANDE</t>
+        </is>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="n">
@@ -30456,6 +34768,16 @@
           <t>200105</t>
         </is>
       </c>
+      <c r="P437" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q437" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="n">
@@ -30525,6 +34847,16 @@
           <t>200110</t>
         </is>
       </c>
+      <c r="P438" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q438" t="inlineStr">
+        <is>
+          <t>UGEL LA UNIÓN</t>
+        </is>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="n">
@@ -30594,6 +34926,16 @@
           <t>200101</t>
         </is>
       </c>
+      <c r="P439" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q439" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="n">
@@ -30663,6 +35005,16 @@
           <t>200114</t>
         </is>
       </c>
+      <c r="P440" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q440" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOGRANDE</t>
+        </is>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="n">
@@ -30732,6 +35084,16 @@
           <t>200101</t>
         </is>
       </c>
+      <c r="P441" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q441" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="n">
@@ -30801,6 +35163,16 @@
           <t>200101</t>
         </is>
       </c>
+      <c r="P442" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q442" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="n">
@@ -30870,6 +35242,16 @@
           <t>200101</t>
         </is>
       </c>
+      <c r="P443" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q443" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="n">
@@ -30939,6 +35321,16 @@
           <t>240203</t>
         </is>
       </c>
+      <c r="P444" t="inlineStr">
+        <is>
+          <t>DRE TUMBES</t>
+        </is>
+      </c>
+      <c r="Q444" t="inlineStr">
+        <is>
+          <t>UGEL CONTRALMIRANTE VILLAR</t>
+        </is>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="n">
@@ -31008,6 +35400,16 @@
           <t>240203</t>
         </is>
       </c>
+      <c r="P445" t="inlineStr">
+        <is>
+          <t>DRE TUMBES</t>
+        </is>
+      </c>
+      <c r="Q445" t="inlineStr">
+        <is>
+          <t>UGEL CONTRALMIRANTE VILLAR</t>
+        </is>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="n">
@@ -31077,6 +35479,16 @@
           <t>240202</t>
         </is>
       </c>
+      <c r="P446" t="inlineStr">
+        <is>
+          <t>DRE TUMBES</t>
+        </is>
+      </c>
+      <c r="Q446" t="inlineStr">
+        <is>
+          <t>UGEL CONTRALMIRANTE VILLAR</t>
+        </is>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="n">
@@ -31146,6 +35558,16 @@
           <t>240105</t>
         </is>
       </c>
+      <c r="P447" t="inlineStr">
+        <is>
+          <t>DRE TUMBES</t>
+        </is>
+      </c>
+      <c r="Q447" t="inlineStr">
+        <is>
+          <t>UGEL TUMBES</t>
+        </is>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="n">
@@ -31215,6 +35637,16 @@
           <t>200303</t>
         </is>
       </c>
+      <c r="P448" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q448" t="inlineStr">
+        <is>
+          <t>UGEL HUANCABAMBA</t>
+        </is>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="n">
@@ -31284,6 +35716,16 @@
           <t>021302</t>
         </is>
       </c>
+      <c r="P449" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q449" t="inlineStr">
+        <is>
+          <t>UGEL MARISCAL LUZURIAGA</t>
+        </is>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="n">
@@ -31353,6 +35795,16 @@
           <t>200402</t>
         </is>
       </c>
+      <c r="P450" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q450" t="inlineStr">
+        <is>
+          <t>UGEL MORROPÓN</t>
+        </is>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="n">
@@ -31422,6 +35874,16 @@
           <t>200402</t>
         </is>
       </c>
+      <c r="P451" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q451" t="inlineStr">
+        <is>
+          <t>UGEL MORROPÓN</t>
+        </is>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="n">
@@ -31491,6 +35953,16 @@
           <t>021801</t>
         </is>
       </c>
+      <c r="P452" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q452" t="inlineStr">
+        <is>
+          <t>UGEL SANTA</t>
+        </is>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="n">
@@ -31560,6 +36032,16 @@
           <t>022005</t>
         </is>
       </c>
+      <c r="P453" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q453" t="inlineStr">
+        <is>
+          <t>UGEL YUNGAY</t>
+        </is>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="n">
@@ -31629,6 +36111,16 @@
           <t>022005</t>
         </is>
       </c>
+      <c r="P454" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q454" t="inlineStr">
+        <is>
+          <t>UGEL YUNGAY</t>
+        </is>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="n">
@@ -31698,6 +36190,16 @@
           <t>200406</t>
         </is>
       </c>
+      <c r="P455" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q455" t="inlineStr">
+        <is>
+          <t>UGEL MORROPÓN</t>
+        </is>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="n">
@@ -31767,6 +36269,16 @@
           <t>200406</t>
         </is>
       </c>
+      <c r="P456" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q456" t="inlineStr">
+        <is>
+          <t>UGEL MORROPÓN</t>
+        </is>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="n">
@@ -31836,6 +36348,16 @@
           <t>200401</t>
         </is>
       </c>
+      <c r="P457" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q457" t="inlineStr">
+        <is>
+          <t>UGEL CHULUCANAS</t>
+        </is>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="n">
@@ -31905,6 +36427,16 @@
           <t>200401</t>
         </is>
       </c>
+      <c r="P458" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q458" t="inlineStr">
+        <is>
+          <t>UGEL CHULUCANAS</t>
+        </is>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="n">
@@ -31974,6 +36506,16 @@
           <t>200401</t>
         </is>
       </c>
+      <c r="P459" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q459" t="inlineStr">
+        <is>
+          <t>UGEL CHULUCANAS</t>
+        </is>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="n">
@@ -32043,6 +36585,16 @@
           <t>200401</t>
         </is>
       </c>
+      <c r="P460" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q460" t="inlineStr">
+        <is>
+          <t>UGEL CHULUCANAS</t>
+        </is>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="n">
@@ -32112,6 +36664,16 @@
           <t>200402</t>
         </is>
       </c>
+      <c r="P461" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q461" t="inlineStr">
+        <is>
+          <t>UGEL MORROPÓN</t>
+        </is>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="n">
@@ -32181,6 +36743,16 @@
           <t>021701</t>
         </is>
       </c>
+      <c r="P462" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q462" t="inlineStr">
+        <is>
+          <t>UGEL RECUAY</t>
+        </is>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="n">
@@ -32250,6 +36822,16 @@
           <t>021809</t>
         </is>
       </c>
+      <c r="P463" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q463" t="inlineStr">
+        <is>
+          <t>UGEL SANTA</t>
+        </is>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="n">
@@ -32319,6 +36901,16 @@
           <t>021802</t>
         </is>
       </c>
+      <c r="P464" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q464" t="inlineStr">
+        <is>
+          <t>UGEL SANTA</t>
+        </is>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="n">
@@ -32388,6 +36980,16 @@
           <t>022001</t>
         </is>
       </c>
+      <c r="P465" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q465" t="inlineStr">
+        <is>
+          <t>UGEL YUNGAY</t>
+        </is>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="n">
@@ -32457,6 +37059,16 @@
           <t>200407</t>
         </is>
       </c>
+      <c r="P466" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q466" t="inlineStr">
+        <is>
+          <t>UGEL MORROPÓN</t>
+        </is>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="n">
@@ -32526,6 +37138,16 @@
           <t>021410</t>
         </is>
       </c>
+      <c r="P467" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q467" t="inlineStr">
+        <is>
+          <t>UGEL OCROS</t>
+        </is>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="n">
@@ -32595,6 +37217,16 @@
           <t>021410</t>
         </is>
       </c>
+      <c r="P468" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q468" t="inlineStr">
+        <is>
+          <t>UGEL OCROS</t>
+        </is>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="n">
@@ -32664,6 +37296,16 @@
           <t>200202</t>
         </is>
       </c>
+      <c r="P469" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q469" t="inlineStr">
+        <is>
+          <t>UGEL CHULUCANAS</t>
+        </is>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="n">
@@ -32733,6 +37375,16 @@
           <t>200304</t>
         </is>
       </c>
+      <c r="P470" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q470" t="inlineStr">
+        <is>
+          <t>UGEL HUARMACA</t>
+        </is>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="n">
@@ -32802,6 +37454,16 @@
           <t>200402</t>
         </is>
       </c>
+      <c r="P471" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q471" t="inlineStr">
+        <is>
+          <t>UGEL MORROPÓN</t>
+        </is>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="n">
@@ -32871,6 +37533,16 @@
           <t>110101</t>
         </is>
       </c>
+      <c r="P472" t="inlineStr">
+        <is>
+          <t>DRE ICA</t>
+        </is>
+      </c>
+      <c r="Q472" t="inlineStr">
+        <is>
+          <t>UGEL ICA</t>
+        </is>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="n">
@@ -32940,6 +37612,16 @@
           <t>110403</t>
         </is>
       </c>
+      <c r="P473" t="inlineStr">
+        <is>
+          <t>DRE ICA</t>
+        </is>
+      </c>
+      <c r="Q473" t="inlineStr">
+        <is>
+          <t>UGEL PALPA</t>
+        </is>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="n">
@@ -33009,6 +37691,16 @@
           <t>021204</t>
         </is>
       </c>
+      <c r="P474" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q474" t="inlineStr">
+        <is>
+          <t>UGEL HUAYLAS</t>
+        </is>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="n">
@@ -33078,6 +37770,16 @@
           <t>021206</t>
         </is>
       </c>
+      <c r="P475" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q475" t="inlineStr">
+        <is>
+          <t>UGEL HUAYLAS</t>
+        </is>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="n">
@@ -33147,6 +37849,16 @@
           <t>021404</t>
         </is>
       </c>
+      <c r="P476" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q476" t="inlineStr">
+        <is>
+          <t>UGEL OCROS</t>
+        </is>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="n">
@@ -33216,6 +37928,16 @@
           <t>021906</t>
         </is>
       </c>
+      <c r="P477" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q477" t="inlineStr">
+        <is>
+          <t>UGEL SIHUAS</t>
+        </is>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="n">
@@ -33285,6 +38007,16 @@
           <t>021801</t>
         </is>
       </c>
+      <c r="P478" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q478" t="inlineStr">
+        <is>
+          <t>UGEL SANTA</t>
+        </is>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="n">
@@ -33354,6 +38086,16 @@
           <t>022005</t>
         </is>
       </c>
+      <c r="P479" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q479" t="inlineStr">
+        <is>
+          <t>UGEL YUNGAY</t>
+        </is>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="n">
@@ -33423,6 +38165,16 @@
           <t>022005</t>
         </is>
       </c>
+      <c r="P480" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q480" t="inlineStr">
+        <is>
+          <t>UGEL YUNGAY</t>
+        </is>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="n">
@@ -33492,6 +38244,16 @@
           <t>022008</t>
         </is>
       </c>
+      <c r="P481" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q481" t="inlineStr">
+        <is>
+          <t>UGEL YUNGAY</t>
+        </is>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="n">
@@ -33561,6 +38323,16 @@
           <t>021809</t>
         </is>
       </c>
+      <c r="P482" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q482" t="inlineStr">
+        <is>
+          <t>UGEL SANTA</t>
+        </is>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="n">
@@ -33628,6 +38400,16 @@
       <c r="O483" t="inlineStr">
         <is>
           <t>021809</t>
+        </is>
+      </c>
+      <c r="P483" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q483" t="inlineStr">
+        <is>
+          <t>UGEL SANTA</t>
         </is>
       </c>
     </row>
@@ -33679,6 +38461,8 @@
       <c r="M484" t="inlineStr"/>
       <c r="N484" t="inlineStr"/>
       <c r="O484" t="inlineStr"/>
+      <c r="P484" t="inlineStr"/>
+      <c r="Q484" t="inlineStr"/>
     </row>
     <row r="485">
       <c r="A485" t="n">
@@ -33748,6 +38532,16 @@
           <t>021708</t>
         </is>
       </c>
+      <c r="P485" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q485" t="inlineStr">
+        <is>
+          <t>UGEL RECUAY</t>
+        </is>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="n">
@@ -33817,6 +38611,16 @@
           <t>021806</t>
         </is>
       </c>
+      <c r="P486" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q486" t="inlineStr">
+        <is>
+          <t>UGEL SANTA</t>
+        </is>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="n">
@@ -33886,6 +38690,16 @@
           <t>022005</t>
         </is>
       </c>
+      <c r="P487" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q487" t="inlineStr">
+        <is>
+          <t>UGEL YUNGAY</t>
+        </is>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="n">
@@ -33955,6 +38769,16 @@
           <t>022005</t>
         </is>
       </c>
+      <c r="P488" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q488" t="inlineStr">
+        <is>
+          <t>UGEL YUNGAY</t>
+        </is>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="n">
@@ -34024,6 +38848,16 @@
           <t>022005</t>
         </is>
       </c>
+      <c r="P489" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q489" t="inlineStr">
+        <is>
+          <t>UGEL YUNGAY</t>
+        </is>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="n">
@@ -34093,6 +38927,16 @@
           <t>021701</t>
         </is>
       </c>
+      <c r="P490" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q490" t="inlineStr">
+        <is>
+          <t>UGEL RECUAY</t>
+        </is>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="n">
@@ -34162,6 +39006,16 @@
           <t>021809</t>
         </is>
       </c>
+      <c r="P491" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q491" t="inlineStr">
+        <is>
+          <t>UGEL SANTA</t>
+        </is>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="n">
@@ -34231,6 +39085,16 @@
           <t>022005</t>
         </is>
       </c>
+      <c r="P492" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q492" t="inlineStr">
+        <is>
+          <t>UGEL YUNGAY</t>
+        </is>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="n">
@@ -34300,6 +39164,16 @@
           <t>022008</t>
         </is>
       </c>
+      <c r="P493" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q493" t="inlineStr">
+        <is>
+          <t>UGEL YUNGAY</t>
+        </is>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="n">
@@ -34369,6 +39243,16 @@
           <t>200402</t>
         </is>
       </c>
+      <c r="P494" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q494" t="inlineStr">
+        <is>
+          <t>UGEL MORROPÓN</t>
+        </is>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="n">
@@ -34438,6 +39322,16 @@
           <t>200404</t>
         </is>
       </c>
+      <c r="P495" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q495" t="inlineStr">
+        <is>
+          <t>UGEL CHULUCANAS</t>
+        </is>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="n">
@@ -34507,6 +39401,16 @@
           <t>200404</t>
         </is>
       </c>
+      <c r="P496" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q496" t="inlineStr">
+        <is>
+          <t>UGEL CHULUCANAS</t>
+        </is>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="n">
@@ -34576,6 +39480,16 @@
           <t>200201</t>
         </is>
       </c>
+      <c r="P497" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q497" t="inlineStr">
+        <is>
+          <t>UGEL AYABACA</t>
+        </is>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="n">
@@ -34645,6 +39559,16 @@
           <t>200202</t>
         </is>
       </c>
+      <c r="P498" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q498" t="inlineStr">
+        <is>
+          <t>UGEL CHULUCANAS</t>
+        </is>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="n">
@@ -34714,6 +39638,16 @@
           <t>200405</t>
         </is>
       </c>
+      <c r="P499" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q499" t="inlineStr">
+        <is>
+          <t>UGEL MORROPÓN</t>
+        </is>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="n">
@@ -34783,6 +39717,16 @@
           <t>200404</t>
         </is>
       </c>
+      <c r="P500" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q500" t="inlineStr">
+        <is>
+          <t>UGEL CHULUCANAS</t>
+        </is>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="n">
@@ -34852,6 +39796,16 @@
           <t>200201</t>
         </is>
       </c>
+      <c r="P501" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q501" t="inlineStr">
+        <is>
+          <t>UGEL AYABACA</t>
+        </is>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="n">
@@ -34921,6 +39875,16 @@
           <t>200202</t>
         </is>
       </c>
+      <c r="P502" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q502" t="inlineStr">
+        <is>
+          <t>UGEL CHULUCANAS</t>
+        </is>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="n">
@@ -34990,6 +39954,16 @@
           <t>021511</t>
         </is>
       </c>
+      <c r="P503" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q503" t="inlineStr">
+        <is>
+          <t>UGEL PALLASCA</t>
+        </is>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="n">
@@ -35059,6 +40033,16 @@
           <t>021302</t>
         </is>
       </c>
+      <c r="P504" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q504" t="inlineStr">
+        <is>
+          <t>UGEL MARISCAL LUZURIAGA</t>
+        </is>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="n">
@@ -35128,6 +40112,16 @@
           <t>200201</t>
         </is>
       </c>
+      <c r="P505" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q505" t="inlineStr">
+        <is>
+          <t>UGEL AYABACA</t>
+        </is>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="n">
@@ -35197,6 +40191,16 @@
           <t>021801</t>
         </is>
       </c>
+      <c r="P506" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q506" t="inlineStr">
+        <is>
+          <t>UGEL SANTA</t>
+        </is>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="n">
@@ -35266,6 +40270,16 @@
           <t>130208</t>
         </is>
       </c>
+      <c r="P507" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="Q507" t="inlineStr">
+        <is>
+          <t>UGEL ASCOPE</t>
+        </is>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="n">
@@ -35335,6 +40349,16 @@
           <t>020109</t>
         </is>
       </c>
+      <c r="P508" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q508" t="inlineStr">
+        <is>
+          <t>UGEL HUARAZ</t>
+        </is>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="n">
@@ -35404,6 +40428,16 @@
           <t>020201</t>
         </is>
       </c>
+      <c r="P509" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q509" t="inlineStr">
+        <is>
+          <t>UGEL AIJA</t>
+        </is>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="n">
@@ -35473,6 +40507,16 @@
           <t>020804</t>
         </is>
       </c>
+      <c r="P510" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q510" t="inlineStr">
+        <is>
+          <t>UGEL CASMA</t>
+        </is>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="n">
@@ -35542,6 +40586,16 @@
           <t>020109</t>
         </is>
       </c>
+      <c r="P511" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q511" t="inlineStr">
+        <is>
+          <t>UGEL HUARAZ</t>
+        </is>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="n">
@@ -35611,6 +40665,16 @@
           <t>240203</t>
         </is>
       </c>
+      <c r="P512" t="inlineStr">
+        <is>
+          <t>DRE TUMBES</t>
+        </is>
+      </c>
+      <c r="Q512" t="inlineStr">
+        <is>
+          <t>UGEL CONTRALMIRANTE VILLAR</t>
+        </is>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="n">
@@ -35680,6 +40744,16 @@
           <t>200402</t>
         </is>
       </c>
+      <c r="P513" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q513" t="inlineStr">
+        <is>
+          <t>UGEL MORROPÓN</t>
+        </is>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="n">
@@ -35749,6 +40823,16 @@
           <t>200405</t>
         </is>
       </c>
+      <c r="P514" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q514" t="inlineStr">
+        <is>
+          <t>UGEL MORROPÓN</t>
+        </is>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="n">
@@ -35818,6 +40902,16 @@
           <t>200405</t>
         </is>
       </c>
+      <c r="P515" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q515" t="inlineStr">
+        <is>
+          <t>UGEL MORROPÓN</t>
+        </is>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="n">
@@ -35891,6 +40985,16 @@
           <t>131101</t>
         </is>
       </c>
+      <c r="P516" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="Q516" t="inlineStr">
+        <is>
+          <t>UGEL GRAN CHIMÚ</t>
+        </is>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="n">
@@ -35964,6 +41068,16 @@
           <t>120608</t>
         </is>
       </c>
+      <c r="P517" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="Q517" t="inlineStr">
+        <is>
+          <t>UGEL RIO TAMBO</t>
+        </is>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="n">
@@ -36035,6 +41149,16 @@
       <c r="O518" t="inlineStr">
         <is>
           <t>200202</t>
+        </is>
+      </c>
+      <c r="P518" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q518" t="inlineStr">
+        <is>
+          <t>UGEL CHULUCANAS</t>
         </is>
       </c>
     </row>

--- a/output/bases_limpias/Grupo_03_MODULOS/df_ugrd_me.xlsx
+++ b/output/bases_limpias/Grupo_03_MODULOS/df_ugrd_me.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q518"/>
+  <dimension ref="A1:R518"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -502,6 +502,11 @@
           <t>ugel</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>fuente</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -581,6 +586,11 @@
           <t>UGEL VIRÚ</t>
         </is>
       </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -660,6 +670,11 @@
           <t>UGEL VIRÚ</t>
         </is>
       </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -739,6 +754,11 @@
           <t>UGEL VIRÚ</t>
         </is>
       </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -818,6 +838,11 @@
           <t>UGEL 01 - EL PORVENIR</t>
         </is>
       </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -897,6 +922,11 @@
           <t>UGEL 03 - TRUJILLO NOR OESTE</t>
         </is>
       </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -976,6 +1006,11 @@
           <t>UGEL FERREÑAFE</t>
         </is>
       </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1055,6 +1090,11 @@
           <t>UGEL FERREÑAFE</t>
         </is>
       </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1134,6 +1174,11 @@
           <t>UGEL 01 - EL PORVENIR</t>
         </is>
       </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1213,6 +1258,11 @@
           <t>UGEL 01 - EL PORVENIR</t>
         </is>
       </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1292,6 +1342,11 @@
           <t>UGEL PACASMAYO</t>
         </is>
       </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1371,6 +1426,11 @@
           <t>UGEL CHICLAYO</t>
         </is>
       </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1450,6 +1510,11 @@
           <t>UGEL FERREÑAFE</t>
         </is>
       </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1529,6 +1594,11 @@
           <t>UGEL FERREÑAFE</t>
         </is>
       </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1608,6 +1678,11 @@
           <t>UGEL FERREÑAFE</t>
         </is>
       </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1687,6 +1762,11 @@
           <t>UGEL CASTROVIRREYNA</t>
         </is>
       </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1766,6 +1846,11 @@
           <t>UGEL CASTROVIRREYNA</t>
         </is>
       </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1845,6 +1930,11 @@
           <t>UGEL CASTROVIRREYNA</t>
         </is>
       </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1924,6 +2014,11 @@
           <t>UGEL CASTROVIRREYNA</t>
         </is>
       </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2003,6 +2098,11 @@
           <t>UGEL CHURCAMPA</t>
         </is>
       </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2082,6 +2182,11 @@
           <t>UGEL CHURCAMPA</t>
         </is>
       </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2161,6 +2266,11 @@
           <t>UGEL CHURCAMPA</t>
         </is>
       </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2240,6 +2350,11 @@
           <t>UGEL CHURCAMPA</t>
         </is>
       </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2319,6 +2434,11 @@
           <t>UGEL ANGARAES</t>
         </is>
       </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2398,6 +2518,11 @@
           <t>UGEL ANGARAES</t>
         </is>
       </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2477,6 +2602,11 @@
           <t>UGEL ANGARAES</t>
         </is>
       </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2556,6 +2686,11 @@
           <t>UGEL ANGARAES</t>
         </is>
       </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2635,6 +2770,11 @@
           <t>UGEL HUAYTARÁ</t>
         </is>
       </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2714,6 +2854,11 @@
           <t>UGEL HUAYTARÁ</t>
         </is>
       </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2793,6 +2938,11 @@
           <t>UGEL OTUZCO</t>
         </is>
       </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2872,6 +3022,11 @@
           <t>UGEL OTUZCO</t>
         </is>
       </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2951,6 +3106,11 @@
           <t>UGEL VIRÚ</t>
         </is>
       </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3030,6 +3190,11 @@
           <t>UGEL GRAN CHIMÚ</t>
         </is>
       </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3109,6 +3274,11 @@
           <t>UGEL GRAN CHIMÚ</t>
         </is>
       </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3188,6 +3358,11 @@
           <t>UGEL ASCOPE</t>
         </is>
       </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -3267,6 +3442,11 @@
           <t>UGEL 03 - TRUJILLO NOR OESTE</t>
         </is>
       </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -3346,6 +3526,11 @@
           <t>UGEL VIRÚ</t>
         </is>
       </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -3390,13 +3575,42 @@
         </is>
       </c>
       <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>CHEPEN</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>PUEBLO NUEVO</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>130403</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>UGEL CHEPÉN</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -3476,6 +3690,11 @@
           <t>UGEL PACASMAYO</t>
         </is>
       </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -3555,6 +3774,11 @@
           <t>UGEL 01 - EL PORVENIR</t>
         </is>
       </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -3634,6 +3858,11 @@
           <t>UGEL VIRÚ</t>
         </is>
       </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -3713,6 +3942,11 @@
           <t>UGEL VIRÚ</t>
         </is>
       </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -3792,6 +4026,11 @@
           <t>UGEL CHEPEN</t>
         </is>
       </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -3871,6 +4110,11 @@
           <t>UGEL 02 - LA ESPERANZA</t>
         </is>
       </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -3950,6 +4194,11 @@
           <t>UGEL GRAN CHIMÚ</t>
         </is>
       </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -4029,6 +4278,11 @@
           <t>UGEL ASCOPE</t>
         </is>
       </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -4108,6 +4362,11 @@
           <t>UGEL ASCOPE</t>
         </is>
       </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -4187,6 +4446,11 @@
           <t>UGEL ASCOPE</t>
         </is>
       </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -4266,6 +4530,11 @@
           <t>UGEL GRAN CHIMÚ</t>
         </is>
       </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -4345,6 +4614,11 @@
           <t>UGEL GRAN CHIMÚ</t>
         </is>
       </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -4424,6 +4698,11 @@
           <t>UGEL OTUZCO</t>
         </is>
       </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -4503,6 +4782,11 @@
           <t>UGEL OTUZCO</t>
         </is>
       </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -4547,13 +4831,42 @@
         </is>
       </c>
       <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>VIRU</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>VIRU</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr"/>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>131201</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>UGEL VIRÚ</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -4633,6 +4946,11 @@
           <t>UGEL GRAN CHIMÚ</t>
         </is>
       </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -4712,6 +5030,11 @@
           <t>UGEL GRAN CHIMÚ</t>
         </is>
       </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -4791,6 +5114,11 @@
           <t>UGEL 02 - LA ESPERANZA</t>
         </is>
       </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -4870,6 +5198,11 @@
           <t>UGEL VIRÚ</t>
         </is>
       </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -4949,6 +5282,11 @@
           <t>UGEL VIRÚ</t>
         </is>
       </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -5028,6 +5366,11 @@
           <t>UGEL VIRÚ</t>
         </is>
       </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -5107,6 +5450,11 @@
           <t>UGEL LAMBAYEQUE</t>
         </is>
       </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -5186,6 +5534,11 @@
           <t>UGEL FERREÑAFE</t>
         </is>
       </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -5265,6 +5618,11 @@
           <t>UGEL FERREÑAFE</t>
         </is>
       </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -5344,6 +5702,11 @@
           <t>UGEL FERREÑAFE</t>
         </is>
       </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -5423,6 +5786,11 @@
           <t>UGEL FERREÑAFE</t>
         </is>
       </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -5502,6 +5870,11 @@
           <t>UGEL FERREÑAFE</t>
         </is>
       </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -5581,6 +5954,11 @@
           <t>UGEL FERREÑAFE</t>
         </is>
       </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -5660,6 +6038,11 @@
           <t>UGEL LAMBAYEQUE</t>
         </is>
       </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -5739,6 +6122,11 @@
           <t>UGEL LAMBAYEQUE</t>
         </is>
       </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -5818,6 +6206,11 @@
           <t>UGEL LAMBAYEQUE</t>
         </is>
       </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -5897,6 +6290,11 @@
           <t>UGEL AIJA</t>
         </is>
       </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -5976,6 +6374,11 @@
           <t>UGEL AIJA</t>
         </is>
       </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -6055,6 +6458,11 @@
           <t>UGEL AIJA</t>
         </is>
       </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -6134,6 +6542,11 @@
           <t>UGEL AIJA</t>
         </is>
       </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -6213,6 +6626,11 @@
           <t>UGEL HUARMEY</t>
         </is>
       </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -6292,6 +6710,11 @@
           <t>UGEL CASMA</t>
         </is>
       </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -6371,6 +6794,11 @@
           <t>UGEL CASMA</t>
         </is>
       </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -6450,6 +6878,11 @@
           <t>UGEL CASMA</t>
         </is>
       </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -6529,6 +6962,11 @@
           <t>UGEL HUARMEY</t>
         </is>
       </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -6608,6 +7046,11 @@
           <t>UGEL CASMA</t>
         </is>
       </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -6687,6 +7130,11 @@
           <t>UGEL HUARMEY</t>
         </is>
       </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -6766,6 +7214,11 @@
           <t>UGEL CORONGO</t>
         </is>
       </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -6845,6 +7298,11 @@
           <t>UGEL BOLOGNESI</t>
         </is>
       </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -6924,6 +7382,11 @@
           <t>UGEL BOLOGNESI</t>
         </is>
       </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -7003,6 +7466,11 @@
           <t>UGEL BOLOGNESI</t>
         </is>
       </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -7082,6 +7550,11 @@
           <t>UGEL CARHUÁZ</t>
         </is>
       </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -7161,6 +7634,11 @@
           <t>UGEL CARHUÁZ</t>
         </is>
       </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -7240,6 +7718,11 @@
           <t>UGEL HUARI</t>
         </is>
       </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -7319,6 +7802,11 @@
           <t>UGEL HUARI</t>
         </is>
       </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -7398,6 +7886,11 @@
           <t>UGEL HUARI</t>
         </is>
       </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -7477,6 +7970,11 @@
           <t>UGEL HUARI</t>
         </is>
       </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -7556,6 +8054,11 @@
           <t>UGEL CASMA</t>
         </is>
       </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -7635,6 +8138,11 @@
           <t>UGEL HUARAZ</t>
         </is>
       </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -7714,6 +8222,11 @@
           <t>UGEL HUARAZ</t>
         </is>
       </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -7793,6 +8306,11 @@
           <t>UGEL CASMA</t>
         </is>
       </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -7872,6 +8390,11 @@
           <t>UGEL AIJA</t>
         </is>
       </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -7951,6 +8474,11 @@
           <t>UGEL AIJA</t>
         </is>
       </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -8030,6 +8558,11 @@
           <t>UGEL CASMA</t>
         </is>
       </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -8109,6 +8642,11 @@
           <t>UGEL AIJA</t>
         </is>
       </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -8188,6 +8726,11 @@
           <t>UGEL HUARMEY</t>
         </is>
       </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -8267,6 +8810,11 @@
           <t>UGEL HUARMEY</t>
         </is>
       </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -8346,6 +8894,11 @@
           <t>UGEL CASMA</t>
         </is>
       </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -8425,6 +8978,11 @@
           <t>UGEL CASMA</t>
         </is>
       </c>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -8504,6 +9062,11 @@
           <t>UGEL CASMA</t>
         </is>
       </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -8583,6 +9146,11 @@
           <t>UGEL CARLOS FERMIN FITZCARRALD</t>
         </is>
       </c>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -8662,6 +9230,11 @@
           <t>UGEL CARLOS FERMIN FITZCARRALD</t>
         </is>
       </c>
+      <c r="R105" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -8741,6 +9314,11 @@
           <t>UGEL CARLOS FERMIN FITZCARRALD</t>
         </is>
       </c>
+      <c r="R106" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -8820,6 +9398,11 @@
           <t>UGEL CARLOS FERMIN FITZCARRALD</t>
         </is>
       </c>
+      <c r="R107" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -8899,6 +9482,11 @@
           <t>UGEL HUARAZ</t>
         </is>
       </c>
+      <c r="R108" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -8978,6 +9566,11 @@
           <t>UGEL HUARAZ</t>
         </is>
       </c>
+      <c r="R109" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -9057,6 +9650,11 @@
           <t>UGEL AIJA</t>
         </is>
       </c>
+      <c r="R110" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -9136,6 +9734,11 @@
           <t>UGEL HUARMEY</t>
         </is>
       </c>
+      <c r="R111" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -9215,6 +9818,11 @@
           <t>UGEL HUARMEY</t>
         </is>
       </c>
+      <c r="R112" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -9294,6 +9902,11 @@
           <t>UGEL HUARMEY</t>
         </is>
       </c>
+      <c r="R113" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -9373,6 +9986,11 @@
           <t>UGEL AIJA</t>
         </is>
       </c>
+      <c r="R114" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -9452,6 +10070,11 @@
           <t>UGEL AIJA</t>
         </is>
       </c>
+      <c r="R115" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -9531,6 +10154,11 @@
           <t>UGEL AIJA</t>
         </is>
       </c>
+      <c r="R116" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -9610,6 +10238,11 @@
           <t>UGEL AIJA</t>
         </is>
       </c>
+      <c r="R117" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -9689,6 +10322,11 @@
           <t>UGEL AIJA</t>
         </is>
       </c>
+      <c r="R118" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -9768,6 +10406,11 @@
           <t>UGEL AIJA</t>
         </is>
       </c>
+      <c r="R119" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -9847,6 +10490,11 @@
           <t>UGEL AIJA</t>
         </is>
       </c>
+      <c r="R120" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -9926,6 +10574,11 @@
           <t>UGEL CASMA</t>
         </is>
       </c>
+      <c r="R121" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -10005,6 +10658,11 @@
           <t>UGEL HUARI</t>
         </is>
       </c>
+      <c r="R122" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -10084,6 +10742,11 @@
           <t>UGEL HUARI</t>
         </is>
       </c>
+      <c r="R123" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -10163,6 +10826,11 @@
           <t>UGEL HUARMEY</t>
         </is>
       </c>
+      <c r="R124" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -10242,6 +10910,11 @@
           <t>UGEL HUARMEY</t>
         </is>
       </c>
+      <c r="R125" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -10321,6 +10994,11 @@
           <t>UGEL HUARMEY</t>
         </is>
       </c>
+      <c r="R126" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -10400,6 +11078,11 @@
           <t>UGEL AIJA</t>
         </is>
       </c>
+      <c r="R127" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -10479,6 +11162,11 @@
           <t>UGEL AIJA</t>
         </is>
       </c>
+      <c r="R128" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -10558,6 +11246,11 @@
           <t>UGEL AIJA</t>
         </is>
       </c>
+      <c r="R129" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -10637,6 +11330,11 @@
           <t>UGEL AIJA</t>
         </is>
       </c>
+      <c r="R130" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -10716,6 +11414,11 @@
           <t>UGEL ANTONIO RAYMONDI</t>
         </is>
       </c>
+      <c r="R131" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -10795,6 +11498,11 @@
           <t>UGEL ANTONIO RAYMONDI</t>
         </is>
       </c>
+      <c r="R132" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -10874,6 +11582,11 @@
           <t>UGEL CARHUÁZ</t>
         </is>
       </c>
+      <c r="R133" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -10953,6 +11666,11 @@
           <t>UGEL CARHUÁZ</t>
         </is>
       </c>
+      <c r="R134" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -11032,6 +11750,11 @@
           <t>UGEL CASMA</t>
         </is>
       </c>
+      <c r="R135" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -11111,6 +11834,11 @@
           <t>UGEL HUARMEY</t>
         </is>
       </c>
+      <c r="R136" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -11190,6 +11918,11 @@
           <t>UGEL HUARMEY</t>
         </is>
       </c>
+      <c r="R137" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -11269,6 +12002,11 @@
           <t>UGEL CAJABAMBA</t>
         </is>
       </c>
+      <c r="R138" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -11348,6 +12086,11 @@
           <t>UGEL CAJABAMBA</t>
         </is>
       </c>
+      <c r="R139" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -11427,6 +12170,11 @@
           <t>UGEL TALARA</t>
         </is>
       </c>
+      <c r="R140" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -11506,6 +12254,11 @@
           <t>UGEL TAMBOGRANDE</t>
         </is>
       </c>
+      <c r="R141" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -11585,6 +12338,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="R142" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -11664,6 +12422,11 @@
           <t>UGEL TAMBOGRANDE</t>
         </is>
       </c>
+      <c r="R143" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -11741,6 +12504,11 @@
       <c r="Q144" t="inlineStr">
         <is>
           <t>UGEL SULLANA</t>
+        </is>
+      </c>
+      <c r="R144" t="inlineStr">
+        <is>
+          <t>UGRD</t>
         </is>
       </c>
     </row>
@@ -11794,6 +12562,11 @@
       <c r="O145" t="inlineStr"/>
       <c r="P145" t="inlineStr"/>
       <c r="Q145" t="inlineStr"/>
+      <c r="R145" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -11873,6 +12646,11 @@
           <t>UGEL 11 CAJATAMBO</t>
         </is>
       </c>
+      <c r="R146" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -11952,6 +12730,11 @@
           <t>UGEL 13 YAUYOS</t>
         </is>
       </c>
+      <c r="R147" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -12031,6 +12814,11 @@
           <t>UGEL 13 YAUYOS</t>
         </is>
       </c>
+      <c r="R148" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -12110,6 +12898,11 @@
           <t>UGEL 15 HUAROCHIRÍ</t>
         </is>
       </c>
+      <c r="R149" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -12189,6 +12982,11 @@
           <t>UGEL 09 HUAURA</t>
         </is>
       </c>
+      <c r="R150" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -12268,6 +13066,11 @@
           <t>UGEL 09 HUAURA</t>
         </is>
       </c>
+      <c r="R151" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -12347,6 +13150,11 @@
           <t>UGEL 12 CANTA</t>
         </is>
       </c>
+      <c r="R152" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -12426,6 +13234,11 @@
           <t>UGEL 13 YAUYOS</t>
         </is>
       </c>
+      <c r="R153" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -12505,6 +13318,11 @@
           <t>UGEL TAMBOGRANDE</t>
         </is>
       </c>
+      <c r="R154" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -12584,6 +13402,11 @@
           <t>UGEL TAMBOGRANDE</t>
         </is>
       </c>
+      <c r="R155" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -12663,6 +13486,11 @@
           <t>UGEL SECHURA</t>
         </is>
       </c>
+      <c r="R156" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -12742,6 +13570,11 @@
           <t>UGEL CONTRALMIRANTE VILLAR</t>
         </is>
       </c>
+      <c r="R157" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -12821,6 +13654,11 @@
           <t>UGEL HUANTA</t>
         </is>
       </c>
+      <c r="R158" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -12900,6 +13738,11 @@
           <t>UGEL HUANTA</t>
         </is>
       </c>
+      <c r="R159" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -12979,6 +13822,11 @@
           <t>UGEL CAJAMARCA</t>
         </is>
       </c>
+      <c r="R160" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -13058,6 +13906,11 @@
           <t>UGEL CAJAMARCA</t>
         </is>
       </c>
+      <c r="R161" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -13137,6 +13990,11 @@
           <t>UGEL CELENDÍN</t>
         </is>
       </c>
+      <c r="R162" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -13216,6 +14074,11 @@
           <t>UGEL CELENDÍN</t>
         </is>
       </c>
+      <c r="R163" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -13295,6 +14158,11 @@
           <t>UGEL CUTERVO</t>
         </is>
       </c>
+      <c r="R164" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -13374,6 +14242,11 @@
           <t>UGEL CUTERVO</t>
         </is>
       </c>
+      <c r="R165" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -13453,6 +14326,11 @@
           <t>UGEL 13 YAUYOS</t>
         </is>
       </c>
+      <c r="R166" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -13532,6 +14410,11 @@
           <t>UGEL 11 CAJATAMBO</t>
         </is>
       </c>
+      <c r="R167" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -13611,6 +14494,11 @@
           <t>UGEL 11 CAJATAMBO</t>
         </is>
       </c>
+      <c r="R168" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -13690,6 +14578,11 @@
           <t>UGEL 15 HUAROCHIRÍ</t>
         </is>
       </c>
+      <c r="R169" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -13769,6 +14662,11 @@
           <t>UGEL 15 HUAROCHIRÍ</t>
         </is>
       </c>
+      <c r="R170" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -13848,6 +14746,11 @@
           <t>UGEL 15 HUAROCHIRÍ</t>
         </is>
       </c>
+      <c r="R171" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -13927,6 +14830,11 @@
           <t>UGEL 15 HUAROCHIRÍ</t>
         </is>
       </c>
+      <c r="R172" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -14006,6 +14914,11 @@
           <t>UGEL 13 YAUYOS</t>
         </is>
       </c>
+      <c r="R173" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -14085,6 +14998,11 @@
           <t>UGEL 10 HUARAL</t>
         </is>
       </c>
+      <c r="R174" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -14164,6 +15082,11 @@
           <t>UGEL 10 HUARAL</t>
         </is>
       </c>
+      <c r="R175" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -14243,6 +15166,11 @@
           <t>UGEL SECHURA</t>
         </is>
       </c>
+      <c r="R176" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -14322,6 +15250,11 @@
           <t>UGEL SECHURA</t>
         </is>
       </c>
+      <c r="R177" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -14401,6 +15334,11 @@
           <t>UGEL SULLANA</t>
         </is>
       </c>
+      <c r="R178" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -14480,6 +15418,11 @@
           <t>UGEL TALARA</t>
         </is>
       </c>
+      <c r="R179" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -14559,6 +15502,11 @@
           <t>UGEL LA UNIÓN</t>
         </is>
       </c>
+      <c r="R180" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -14638,6 +15586,11 @@
           <t>UGEL TAMBOGRANDE</t>
         </is>
       </c>
+      <c r="R181" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -14717,6 +15670,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="R182" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -14796,6 +15754,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="R183" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -14875,6 +15838,11 @@
           <t>UGEL LA UNIÓN</t>
         </is>
       </c>
+      <c r="R184" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -14954,6 +15922,11 @@
           <t>UGEL LA UNIÓN</t>
         </is>
       </c>
+      <c r="R185" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -15033,6 +16006,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="R186" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -15112,6 +16090,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="R187" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -15191,6 +16174,11 @@
           <t>UGEL TAMBOGRANDE</t>
         </is>
       </c>
+      <c r="R188" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -15270,6 +16258,11 @@
           <t>UGEL TAMBOGRANDE</t>
         </is>
       </c>
+      <c r="R189" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -15349,6 +16342,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="R190" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -15428,6 +16426,11 @@
           <t>UGEL LA UNIÓN</t>
         </is>
       </c>
+      <c r="R191" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -15507,6 +16510,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="R192" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -15586,6 +16594,11 @@
           <t>UGEL TAMBOGRANDE</t>
         </is>
       </c>
+      <c r="R193" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -15665,6 +16678,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="R194" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -15744,6 +16762,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="R195" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -15823,6 +16846,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="R196" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -15902,6 +16930,11 @@
           <t>UGEL CONTRALMIRANTE VILLAR</t>
         </is>
       </c>
+      <c r="R197" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -15981,6 +17014,11 @@
           <t>UGEL CONTRALMIRANTE VILLAR</t>
         </is>
       </c>
+      <c r="R198" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -16060,6 +17098,11 @@
           <t>UGEL CONTRALMIRANTE VILLAR</t>
         </is>
       </c>
+      <c r="R199" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -16139,6 +17182,11 @@
           <t>UGEL CONTRALMIRANTE VILLAR</t>
         </is>
       </c>
+      <c r="R200" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -16218,6 +17266,11 @@
           <t>UGEL CONTRALMIRANTE VILLAR</t>
         </is>
       </c>
+      <c r="R201" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -16297,6 +17350,11 @@
           <t>UGEL CONTRALMIRANTE VILLAR</t>
         </is>
       </c>
+      <c r="R202" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -16376,6 +17434,11 @@
           <t>UGEL TUMBES</t>
         </is>
       </c>
+      <c r="R203" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -16455,6 +17518,11 @@
           <t>UGEL CONTRALMIRANTE VILLAR</t>
         </is>
       </c>
+      <c r="R204" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -16534,6 +17602,11 @@
           <t>UGEL TUMBES</t>
         </is>
       </c>
+      <c r="R205" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -16613,6 +17686,11 @@
           <t>UGEL ZARUMILLA</t>
         </is>
       </c>
+      <c r="R206" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -16692,6 +17770,11 @@
           <t>UGEL SAN MIGUEL</t>
         </is>
       </c>
+      <c r="R207" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -16771,6 +17854,11 @@
           <t>UGEL SAN MIGUEL</t>
         </is>
       </c>
+      <c r="R208" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -16850,6 +17938,11 @@
           <t>UGEL CUTERVO</t>
         </is>
       </c>
+      <c r="R209" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -16929,6 +18022,11 @@
           <t>UGEL CAJABAMBA</t>
         </is>
       </c>
+      <c r="R210" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -17008,6 +18106,11 @@
           <t>UGEL CAJABAMBA</t>
         </is>
       </c>
+      <c r="R211" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -17087,6 +18190,11 @@
           <t>UGEL RIO TAMBO</t>
         </is>
       </c>
+      <c r="R212" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -17166,6 +18274,11 @@
           <t>UGEL HUANCABAMBA</t>
         </is>
       </c>
+      <c r="R213" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -17245,6 +18358,11 @@
           <t>UGEL HUANCABAMBA</t>
         </is>
       </c>
+      <c r="R214" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -17324,6 +18442,11 @@
           <t>UGEL AYABACA</t>
         </is>
       </c>
+      <c r="R215" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -17403,6 +18526,11 @@
           <t>UGEL AYABACA</t>
         </is>
       </c>
+      <c r="R216" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -17482,6 +18610,11 @@
           <t>UGEL AYABACA</t>
         </is>
       </c>
+      <c r="R217" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -17561,6 +18694,11 @@
           <t>UGEL AYABACA</t>
         </is>
       </c>
+      <c r="R218" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -17640,6 +18778,11 @@
           <t>UGEL MARISCAL LUZURIAGA</t>
         </is>
       </c>
+      <c r="R219" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -17719,6 +18862,11 @@
           <t>UGEL MARISCAL LUZURIAGA</t>
         </is>
       </c>
+      <c r="R220" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -17798,6 +18946,11 @@
           <t>UGEL MORROPÓN</t>
         </is>
       </c>
+      <c r="R221" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -17877,6 +19030,11 @@
           <t>UGEL MORROPÓN</t>
         </is>
       </c>
+      <c r="R222" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -17956,6 +19114,11 @@
           <t>UGEL CHULUCANAS</t>
         </is>
       </c>
+      <c r="R223" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -18035,6 +19198,11 @@
           <t>UGEL CHULUCANAS</t>
         </is>
       </c>
+      <c r="R224" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -18114,6 +19282,11 @@
           <t>UGEL CHULUCANAS</t>
         </is>
       </c>
+      <c r="R225" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -18193,6 +19366,11 @@
           <t>UGEL MORROPÓN</t>
         </is>
       </c>
+      <c r="R226" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -18272,6 +19450,11 @@
           <t>UGEL RECUAY</t>
         </is>
       </c>
+      <c r="R227" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -18351,6 +19534,11 @@
           <t>UGEL RECUAY</t>
         </is>
       </c>
+      <c r="R228" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -18430,6 +19618,11 @@
           <t>UGEL RECUAY</t>
         </is>
       </c>
+      <c r="R229" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -18509,6 +19702,11 @@
           <t>UGEL RECUAY</t>
         </is>
       </c>
+      <c r="R230" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -18588,6 +19786,11 @@
           <t>UGEL RECUAY</t>
         </is>
       </c>
+      <c r="R231" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -18667,6 +19870,11 @@
           <t>UGEL RECUAY</t>
         </is>
       </c>
+      <c r="R232" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -18746,6 +19954,11 @@
           <t>UGEL RECUAY</t>
         </is>
       </c>
+      <c r="R233" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -18825,6 +20038,11 @@
           <t>UGEL RECUAY</t>
         </is>
       </c>
+      <c r="R234" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -18904,6 +20122,11 @@
           <t>UGEL SANTA</t>
         </is>
       </c>
+      <c r="R235" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -18983,6 +20206,11 @@
           <t>UGEL SANTA</t>
         </is>
       </c>
+      <c r="R236" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -19062,6 +20290,11 @@
           <t>UGEL SANTA</t>
         </is>
       </c>
+      <c r="R237" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -19141,6 +20374,11 @@
           <t>UGEL YUNGAY</t>
         </is>
       </c>
+      <c r="R238" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -19220,6 +20458,11 @@
           <t>UGEL YUNGAY</t>
         </is>
       </c>
+      <c r="R239" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -19299,6 +20542,11 @@
           <t>UGEL MORROPÓN</t>
         </is>
       </c>
+      <c r="R240" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -19378,6 +20626,11 @@
           <t>UGEL OCROS</t>
         </is>
       </c>
+      <c r="R241" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -19457,6 +20710,11 @@
           <t>UGEL OCROS</t>
         </is>
       </c>
+      <c r="R242" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -19536,6 +20794,11 @@
           <t>UGEL MORROPÓN</t>
         </is>
       </c>
+      <c r="R243" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -19615,6 +20878,11 @@
           <t>UGEL MORROPÓN</t>
         </is>
       </c>
+      <c r="R244" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -19694,6 +20962,11 @@
           <t>UGEL HUARMACA</t>
         </is>
       </c>
+      <c r="R245" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -19773,6 +21046,11 @@
           <t>UGEL OCROS</t>
         </is>
       </c>
+      <c r="R246" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -19852,6 +21130,11 @@
           <t>UGEL RECUAY</t>
         </is>
       </c>
+      <c r="R247" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -19931,6 +21214,11 @@
           <t>UGEL HUAYLAS</t>
         </is>
       </c>
+      <c r="R248" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -20010,6 +21298,11 @@
           <t>UGEL HUAYLAS</t>
         </is>
       </c>
+      <c r="R249" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -20089,6 +21382,11 @@
           <t>UGEL HUAYLAS</t>
         </is>
       </c>
+      <c r="R250" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -20168,6 +21466,11 @@
           <t>UGEL HUAYLAS</t>
         </is>
       </c>
+      <c r="R251" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -20247,6 +21550,11 @@
           <t>UGEL HUAYLAS</t>
         </is>
       </c>
+      <c r="R252" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -20326,6 +21634,11 @@
           <t>UGEL OCROS</t>
         </is>
       </c>
+      <c r="R253" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -20405,6 +21718,11 @@
           <t>UGEL OCROS</t>
         </is>
       </c>
+      <c r="R254" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -20484,6 +21802,11 @@
           <t>UGEL RECUAY</t>
         </is>
       </c>
+      <c r="R255" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -20563,6 +21886,11 @@
           <t>UGEL SIHUAS</t>
         </is>
       </c>
+      <c r="R256" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -20642,6 +21970,11 @@
           <t>UGEL SIHUAS</t>
         </is>
       </c>
+      <c r="R257" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -20721,6 +22054,11 @@
           <t>UGEL SANTA</t>
         </is>
       </c>
+      <c r="R258" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -20800,6 +22138,11 @@
           <t>UGEL YUNGAY</t>
         </is>
       </c>
+      <c r="R259" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -20879,6 +22222,11 @@
           <t>UGEL YUNGAY</t>
         </is>
       </c>
+      <c r="R260" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -20958,6 +22306,11 @@
           <t>UGEL YUNGAY</t>
         </is>
       </c>
+      <c r="R261" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -21037,6 +22390,11 @@
           <t>UGEL YUNGAY</t>
         </is>
       </c>
+      <c r="R262" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -21116,6 +22474,11 @@
           <t>UGEL SANTA</t>
         </is>
       </c>
+      <c r="R263" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -21195,6 +22558,11 @@
           <t>UGEL OCROS</t>
         </is>
       </c>
+      <c r="R264" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -21274,6 +22642,11 @@
           <t>UGEL YUNGAY</t>
         </is>
       </c>
+      <c r="R265" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -21353,6 +22726,11 @@
           <t>UGEL YUNGAY</t>
         </is>
       </c>
+      <c r="R266" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -21397,13 +22775,42 @@
         </is>
       </c>
       <c r="J267" t="inlineStr"/>
-      <c r="K267" t="inlineStr"/>
-      <c r="L267" t="inlineStr"/>
-      <c r="M267" t="inlineStr"/>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>MARISCAL LUZURIAGA</t>
+        </is>
+      </c>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>FIDEL OLIVAS ESCUDERO</t>
+        </is>
+      </c>
       <c r="N267" t="inlineStr"/>
-      <c r="O267" t="inlineStr"/>
-      <c r="P267" t="inlineStr"/>
-      <c r="Q267" t="inlineStr"/>
+      <c r="O267" t="inlineStr">
+        <is>
+          <t>021304</t>
+        </is>
+      </c>
+      <c r="P267" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q267" t="inlineStr">
+        <is>
+          <t>UGEL MARISCAL LUZURIAGA</t>
+        </is>
+      </c>
+      <c r="R267" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -21448,13 +22855,42 @@
         </is>
       </c>
       <c r="J268" t="inlineStr"/>
-      <c r="K268" t="inlineStr"/>
-      <c r="L268" t="inlineStr"/>
-      <c r="M268" t="inlineStr"/>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>MARISCAL LUZURIAGA</t>
+        </is>
+      </c>
+      <c r="M268" t="inlineStr">
+        <is>
+          <t>FIDEL OLIVAS ESCUDERO</t>
+        </is>
+      </c>
       <c r="N268" t="inlineStr"/>
-      <c r="O268" t="inlineStr"/>
-      <c r="P268" t="inlineStr"/>
-      <c r="Q268" t="inlineStr"/>
+      <c r="O268" t="inlineStr">
+        <is>
+          <t>021304</t>
+        </is>
+      </c>
+      <c r="P268" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q268" t="inlineStr">
+        <is>
+          <t>UGEL MARISCAL LUZURIAGA</t>
+        </is>
+      </c>
+      <c r="R268" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -21534,6 +22970,11 @@
           <t>UGEL RECUAY</t>
         </is>
       </c>
+      <c r="R269" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -21613,6 +23054,11 @@
           <t>UGEL RECUAY</t>
         </is>
       </c>
+      <c r="R270" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -21692,6 +23138,11 @@
           <t>UGEL RECUAY</t>
         </is>
       </c>
+      <c r="R271" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -21771,6 +23222,11 @@
           <t>UGEL RECUAY</t>
         </is>
       </c>
+      <c r="R272" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -21850,6 +23306,11 @@
           <t>UGEL RECUAY</t>
         </is>
       </c>
+      <c r="R273" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -21929,6 +23390,11 @@
           <t>UGEL SANTA</t>
         </is>
       </c>
+      <c r="R274" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -22008,6 +23474,11 @@
           <t>UGEL YUNGAY</t>
         </is>
       </c>
+      <c r="R275" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -22087,6 +23558,11 @@
           <t>UGEL YUNGAY</t>
         </is>
       </c>
+      <c r="R276" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -22166,6 +23642,11 @@
           <t>UGEL SANTA</t>
         </is>
       </c>
+      <c r="R277" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -22245,6 +23726,11 @@
           <t>UGEL YUNGAY</t>
         </is>
       </c>
+      <c r="R278" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -22324,6 +23810,11 @@
           <t>UGEL YUNGAY</t>
         </is>
       </c>
+      <c r="R279" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -22403,6 +23894,11 @@
           <t>UGEL YUNGAY</t>
         </is>
       </c>
+      <c r="R280" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -22482,6 +23978,11 @@
           <t>UGEL CAYLLOMA</t>
         </is>
       </c>
+      <c r="R281" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -22561,6 +24062,11 @@
           <t>UGEL CAYLLOMA</t>
         </is>
       </c>
+      <c r="R282" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -22640,6 +24146,11 @@
           <t>UGEL CHULUCANAS</t>
         </is>
       </c>
+      <c r="R283" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -22719,6 +24230,11 @@
           <t>UGEL MORROPÓN</t>
         </is>
       </c>
+      <c r="R284" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -22798,6 +24314,11 @@
           <t>UGEL CHULUCANAS</t>
         </is>
       </c>
+      <c r="R285" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -22877,6 +24398,11 @@
           <t>UGEL AYABACA</t>
         </is>
       </c>
+      <c r="R286" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -22956,6 +24482,11 @@
           <t>UGEL AYABACA</t>
         </is>
       </c>
+      <c r="R287" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -23035,6 +24566,11 @@
           <t>UGEL AYABACA</t>
         </is>
       </c>
+      <c r="R288" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -23114,6 +24650,11 @@
           <t>UGEL AYABACA</t>
         </is>
       </c>
+      <c r="R289" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -23193,6 +24734,11 @@
           <t>UGEL AYABACA</t>
         </is>
       </c>
+      <c r="R290" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -23272,6 +24818,11 @@
           <t>UGEL AYABACA</t>
         </is>
       </c>
+      <c r="R291" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -23351,6 +24902,11 @@
           <t>UGEL CHULUCANAS</t>
         </is>
       </c>
+      <c r="R292" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -23430,6 +24986,11 @@
           <t>UGEL CHULUCANAS</t>
         </is>
       </c>
+      <c r="R293" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -23509,6 +25070,11 @@
           <t>UGEL MORROPÓN</t>
         </is>
       </c>
+      <c r="R294" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -23588,6 +25154,11 @@
           <t>UGEL MORROPÓN</t>
         </is>
       </c>
+      <c r="R295" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -23667,6 +25238,11 @@
           <t>UGEL CHULUCANAS</t>
         </is>
       </c>
+      <c r="R296" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -23746,6 +25322,11 @@
           <t>UGEL MORROPÓN</t>
         </is>
       </c>
+      <c r="R297" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -23825,6 +25406,11 @@
           <t>UGEL CHULUCANAS</t>
         </is>
       </c>
+      <c r="R298" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -23904,6 +25490,11 @@
           <t>UGEL AYABACA</t>
         </is>
       </c>
+      <c r="R299" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -23983,6 +25574,11 @@
           <t>UGEL AYABACA</t>
         </is>
       </c>
+      <c r="R300" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -24062,6 +25658,11 @@
           <t>UGEL AYABACA</t>
         </is>
       </c>
+      <c r="R301" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -24141,6 +25742,11 @@
           <t>UGEL AYABACA</t>
         </is>
       </c>
+      <c r="R302" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -24220,6 +25826,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="R303" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -24299,6 +25910,11 @@
           <t>UGEL CHULUCANAS</t>
         </is>
       </c>
+      <c r="R304" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -24378,6 +25994,11 @@
           <t>UGEL CHULUCANAS</t>
         </is>
       </c>
+      <c r="R305" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -24457,6 +26078,11 @@
           <t>UGEL MORROPÓN</t>
         </is>
       </c>
+      <c r="R306" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -24536,6 +26162,11 @@
           <t>UGEL MORROPÓN</t>
         </is>
       </c>
+      <c r="R307" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -24615,6 +26246,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="R308" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -24694,6 +26330,11 @@
           <t>UGEL PALLASCA</t>
         </is>
       </c>
+      <c r="R309" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -24773,6 +26414,11 @@
           <t>UGEL PALLASCA</t>
         </is>
       </c>
+      <c r="R310" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -24852,6 +26498,11 @@
           <t>UGEL MARISCAL LUZURIAGA</t>
         </is>
       </c>
+      <c r="R311" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -24931,6 +26582,11 @@
           <t>UGEL MARISCAL LUZURIAGA</t>
         </is>
       </c>
+      <c r="R312" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -25010,6 +26666,11 @@
           <t>UGEL AYABACA</t>
         </is>
       </c>
+      <c r="R313" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -25089,6 +26750,11 @@
           <t>UGEL AYABACA</t>
         </is>
       </c>
+      <c r="R314" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -25168,6 +26834,11 @@
           <t>UGEL AYABACA</t>
         </is>
       </c>
+      <c r="R315" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -25247,6 +26918,11 @@
           <t>UGEL AYABACA</t>
         </is>
       </c>
+      <c r="R316" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -25326,6 +27002,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="R317" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -25405,6 +27086,11 @@
           <t>UGEL AYABACA</t>
         </is>
       </c>
+      <c r="R318" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -25484,6 +27170,11 @@
           <t>UGEL AYABACA</t>
         </is>
       </c>
+      <c r="R319" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -25563,6 +27254,11 @@
           <t>UGEL VIRÚ</t>
         </is>
       </c>
+      <c r="R320" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
@@ -25642,6 +27338,11 @@
           <t>UGEL VIRÚ</t>
         </is>
       </c>
+      <c r="R321" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -25721,6 +27422,11 @@
           <t>UGEL VIRÚ</t>
         </is>
       </c>
+      <c r="R322" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -25800,6 +27506,11 @@
           <t>UGEL CHEPEN</t>
         </is>
       </c>
+      <c r="R323" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
@@ -25879,6 +27590,11 @@
           <t>UGEL CHEPEN</t>
         </is>
       </c>
+      <c r="R324" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
@@ -25958,6 +27674,11 @@
           <t>UGEL 01 - EL PORVENIR</t>
         </is>
       </c>
+      <c r="R325" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
@@ -26037,6 +27758,11 @@
           <t>UGEL 03 - TRUJILLO NOR OESTE</t>
         </is>
       </c>
+      <c r="R326" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
@@ -26116,6 +27842,11 @@
           <t>UGEL 03 - TRUJILLO NOR OESTE</t>
         </is>
       </c>
+      <c r="R327" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -26195,6 +27926,11 @@
           <t>UGEL FERREÑAFE</t>
         </is>
       </c>
+      <c r="R328" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
@@ -26274,6 +28010,11 @@
           <t>UGEL FERREÑAFE</t>
         </is>
       </c>
+      <c r="R329" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
@@ -26353,6 +28094,11 @@
           <t>UGEL LAMBAYEQUE</t>
         </is>
       </c>
+      <c r="R330" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -26432,6 +28178,11 @@
           <t>UGEL FERREÑAFE</t>
         </is>
       </c>
+      <c r="R331" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
@@ -26511,6 +28262,11 @@
           <t>UGEL FERREÑAFE</t>
         </is>
       </c>
+      <c r="R332" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
@@ -26590,6 +28346,11 @@
           <t>UGEL CHEPEN</t>
         </is>
       </c>
+      <c r="R333" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -26669,6 +28430,11 @@
           <t>UGEL 01 - EL PORVENIR</t>
         </is>
       </c>
+      <c r="R334" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
@@ -26748,6 +28514,11 @@
           <t>UGEL 01 - EL PORVENIR</t>
         </is>
       </c>
+      <c r="R335" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
@@ -26827,6 +28598,11 @@
           <t>UGEL CHEPEN</t>
         </is>
       </c>
+      <c r="R336" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
@@ -26906,6 +28682,11 @@
           <t>UGEL CHICLAYO</t>
         </is>
       </c>
+      <c r="R337" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
@@ -26985,6 +28766,11 @@
           <t>UGEL ASCOPE</t>
         </is>
       </c>
+      <c r="R338" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
@@ -27064,6 +28850,11 @@
           <t>UGEL ASCOPE</t>
         </is>
       </c>
+      <c r="R339" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
@@ -27143,6 +28934,11 @@
           <t>UGEL FERREÑAFE</t>
         </is>
       </c>
+      <c r="R340" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
@@ -27222,6 +29018,11 @@
           <t>UGEL LAMBAYEQUE</t>
         </is>
       </c>
+      <c r="R341" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
@@ -27301,6 +29102,11 @@
           <t>UGEL CASTROVIRREYNA</t>
         </is>
       </c>
+      <c r="R342" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
@@ -27380,6 +29186,11 @@
           <t>UGEL CHURCAMPA</t>
         </is>
       </c>
+      <c r="R343" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
@@ -27459,6 +29270,11 @@
           <t>UGEL HUAYTARÁ</t>
         </is>
       </c>
+      <c r="R344" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
@@ -27538,6 +29354,11 @@
           <t>UGEL HUAYTARÁ</t>
         </is>
       </c>
+      <c r="R345" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
@@ -27617,6 +29438,11 @@
           <t>UGEL CHEPEN</t>
         </is>
       </c>
+      <c r="R346" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
@@ -27696,6 +29522,11 @@
           <t>UGEL 02 - LA ESPERANZA</t>
         </is>
       </c>
+      <c r="R347" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
@@ -27775,6 +29606,11 @@
           <t>UGEL GRAN CHIMÚ</t>
         </is>
       </c>
+      <c r="R348" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
@@ -27854,6 +29690,11 @@
           <t>UGEL ASCOPE</t>
         </is>
       </c>
+      <c r="R349" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
@@ -27933,6 +29774,11 @@
           <t>UGEL GRAN CHIMÚ</t>
         </is>
       </c>
+      <c r="R350" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
@@ -28012,6 +29858,11 @@
           <t>UGEL GRAN CHIMÚ</t>
         </is>
       </c>
+      <c r="R351" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
@@ -28091,6 +29942,11 @@
           <t>UGEL GRAN CHIMÚ</t>
         </is>
       </c>
+      <c r="R352" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
@@ -28170,6 +30026,11 @@
           <t>UGEL GRAN CHIMÚ</t>
         </is>
       </c>
+      <c r="R353" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
@@ -28249,6 +30110,11 @@
           <t>UGEL 02 - LA ESPERANZA</t>
         </is>
       </c>
+      <c r="R354" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
@@ -28328,6 +30194,11 @@
           <t>UGEL 02 - LA ESPERANZA</t>
         </is>
       </c>
+      <c r="R355" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
@@ -28407,6 +30278,11 @@
           <t>UGEL VIRÚ</t>
         </is>
       </c>
+      <c r="R356" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
@@ -28486,6 +30362,11 @@
           <t>UGEL VIRÚ</t>
         </is>
       </c>
+      <c r="R357" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
@@ -28565,6 +30446,11 @@
           <t>UGEL LAMBAYEQUE</t>
         </is>
       </c>
+      <c r="R358" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
@@ -28644,6 +30530,11 @@
           <t>UGEL FERREÑAFE</t>
         </is>
       </c>
+      <c r="R359" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
@@ -28723,6 +30614,11 @@
           <t>UGEL FERREÑAFE</t>
         </is>
       </c>
+      <c r="R360" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
@@ -28802,6 +30698,11 @@
           <t>UGEL FERREÑAFE</t>
         </is>
       </c>
+      <c r="R361" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
@@ -28881,6 +30782,11 @@
           <t>UGEL FERREÑAFE</t>
         </is>
       </c>
+      <c r="R362" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
@@ -28960,6 +30866,11 @@
           <t>UGEL FERREÑAFE</t>
         </is>
       </c>
+      <c r="R363" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
@@ -29039,6 +30950,11 @@
           <t>UGEL LAMBAYEQUE</t>
         </is>
       </c>
+      <c r="R364" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
@@ -29118,6 +31034,11 @@
           <t>UGEL LAMBAYEQUE</t>
         </is>
       </c>
+      <c r="R365" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
@@ -29197,6 +31118,11 @@
           <t>UGEL LAMBAYEQUE</t>
         </is>
       </c>
+      <c r="R366" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
@@ -29276,6 +31202,11 @@
           <t>UGEL LAMBAYEQUE</t>
         </is>
       </c>
+      <c r="R367" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
@@ -29355,6 +31286,11 @@
           <t>UGEL BOLOGNESI</t>
         </is>
       </c>
+      <c r="R368" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="n">
@@ -29434,6 +31370,11 @@
           <t>UGEL HUARMEY</t>
         </is>
       </c>
+      <c r="R369" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
@@ -29513,6 +31454,11 @@
           <t>UGEL HUARMEY</t>
         </is>
       </c>
+      <c r="R370" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
@@ -29592,6 +31538,11 @@
           <t>UGEL HUARMEY</t>
         </is>
       </c>
+      <c r="R371" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
@@ -29671,6 +31622,11 @@
           <t>UGEL AIJA</t>
         </is>
       </c>
+      <c r="R372" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
@@ -29750,6 +31706,11 @@
           <t>UGEL AIJA</t>
         </is>
       </c>
+      <c r="R373" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
@@ -29829,6 +31790,11 @@
           <t>UGEL HUARMEY</t>
         </is>
       </c>
+      <c r="R374" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
@@ -29908,6 +31874,11 @@
           <t>UGEL CORONGO</t>
         </is>
       </c>
+      <c r="R375" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
@@ -29987,6 +31958,11 @@
           <t>UGEL BOLOGNESI</t>
         </is>
       </c>
+      <c r="R376" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
@@ -30066,6 +32042,11 @@
           <t>UGEL BOLOGNESI</t>
         </is>
       </c>
+      <c r="R377" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
@@ -30145,6 +32126,11 @@
           <t>UGEL BOLOGNESI</t>
         </is>
       </c>
+      <c r="R378" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
@@ -30224,6 +32210,11 @@
           <t>UGEL CARHUÁZ</t>
         </is>
       </c>
+      <c r="R379" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="n">
@@ -30303,6 +32294,11 @@
           <t>UGEL CASMA</t>
         </is>
       </c>
+      <c r="R380" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
@@ -30382,6 +32378,11 @@
           <t>UGEL HUARAZ</t>
         </is>
       </c>
+      <c r="R381" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
@@ -30461,6 +32462,11 @@
           <t>UGEL CASMA</t>
         </is>
       </c>
+      <c r="R382" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
@@ -30540,6 +32546,11 @@
           <t>UGEL CARLOS FERMIN FITZCARRALD</t>
         </is>
       </c>
+      <c r="R383" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="n">
@@ -30619,6 +32630,11 @@
           <t>UGEL CARLOS FERMIN FITZCARRALD</t>
         </is>
       </c>
+      <c r="R384" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="n">
@@ -30698,6 +32714,11 @@
           <t>UGEL HUARAZ</t>
         </is>
       </c>
+      <c r="R385" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="n">
@@ -30777,6 +32798,11 @@
           <t>UGEL AIJA</t>
         </is>
       </c>
+      <c r="R386" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="n">
@@ -30856,6 +32882,11 @@
           <t>UGEL AIJA</t>
         </is>
       </c>
+      <c r="R387" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="n">
@@ -30935,6 +32966,11 @@
           <t>UGEL AIJA</t>
         </is>
       </c>
+      <c r="R388" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
@@ -31014,6 +33050,11 @@
           <t>UGEL AIJA</t>
         </is>
       </c>
+      <c r="R389" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="n">
@@ -31093,6 +33134,11 @@
           <t>UGEL AIJA</t>
         </is>
       </c>
+      <c r="R390" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="n">
@@ -31172,6 +33218,11 @@
           <t>UGEL AIJA</t>
         </is>
       </c>
+      <c r="R391" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
@@ -31251,6 +33302,11 @@
           <t>UGEL AIJA</t>
         </is>
       </c>
+      <c r="R392" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="n">
@@ -31330,6 +33386,11 @@
           <t>UGEL ANTONIO RAYMONDI</t>
         </is>
       </c>
+      <c r="R393" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="n">
@@ -31409,6 +33470,11 @@
           <t>UGEL CARHUÁZ</t>
         </is>
       </c>
+      <c r="R394" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="n">
@@ -31488,6 +33554,11 @@
           <t>UGEL CARHUÁZ</t>
         </is>
       </c>
+      <c r="R395" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="n">
@@ -31567,6 +33638,11 @@
           <t>UGEL CARHUÁZ</t>
         </is>
       </c>
+      <c r="R396" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="n">
@@ -31646,6 +33722,11 @@
           <t>UGEL CAJABAMBA</t>
         </is>
       </c>
+      <c r="R397" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="n">
@@ -31725,6 +33806,11 @@
           <t>UGEL CAJABAMBA</t>
         </is>
       </c>
+      <c r="R398" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="n">
@@ -31804,6 +33890,11 @@
           <t>UGEL CAJABAMBA</t>
         </is>
       </c>
+      <c r="R399" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="n">
@@ -31883,6 +33974,11 @@
           <t>UGEL TAMBOGRANDE</t>
         </is>
       </c>
+      <c r="R400" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="n">
@@ -31962,6 +34058,11 @@
           <t>UGEL TAMBOGRANDE</t>
         </is>
       </c>
+      <c r="R401" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="n">
@@ -32041,6 +34142,11 @@
           <t>UGEL TALARA</t>
         </is>
       </c>
+      <c r="R402" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="n">
@@ -32120,6 +34226,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="R403" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="n">
@@ -32199,6 +34310,11 @@
           <t>UGEL SULLANA</t>
         </is>
       </c>
+      <c r="R404" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="n">
@@ -32278,6 +34394,11 @@
           <t>UGEL SULLANA</t>
         </is>
       </c>
+      <c r="R405" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="n">
@@ -32355,6 +34476,11 @@
       <c r="Q406" t="inlineStr">
         <is>
           <t>UGEL SULLANA</t>
+        </is>
+      </c>
+      <c r="R406" t="inlineStr">
+        <is>
+          <t>UGRD</t>
         </is>
       </c>
     </row>
@@ -32408,6 +34534,11 @@
       <c r="O407" t="inlineStr"/>
       <c r="P407" t="inlineStr"/>
       <c r="Q407" t="inlineStr"/>
+      <c r="R407" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="n">
@@ -32487,6 +34618,11 @@
           <t>UGEL 11 CAJATAMBO</t>
         </is>
       </c>
+      <c r="R408" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="n">
@@ -32566,6 +34702,11 @@
           <t>UGEL 09 HUAURA</t>
         </is>
       </c>
+      <c r="R409" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="n">
@@ -32645,6 +34786,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="R410" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="n">
@@ -32724,6 +34870,11 @@
           <t>UGEL TAMBOGRANDE</t>
         </is>
       </c>
+      <c r="R411" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="n">
@@ -32803,6 +34954,11 @@
           <t>UGEL TAMBOGRANDE</t>
         </is>
       </c>
+      <c r="R412" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="n">
@@ -32882,6 +35038,11 @@
           <t>UGEL TAMBOGRANDE</t>
         </is>
       </c>
+      <c r="R413" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="n">
@@ -32961,6 +35122,11 @@
           <t>UGEL TAMBOGRANDE</t>
         </is>
       </c>
+      <c r="R414" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="n">
@@ -33040,6 +35206,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="R415" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="n">
@@ -33119,6 +35290,11 @@
           <t>UGEL CONTRALMIRANTE VILLAR</t>
         </is>
       </c>
+      <c r="R416" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="n">
@@ -33198,6 +35374,11 @@
           <t>UGEL CAJAMARCA</t>
         </is>
       </c>
+      <c r="R417" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="n">
@@ -33277,6 +35458,11 @@
           <t>UGEL 15 HUAROCHIRÍ</t>
         </is>
       </c>
+      <c r="R418" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="n">
@@ -33356,6 +35542,11 @@
           <t>UGEL 16 BARRANCA</t>
         </is>
       </c>
+      <c r="R419" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="n">
@@ -33435,6 +35626,11 @@
           <t>UGEL 15 HUAROCHIRÍ</t>
         </is>
       </c>
+      <c r="R420" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="n">
@@ -33514,6 +35710,11 @@
           <t>UGEL 10 HUARAL</t>
         </is>
       </c>
+      <c r="R421" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="n">
@@ -33593,6 +35794,11 @@
           <t>UGEL SECHURA</t>
         </is>
       </c>
+      <c r="R422" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="n">
@@ -33672,6 +35878,11 @@
           <t>UGEL SECHURA</t>
         </is>
       </c>
+      <c r="R423" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="n">
@@ -33751,6 +35962,11 @@
           <t>UGEL SULLANA</t>
         </is>
       </c>
+      <c r="R424" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="n">
@@ -33830,6 +36046,11 @@
           <t>UGEL TALARA</t>
         </is>
       </c>
+      <c r="R425" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="n">
@@ -33909,6 +36130,11 @@
           <t>UGEL TAMBOGRANDE</t>
         </is>
       </c>
+      <c r="R426" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="n">
@@ -33988,6 +36214,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="R427" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="n">
@@ -34067,6 +36298,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="R428" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="n">
@@ -34146,6 +36382,11 @@
           <t>UGEL LA UNIÓN</t>
         </is>
       </c>
+      <c r="R429" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="n">
@@ -34225,6 +36466,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="R430" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="n">
@@ -34304,6 +36550,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="R431" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="n">
@@ -34383,6 +36634,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="R432" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="n">
@@ -34462,6 +36718,11 @@
           <t>UGEL TAMBOGRANDE</t>
         </is>
       </c>
+      <c r="R433" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="n">
@@ -34541,6 +36802,11 @@
           <t>UGEL TAMBOGRANDE</t>
         </is>
       </c>
+      <c r="R434" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="n">
@@ -34620,6 +36886,11 @@
           <t>UGEL TAMBOGRANDE</t>
         </is>
       </c>
+      <c r="R435" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="n">
@@ -34699,6 +36970,11 @@
           <t>UGEL TAMBOGRANDE</t>
         </is>
       </c>
+      <c r="R436" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="n">
@@ -34778,6 +37054,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="R437" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="n">
@@ -34857,6 +37138,11 @@
           <t>UGEL LA UNIÓN</t>
         </is>
       </c>
+      <c r="R438" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="n">
@@ -34936,6 +37222,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="R439" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="n">
@@ -35015,6 +37306,11 @@
           <t>UGEL TAMBOGRANDE</t>
         </is>
       </c>
+      <c r="R440" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="n">
@@ -35094,6 +37390,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="R441" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="n">
@@ -35173,6 +37474,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="R442" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="n">
@@ -35252,6 +37558,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="R443" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="n">
@@ -35331,6 +37642,11 @@
           <t>UGEL CONTRALMIRANTE VILLAR</t>
         </is>
       </c>
+      <c r="R444" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="n">
@@ -35410,6 +37726,11 @@
           <t>UGEL CONTRALMIRANTE VILLAR</t>
         </is>
       </c>
+      <c r="R445" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="n">
@@ -35489,6 +37810,11 @@
           <t>UGEL CONTRALMIRANTE VILLAR</t>
         </is>
       </c>
+      <c r="R446" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="n">
@@ -35568,6 +37894,11 @@
           <t>UGEL TUMBES</t>
         </is>
       </c>
+      <c r="R447" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="n">
@@ -35647,6 +37978,11 @@
           <t>UGEL HUANCABAMBA</t>
         </is>
       </c>
+      <c r="R448" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="n">
@@ -35726,6 +38062,11 @@
           <t>UGEL MARISCAL LUZURIAGA</t>
         </is>
       </c>
+      <c r="R449" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="n">
@@ -35805,6 +38146,11 @@
           <t>UGEL MORROPÓN</t>
         </is>
       </c>
+      <c r="R450" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="n">
@@ -35884,6 +38230,11 @@
           <t>UGEL MORROPÓN</t>
         </is>
       </c>
+      <c r="R451" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="n">
@@ -35963,6 +38314,11 @@
           <t>UGEL SANTA</t>
         </is>
       </c>
+      <c r="R452" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="n">
@@ -36042,6 +38398,11 @@
           <t>UGEL YUNGAY</t>
         </is>
       </c>
+      <c r="R453" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="n">
@@ -36121,6 +38482,11 @@
           <t>UGEL YUNGAY</t>
         </is>
       </c>
+      <c r="R454" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="n">
@@ -36200,6 +38566,11 @@
           <t>UGEL MORROPÓN</t>
         </is>
       </c>
+      <c r="R455" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="n">
@@ -36279,6 +38650,11 @@
           <t>UGEL MORROPÓN</t>
         </is>
       </c>
+      <c r="R456" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="n">
@@ -36358,6 +38734,11 @@
           <t>UGEL CHULUCANAS</t>
         </is>
       </c>
+      <c r="R457" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="n">
@@ -36437,6 +38818,11 @@
           <t>UGEL CHULUCANAS</t>
         </is>
       </c>
+      <c r="R458" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="n">
@@ -36516,6 +38902,11 @@
           <t>UGEL CHULUCANAS</t>
         </is>
       </c>
+      <c r="R459" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="n">
@@ -36595,6 +38986,11 @@
           <t>UGEL CHULUCANAS</t>
         </is>
       </c>
+      <c r="R460" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="n">
@@ -36674,6 +39070,11 @@
           <t>UGEL MORROPÓN</t>
         </is>
       </c>
+      <c r="R461" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="n">
@@ -36753,6 +39154,11 @@
           <t>UGEL RECUAY</t>
         </is>
       </c>
+      <c r="R462" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="n">
@@ -36832,6 +39238,11 @@
           <t>UGEL SANTA</t>
         </is>
       </c>
+      <c r="R463" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="n">
@@ -36911,6 +39322,11 @@
           <t>UGEL SANTA</t>
         </is>
       </c>
+      <c r="R464" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="n">
@@ -36990,6 +39406,11 @@
           <t>UGEL YUNGAY</t>
         </is>
       </c>
+      <c r="R465" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="n">
@@ -37069,6 +39490,11 @@
           <t>UGEL MORROPÓN</t>
         </is>
       </c>
+      <c r="R466" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="n">
@@ -37148,6 +39574,11 @@
           <t>UGEL OCROS</t>
         </is>
       </c>
+      <c r="R467" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="n">
@@ -37227,6 +39658,11 @@
           <t>UGEL OCROS</t>
         </is>
       </c>
+      <c r="R468" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="n">
@@ -37306,6 +39742,11 @@
           <t>UGEL CHULUCANAS</t>
         </is>
       </c>
+      <c r="R469" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="n">
@@ -37385,6 +39826,11 @@
           <t>UGEL HUARMACA</t>
         </is>
       </c>
+      <c r="R470" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="n">
@@ -37464,6 +39910,11 @@
           <t>UGEL MORROPÓN</t>
         </is>
       </c>
+      <c r="R471" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="n">
@@ -37543,6 +39994,11 @@
           <t>UGEL ICA</t>
         </is>
       </c>
+      <c r="R472" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="n">
@@ -37622,6 +40078,11 @@
           <t>UGEL PALPA</t>
         </is>
       </c>
+      <c r="R473" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="n">
@@ -37701,6 +40162,11 @@
           <t>UGEL HUAYLAS</t>
         </is>
       </c>
+      <c r="R474" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="n">
@@ -37780,6 +40246,11 @@
           <t>UGEL HUAYLAS</t>
         </is>
       </c>
+      <c r="R475" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="n">
@@ -37859,6 +40330,11 @@
           <t>UGEL OCROS</t>
         </is>
       </c>
+      <c r="R476" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="n">
@@ -37938,6 +40414,11 @@
           <t>UGEL SIHUAS</t>
         </is>
       </c>
+      <c r="R477" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="n">
@@ -38017,6 +40498,11 @@
           <t>UGEL SANTA</t>
         </is>
       </c>
+      <c r="R478" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="n">
@@ -38096,6 +40582,11 @@
           <t>UGEL YUNGAY</t>
         </is>
       </c>
+      <c r="R479" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="n">
@@ -38175,6 +40666,11 @@
           <t>UGEL YUNGAY</t>
         </is>
       </c>
+      <c r="R480" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="n">
@@ -38254,6 +40750,11 @@
           <t>UGEL YUNGAY</t>
         </is>
       </c>
+      <c r="R481" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="n">
@@ -38333,6 +40834,11 @@
           <t>UGEL SANTA</t>
         </is>
       </c>
+      <c r="R482" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="n">
@@ -38412,6 +40918,11 @@
           <t>UGEL SANTA</t>
         </is>
       </c>
+      <c r="R483" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="n">
@@ -38456,13 +40967,42 @@
         </is>
       </c>
       <c r="J484" t="inlineStr"/>
-      <c r="K484" t="inlineStr"/>
-      <c r="L484" t="inlineStr"/>
-      <c r="M484" t="inlineStr"/>
+      <c r="K484" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="L484" t="inlineStr">
+        <is>
+          <t>MARISCAL LUZURIAGA</t>
+        </is>
+      </c>
+      <c r="M484" t="inlineStr">
+        <is>
+          <t>FIDEL OLIVAS ESCUDERO</t>
+        </is>
+      </c>
       <c r="N484" t="inlineStr"/>
-      <c r="O484" t="inlineStr"/>
-      <c r="P484" t="inlineStr"/>
-      <c r="Q484" t="inlineStr"/>
+      <c r="O484" t="inlineStr">
+        <is>
+          <t>021304</t>
+        </is>
+      </c>
+      <c r="P484" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Q484" t="inlineStr">
+        <is>
+          <t>UGEL MARISCAL LUZURIAGA</t>
+        </is>
+      </c>
+      <c r="R484" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="n">
@@ -38542,6 +41082,11 @@
           <t>UGEL RECUAY</t>
         </is>
       </c>
+      <c r="R485" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="n">
@@ -38621,6 +41166,11 @@
           <t>UGEL SANTA</t>
         </is>
       </c>
+      <c r="R486" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="n">
@@ -38700,6 +41250,11 @@
           <t>UGEL YUNGAY</t>
         </is>
       </c>
+      <c r="R487" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="n">
@@ -38779,6 +41334,11 @@
           <t>UGEL YUNGAY</t>
         </is>
       </c>
+      <c r="R488" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="n">
@@ -38858,6 +41418,11 @@
           <t>UGEL YUNGAY</t>
         </is>
       </c>
+      <c r="R489" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="n">
@@ -38937,6 +41502,11 @@
           <t>UGEL RECUAY</t>
         </is>
       </c>
+      <c r="R490" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="n">
@@ -39016,6 +41586,11 @@
           <t>UGEL SANTA</t>
         </is>
       </c>
+      <c r="R491" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="n">
@@ -39095,6 +41670,11 @@
           <t>UGEL YUNGAY</t>
         </is>
       </c>
+      <c r="R492" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="n">
@@ -39174,6 +41754,11 @@
           <t>UGEL YUNGAY</t>
         </is>
       </c>
+      <c r="R493" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="n">
@@ -39253,6 +41838,11 @@
           <t>UGEL MORROPÓN</t>
         </is>
       </c>
+      <c r="R494" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="n">
@@ -39332,6 +41922,11 @@
           <t>UGEL CHULUCANAS</t>
         </is>
       </c>
+      <c r="R495" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="n">
@@ -39411,6 +42006,11 @@
           <t>UGEL CHULUCANAS</t>
         </is>
       </c>
+      <c r="R496" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="n">
@@ -39490,6 +42090,11 @@
           <t>UGEL AYABACA</t>
         </is>
       </c>
+      <c r="R497" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="n">
@@ -39569,6 +42174,11 @@
           <t>UGEL CHULUCANAS</t>
         </is>
       </c>
+      <c r="R498" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="n">
@@ -39648,6 +42258,11 @@
           <t>UGEL MORROPÓN</t>
         </is>
       </c>
+      <c r="R499" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="n">
@@ -39727,6 +42342,11 @@
           <t>UGEL CHULUCANAS</t>
         </is>
       </c>
+      <c r="R500" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="n">
@@ -39806,6 +42426,11 @@
           <t>UGEL AYABACA</t>
         </is>
       </c>
+      <c r="R501" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="n">
@@ -39885,6 +42510,11 @@
           <t>UGEL CHULUCANAS</t>
         </is>
       </c>
+      <c r="R502" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="n">
@@ -39964,6 +42594,11 @@
           <t>UGEL PALLASCA</t>
         </is>
       </c>
+      <c r="R503" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="n">
@@ -40043,6 +42678,11 @@
           <t>UGEL MARISCAL LUZURIAGA</t>
         </is>
       </c>
+      <c r="R504" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="n">
@@ -40122,6 +42762,11 @@
           <t>UGEL AYABACA</t>
         </is>
       </c>
+      <c r="R505" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="n">
@@ -40201,6 +42846,11 @@
           <t>UGEL SANTA</t>
         </is>
       </c>
+      <c r="R506" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="n">
@@ -40280,6 +42930,11 @@
           <t>UGEL ASCOPE</t>
         </is>
       </c>
+      <c r="R507" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="n">
@@ -40359,6 +43014,11 @@
           <t>UGEL HUARAZ</t>
         </is>
       </c>
+      <c r="R508" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="n">
@@ -40438,6 +43098,11 @@
           <t>UGEL AIJA</t>
         </is>
       </c>
+      <c r="R509" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="n">
@@ -40517,6 +43182,11 @@
           <t>UGEL CASMA</t>
         </is>
       </c>
+      <c r="R510" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="n">
@@ -40596,6 +43266,11 @@
           <t>UGEL HUARAZ</t>
         </is>
       </c>
+      <c r="R511" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="n">
@@ -40675,6 +43350,11 @@
           <t>UGEL CONTRALMIRANTE VILLAR</t>
         </is>
       </c>
+      <c r="R512" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="n">
@@ -40754,6 +43434,11 @@
           <t>UGEL MORROPÓN</t>
         </is>
       </c>
+      <c r="R513" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="n">
@@ -40833,6 +43518,11 @@
           <t>UGEL MORROPÓN</t>
         </is>
       </c>
+      <c r="R514" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="n">
@@ -40912,6 +43602,11 @@
           <t>UGEL MORROPÓN</t>
         </is>
       </c>
+      <c r="R515" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="n">
@@ -40995,6 +43690,11 @@
           <t>UGEL GRAN CHIMÚ</t>
         </is>
       </c>
+      <c r="R516" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="n">
@@ -41078,6 +43778,11 @@
           <t>UGEL RIO TAMBO</t>
         </is>
       </c>
+      <c r="R517" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="n">
@@ -41159,6 +43864,11 @@
       <c r="Q518" t="inlineStr">
         <is>
           <t>UGEL CHULUCANAS</t>
+        </is>
+      </c>
+      <c r="R518" t="inlineStr">
+        <is>
+          <t>UGRD</t>
         </is>
       </c>
     </row>

--- a/output/bases_limpias/Grupo_03_MODULOS/df_ugrd_me.xlsx
+++ b/output/bases_limpias/Grupo_03_MODULOS/df_ugrd_me.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R518"/>
+  <dimension ref="A1:T518"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -504,6 +504,16 @@
       </c>
       <c r="R1" t="inlineStr">
         <is>
+          <t>nombre_ie</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
           <t>fuente</t>
         </is>
       </c>
@@ -588,6 +598,16 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
+          <t>2315</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -672,6 +692,16 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
+          <t>80093 JOSE OLAYA/80093 JOSE OLAYA</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -756,6 +786,16 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
+          <t>82106</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -840,6 +880,16 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
+          <t>82208 MARQUEZ DE TORRE TAGLE/82208 MARQUEZ DE TORRE TAGLE/82208 MARQUEZ DE TORRE TAGLE</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -924,6 +974,16 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
+          <t>2343</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -1008,6 +1068,16 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
+          <t>388</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -1092,6 +1162,16 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
+          <t>389</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -1176,6 +1256,16 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
+          <t>2192</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -1260,6 +1350,16 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
+          <t>80942 LEONCIO PRADO GUTIERREZ</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -1344,6 +1444,16 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
+          <t>81573</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -1428,6 +1538,16 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
+          <t>501</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -1512,6 +1632,16 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
+          <t>10241</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -1596,6 +1726,16 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
+          <t>11145</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -1680,6 +1820,16 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
+          <t>11145</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -1764,6 +1914,16 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
+          <t>997</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -1848,6 +2008,16 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
+          <t>997</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -1932,6 +2102,16 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
+          <t>22583</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -2016,6 +2196,16 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
+          <t>22583</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -2100,6 +2290,16 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
+          <t>36808</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -2184,6 +2384,16 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
+          <t>36808</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -2268,6 +2478,16 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
+          <t>1109</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -2352,6 +2572,16 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
+          <t>1109</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -2436,6 +2666,16 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
+          <t>36435</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -2520,6 +2760,16 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
+          <t>36435</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -2604,6 +2854,16 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
+          <t>36436</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -2688,6 +2948,16 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
+          <t>36436</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -2772,6 +3042,16 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
+          <t>895</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -2856,6 +3136,16 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
+          <t>895</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -2940,6 +3230,16 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
+          <t>82173</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -3024,6 +3324,16 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
+          <t>82173</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -3108,6 +3418,16 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
+          <t>80843 VICTOR R. HAYA DE LA TORRE</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -3192,6 +3512,16 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
+          <t>82610</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -3276,6 +3606,16 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
+          <t>82610</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -3360,6 +3700,16 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
+          <t>81507 VIRGEN DE LOURDES</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -3444,6 +3794,16 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
+          <t>80079 MIGUEL GRAU</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -3528,6 +3888,16 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
+          <t>81753</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -3608,6 +3978,16 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
+          <t>81899</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -3692,6 +4072,16 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
+          <t>80415</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -3776,6 +4166,16 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
+          <t>81655 ENRIQUE CORCUERA RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -3860,6 +4260,16 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
+          <t>81754</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -3944,6 +4354,16 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
+          <t>82045 ALBERTO FUJIMORI</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -4028,6 +4448,16 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
+          <t>81903</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -4112,6 +4542,16 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
+          <t>2305</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -4196,6 +4636,16 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
+          <t>82613</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -4280,6 +4730,16 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
+          <t>81718</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -4364,6 +4824,16 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
+          <t>80083</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -4448,6 +4918,16 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
+          <t>81533 SAN ANTONIO DE PADUA</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -4532,6 +5012,16 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
+          <t>82000</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -4616,6 +5106,16 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
+          <t>82000</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -4700,6 +5200,16 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
+          <t>81632</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -4784,6 +5294,16 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
+          <t>81632</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -4864,6 +5384,16 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
+          <t>82089</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -4948,6 +5478,16 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
+          <t>122 PEDRO DIAZ VERGARA</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -5032,6 +5572,16 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -5116,6 +5666,16 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
+          <t>2310</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -5200,6 +5760,16 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
+          <t>2175</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -5284,6 +5854,16 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
+          <t>2287</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -5368,6 +5948,16 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
+          <t>2289</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -5452,6 +6042,16 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
+          <t>10779 GENERAL OSCAR RAIMUNDO BENAVIDES LARREA</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -5536,6 +6136,16 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
+          <t>10095</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -5620,6 +6230,16 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
+          <t>11590 JUAN PABLO II</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -5704,6 +6324,16 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
+          <t>377</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -5788,6 +6418,16 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
+          <t>456</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -5872,6 +6512,16 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
+          <t>456</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -5956,6 +6606,16 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
+          <t>384</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -6040,6 +6700,16 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
+          <t>510 BLANCA VALERA GONZALES</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -6124,6 +6794,16 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
+          <t>11238</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -6208,6 +6888,16 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
+          <t>11243</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -6292,6 +6982,16 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
+          <t>265 INMACULADA NIÑA MARIA</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -6376,6 +7076,16 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -6460,6 +7170,16 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
+          <t>86917</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -6544,6 +7264,16 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
+          <t>86917</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -6628,6 +7358,16 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
+          <t>1652</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -6712,6 +7452,16 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
+          <t>1704</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -6796,6 +7546,16 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
+          <t>88122</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -6880,6 +7640,16 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
+          <t>88289</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -6964,6 +7734,16 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
+          <t>026</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -7048,6 +7828,16 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
+          <t>88113/88113</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -7132,6 +7922,16 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
+          <t>88339</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -7216,6 +8016,16 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
+          <t>315</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -7300,6 +8110,16 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
+          <t>86237 JOSE ANDRES RAZURI/86237 JOSE ANDRES RAZURI</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -7384,6 +8204,16 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
+          <t>86237 JOSE ANDRES RAZURI/86237 JOSE ANDRES RAZURI</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -7468,6 +8298,16 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
+          <t>86247/86247</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -7552,6 +8392,16 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
+          <t>86307 TEOFILO CASTILLO</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -7636,6 +8486,16 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
+          <t>86307 TEOFILO CASTILLO</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -7720,6 +8580,16 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
+          <t>86389</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -7804,6 +8674,16 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
+          <t>86389</t>
+        </is>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -7888,6 +8768,16 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
+          <t>JAVIER HERAUD PEREZ</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -7972,6 +8862,16 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
+          <t>JAVIER HERAUD PEREZ</t>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -8056,6 +8956,16 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
+          <t>88249 RAMON CASTILLA</t>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -8140,6 +9050,16 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
+          <t>86053</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -8224,6 +9144,16 @@
       </c>
       <c r="R93" t="inlineStr">
         <is>
+          <t>86053</t>
+        </is>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -8308,6 +9238,16 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
+          <t>88358 TERESA GONZALES DE FANNING</t>
+        </is>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -8392,6 +9332,16 @@
       </c>
       <c r="R95" t="inlineStr">
         <is>
+          <t>86832</t>
+        </is>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -8476,6 +9426,16 @@
       </c>
       <c r="R96" t="inlineStr">
         <is>
+          <t>86832</t>
+        </is>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -8560,6 +9520,16 @@
       </c>
       <c r="R97" t="inlineStr">
         <is>
+          <t>88103</t>
+        </is>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -8644,6 +9614,16 @@
       </c>
       <c r="R98" t="inlineStr">
         <is>
+          <t>HUAYUP</t>
+        </is>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -8728,6 +9708,16 @@
       </c>
       <c r="R99" t="inlineStr">
         <is>
+          <t>88328</t>
+        </is>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -8812,6 +9802,16 @@
       </c>
       <c r="R100" t="inlineStr">
         <is>
+          <t>88328</t>
+        </is>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -8896,6 +9896,16 @@
       </c>
       <c r="R101" t="inlineStr">
         <is>
+          <t>88379 HORACIO ZEBALLOS GAMEZ</t>
+        </is>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -8980,6 +9990,16 @@
       </c>
       <c r="R102" t="inlineStr">
         <is>
+          <t>620</t>
+        </is>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -9064,6 +10084,16 @@
       </c>
       <c r="R103" t="inlineStr">
         <is>
+          <t>88297</t>
+        </is>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -9148,6 +10178,16 @@
       </c>
       <c r="R104" t="inlineStr">
         <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -9232,6 +10272,16 @@
       </c>
       <c r="R105" t="inlineStr">
         <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -9316,6 +10366,16 @@
       </c>
       <c r="R106" t="inlineStr">
         <is>
+          <t>86451</t>
+        </is>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -9400,6 +10460,16 @@
       </c>
       <c r="R107" t="inlineStr">
         <is>
+          <t>86451</t>
+        </is>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -9484,6 +10554,16 @@
       </c>
       <c r="R108" t="inlineStr">
         <is>
+          <t>86105</t>
+        </is>
+      </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -9568,6 +10648,16 @@
       </c>
       <c r="R109" t="inlineStr">
         <is>
+          <t>86105</t>
+        </is>
+      </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -9652,6 +10742,16 @@
       </c>
       <c r="R110" t="inlineStr">
         <is>
+          <t>321</t>
+        </is>
+      </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -9736,6 +10836,16 @@
       </c>
       <c r="R111" t="inlineStr">
         <is>
+          <t>86808 AUGUSTO B. LEGUIA</t>
+        </is>
+      </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -9820,6 +10930,16 @@
       </c>
       <c r="R112" t="inlineStr">
         <is>
+          <t>86817</t>
+        </is>
+      </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -9904,6 +11024,16 @@
       </c>
       <c r="R113" t="inlineStr">
         <is>
+          <t>88123</t>
+        </is>
+      </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -9988,6 +11118,16 @@
       </c>
       <c r="R114" t="inlineStr">
         <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -10072,6 +11212,16 @@
       </c>
       <c r="R115" t="inlineStr">
         <is>
+          <t>431</t>
+        </is>
+      </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -10156,6 +11306,16 @@
       </c>
       <c r="R116" t="inlineStr">
         <is>
+          <t>431</t>
+        </is>
+      </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -10240,6 +11400,16 @@
       </c>
       <c r="R117" t="inlineStr">
         <is>
+          <t>442</t>
+        </is>
+      </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -10324,6 +11494,16 @@
       </c>
       <c r="R118" t="inlineStr">
         <is>
+          <t>442</t>
+        </is>
+      </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -10408,6 +11588,16 @@
       </c>
       <c r="R119" t="inlineStr">
         <is>
+          <t>2605</t>
+        </is>
+      </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -10492,6 +11682,16 @@
       </c>
       <c r="R120" t="inlineStr">
         <is>
+          <t>2605</t>
+        </is>
+      </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -10576,6 +11776,16 @@
       </c>
       <c r="R121" t="inlineStr">
         <is>
+          <t>88112 RICARDO PALMA</t>
+        </is>
+      </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -10660,6 +11870,16 @@
       </c>
       <c r="R122" t="inlineStr">
         <is>
+          <t>86863</t>
+        </is>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -10744,6 +11964,16 @@
       </c>
       <c r="R123" t="inlineStr">
         <is>
+          <t>86863</t>
+        </is>
+      </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -10828,6 +12058,16 @@
       </c>
       <c r="R124" t="inlineStr">
         <is>
+          <t>88121</t>
+        </is>
+      </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -10912,6 +12152,16 @@
       </c>
       <c r="R125" t="inlineStr">
         <is>
+          <t>1659</t>
+        </is>
+      </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -10996,6 +12246,16 @@
       </c>
       <c r="R126" t="inlineStr">
         <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -11080,6 +12340,16 @@
       </c>
       <c r="R127" t="inlineStr">
         <is>
+          <t>422</t>
+        </is>
+      </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -11164,6 +12434,16 @@
       </c>
       <c r="R128" t="inlineStr">
         <is>
+          <t>422</t>
+        </is>
+      </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -11248,6 +12528,16 @@
       </c>
       <c r="R129" t="inlineStr">
         <is>
+          <t>421</t>
+        </is>
+      </c>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -11332,6 +12622,16 @@
       </c>
       <c r="R130" t="inlineStr">
         <is>
+          <t>421</t>
+        </is>
+      </c>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -11416,6 +12716,16 @@
       </c>
       <c r="R131" t="inlineStr">
         <is>
+          <t>86933</t>
+        </is>
+      </c>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -11500,6 +12810,16 @@
       </c>
       <c r="R132" t="inlineStr">
         <is>
+          <t>86933</t>
+        </is>
+      </c>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -11584,6 +12904,16 @@
       </c>
       <c r="R133" t="inlineStr">
         <is>
+          <t>86311/86311</t>
+        </is>
+      </c>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -11668,6 +12998,16 @@
       </c>
       <c r="R134" t="inlineStr">
         <is>
+          <t>86311/86311</t>
+        </is>
+      </c>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -11752,6 +13092,16 @@
       </c>
       <c r="R135" t="inlineStr">
         <is>
+          <t>89018</t>
+        </is>
+      </c>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -11836,6 +13186,16 @@
       </c>
       <c r="R136" t="inlineStr">
         <is>
+          <t>86172</t>
+        </is>
+      </c>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -11920,6 +13280,16 @@
       </c>
       <c r="R137" t="inlineStr">
         <is>
+          <t>86172</t>
+        </is>
+      </c>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -12004,6 +13374,16 @@
       </c>
       <c r="R138" t="inlineStr">
         <is>
+          <t>1122</t>
+        </is>
+      </c>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -12088,6 +13468,16 @@
       </c>
       <c r="R139" t="inlineStr">
         <is>
+          <t>1122</t>
+        </is>
+      </c>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -12172,6 +13562,16 @@
       </c>
       <c r="R140" t="inlineStr">
         <is>
+          <t>20487 SANTA ELENA/20487 SANTA ELENA</t>
+        </is>
+      </c>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -12256,6 +13656,16 @@
       </c>
       <c r="R141" t="inlineStr">
         <is>
+          <t>1554</t>
+        </is>
+      </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -12340,6 +13750,16 @@
       </c>
       <c r="R142" t="inlineStr">
         <is>
+          <t>1148</t>
+        </is>
+      </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -12424,6 +13844,16 @@
       </c>
       <c r="R143" t="inlineStr">
         <is>
+          <t>1420</t>
+        </is>
+      </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -12507,6 +13937,16 @@
         </is>
       </c>
       <c r="R144" t="inlineStr">
+        <is>
+          <t>1596</t>
+        </is>
+      </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T144" t="inlineStr">
         <is>
           <t>UGRD</t>
         </is>
@@ -12562,7 +14002,9 @@
       <c r="O145" t="inlineStr"/>
       <c r="P145" t="inlineStr"/>
       <c r="Q145" t="inlineStr"/>
-      <c r="R145" t="inlineStr">
+      <c r="R145" t="inlineStr"/>
+      <c r="S145" t="inlineStr"/>
+      <c r="T145" t="inlineStr">
         <is>
           <t>UGRD</t>
         </is>
@@ -12648,6 +14090,16 @@
       </c>
       <c r="R146" t="inlineStr">
         <is>
+          <t>486</t>
+        </is>
+      </c>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -12732,6 +14184,16 @@
       </c>
       <c r="R147" t="inlineStr">
         <is>
+          <t>20690 SAN ANTONIO DE QUIRIMAN/20690 SAN ANTONIO DE QUIRIMAN</t>
+        </is>
+      </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -12816,6 +14278,16 @@
       </c>
       <c r="R148" t="inlineStr">
         <is>
+          <t>20690 SAN ANTONIO DE QUIRIMAN/20690 SAN ANTONIO DE QUIRIMAN</t>
+        </is>
+      </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -12900,6 +14372,16 @@
       </c>
       <c r="R149" t="inlineStr">
         <is>
+          <t>20897 SAN JOSE DE NIEVE NIEVE</t>
+        </is>
+      </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -12984,6 +14466,16 @@
       </c>
       <c r="R150" t="inlineStr">
         <is>
+          <t>358</t>
+        </is>
+      </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -13068,6 +14560,16 @@
       </c>
       <c r="R151" t="inlineStr">
         <is>
+          <t>358</t>
+        </is>
+      </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -13152,6 +14654,16 @@
       </c>
       <c r="R152" t="inlineStr">
         <is>
+          <t>MARISCAL CHAPERITO</t>
+        </is>
+      </c>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -13236,6 +14748,16 @@
       </c>
       <c r="R153" t="inlineStr">
         <is>
+          <t>SAN PEDRO DE PILAS</t>
+        </is>
+      </c>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -13320,6 +14842,16 @@
       </c>
       <c r="R154" t="inlineStr">
         <is>
+          <t>1349</t>
+        </is>
+      </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T154" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -13404,6 +14936,16 @@
       </c>
       <c r="R155" t="inlineStr">
         <is>
+          <t>1432</t>
+        </is>
+      </c>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -13488,6 +15030,16 @@
       </c>
       <c r="R156" t="inlineStr">
         <is>
+          <t>14084</t>
+        </is>
+      </c>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T156" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -13572,6 +15124,16 @@
       </c>
       <c r="R157" t="inlineStr">
         <is>
+          <t>074 HILARIO MONTOYA SALDARRIAGA</t>
+        </is>
+      </c>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T157" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -13656,6 +15218,16 @@
       </c>
       <c r="R158" t="inlineStr">
         <is>
+          <t>429-173</t>
+        </is>
+      </c>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T158" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -13740,6 +15312,16 @@
       </c>
       <c r="R159" t="inlineStr">
         <is>
+          <t>429-173</t>
+        </is>
+      </c>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T159" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -13824,6 +15406,16 @@
       </c>
       <c r="R160" t="inlineStr">
         <is>
+          <t>794</t>
+        </is>
+      </c>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T160" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -13908,6 +15500,16 @@
       </c>
       <c r="R161" t="inlineStr">
         <is>
+          <t>794</t>
+        </is>
+      </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T161" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -13992,6 +15594,16 @@
       </c>
       <c r="R162" t="inlineStr">
         <is>
+          <t>1198</t>
+        </is>
+      </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T162" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -14076,6 +15688,16 @@
       </c>
       <c r="R163" t="inlineStr">
         <is>
+          <t>1198</t>
+        </is>
+      </c>
+      <c r="S163" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T163" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -14160,6 +15782,16 @@
       </c>
       <c r="R164" t="inlineStr">
         <is>
+          <t>542</t>
+        </is>
+      </c>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T164" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -14244,6 +15876,16 @@
       </c>
       <c r="R165" t="inlineStr">
         <is>
+          <t>542</t>
+        </is>
+      </c>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T165" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -14328,6 +15970,16 @@
       </c>
       <c r="R166" t="inlineStr">
         <is>
+          <t>JOYITAS DE JESUS</t>
+        </is>
+      </c>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T166" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -14412,6 +16064,16 @@
       </c>
       <c r="R167" t="inlineStr">
         <is>
+          <t>20031</t>
+        </is>
+      </c>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T167" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -14496,6 +16158,16 @@
       </c>
       <c r="R168" t="inlineStr">
         <is>
+          <t>20031</t>
+        </is>
+      </c>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T168" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -14580,6 +16252,16 @@
       </c>
       <c r="R169" t="inlineStr">
         <is>
+          <t>VIRGEN DEL ROSARIO</t>
+        </is>
+      </c>
+      <c r="S169" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T169" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -14664,6 +16346,16 @@
       </c>
       <c r="R170" t="inlineStr">
         <is>
+          <t>20648</t>
+        </is>
+      </c>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T170" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -14748,6 +16440,16 @@
       </c>
       <c r="R171" t="inlineStr">
         <is>
+          <t>20648</t>
+        </is>
+      </c>
+      <c r="S171" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T171" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -14832,6 +16534,16 @@
       </c>
       <c r="R172" t="inlineStr">
         <is>
+          <t>20913 ANTONIO PARCO CAJAHUARINGA</t>
+        </is>
+      </c>
+      <c r="S172" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T172" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -14916,6 +16628,16 @@
       </c>
       <c r="R173" t="inlineStr">
         <is>
+          <t>20950</t>
+        </is>
+      </c>
+      <c r="S173" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T173" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -15000,6 +16722,16 @@
       </c>
       <c r="R174" t="inlineStr">
         <is>
+          <t>20888 ALFONSO UGARTE</t>
+        </is>
+      </c>
+      <c r="S174" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T174" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -15084,6 +16816,16 @@
       </c>
       <c r="R175" t="inlineStr">
         <is>
+          <t>20888 ALFONSO UGARTE</t>
+        </is>
+      </c>
+      <c r="S175" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T175" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -15168,6 +16910,16 @@
       </c>
       <c r="R176" t="inlineStr">
         <is>
+          <t>1335</t>
+        </is>
+      </c>
+      <c r="S176" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T176" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -15252,6 +17004,16 @@
       </c>
       <c r="R177" t="inlineStr">
         <is>
+          <t>1336</t>
+        </is>
+      </c>
+      <c r="S177" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T177" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -15336,6 +17098,16 @@
       </c>
       <c r="R178" t="inlineStr">
         <is>
+          <t>1512</t>
+        </is>
+      </c>
+      <c r="S178" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T178" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -15420,6 +17192,16 @@
       </c>
       <c r="R179" t="inlineStr">
         <is>
+          <t>1520</t>
+        </is>
+      </c>
+      <c r="S179" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T179" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -15504,6 +17286,16 @@
       </c>
       <c r="R180" t="inlineStr">
         <is>
+          <t>14088</t>
+        </is>
+      </c>
+      <c r="S180" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T180" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -15588,6 +17380,16 @@
       </c>
       <c r="R181" t="inlineStr">
         <is>
+          <t>1339</t>
+        </is>
+      </c>
+      <c r="S181" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T181" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -15672,6 +17474,16 @@
       </c>
       <c r="R182" t="inlineStr">
         <is>
+          <t>ISAAC RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="S182" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T182" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -15756,6 +17568,16 @@
       </c>
       <c r="R183" t="inlineStr">
         <is>
+          <t>14973</t>
+        </is>
+      </c>
+      <c r="S183" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T183" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -15840,6 +17662,16 @@
       </c>
       <c r="R184" t="inlineStr">
         <is>
+          <t>20156</t>
+        </is>
+      </c>
+      <c r="S184" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T184" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -15924,6 +17756,16 @@
       </c>
       <c r="R185" t="inlineStr">
         <is>
+          <t>20177</t>
+        </is>
+      </c>
+      <c r="S185" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T185" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -16008,6 +17850,16 @@
       </c>
       <c r="R186" t="inlineStr">
         <is>
+          <t>20140</t>
+        </is>
+      </c>
+      <c r="S186" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T186" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -16092,6 +17944,16 @@
       </c>
       <c r="R187" t="inlineStr">
         <is>
+          <t>1382</t>
+        </is>
+      </c>
+      <c r="S187" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T187" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -16176,6 +18038,16 @@
       </c>
       <c r="R188" t="inlineStr">
         <is>
+          <t>15219</t>
+        </is>
+      </c>
+      <c r="S188" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T188" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -16260,6 +18132,16 @@
       </c>
       <c r="R189" t="inlineStr">
         <is>
+          <t>1445</t>
+        </is>
+      </c>
+      <c r="S189" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T189" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -16344,6 +18226,16 @@
       </c>
       <c r="R190" t="inlineStr">
         <is>
+          <t>20232/20232</t>
+        </is>
+      </c>
+      <c r="S190" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T190" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -16428,6 +18320,16 @@
       </c>
       <c r="R191" t="inlineStr">
         <is>
+          <t>1451</t>
+        </is>
+      </c>
+      <c r="S191" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T191" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -16512,6 +18414,16 @@
       </c>
       <c r="R192" t="inlineStr">
         <is>
+          <t>1399</t>
+        </is>
+      </c>
+      <c r="S192" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T192" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -16596,6 +18508,16 @@
       </c>
       <c r="R193" t="inlineStr">
         <is>
+          <t>15220</t>
+        </is>
+      </c>
+      <c r="S193" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T193" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -16680,6 +18602,16 @@
       </c>
       <c r="R194" t="inlineStr">
         <is>
+          <t>1368</t>
+        </is>
+      </c>
+      <c r="S194" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T194" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -16764,6 +18696,16 @@
       </c>
       <c r="R195" t="inlineStr">
         <is>
+          <t>1369</t>
+        </is>
+      </c>
+      <c r="S195" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T195" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -16848,6 +18790,16 @@
       </c>
       <c r="R196" t="inlineStr">
         <is>
+          <t>1381</t>
+        </is>
+      </c>
+      <c r="S196" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T196" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -16932,6 +18884,16 @@
       </c>
       <c r="R197" t="inlineStr">
         <is>
+          <t>068 MARIA MUÑOZ DE MEDINA</t>
+        </is>
+      </c>
+      <c r="S197" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T197" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -17016,6 +18978,16 @@
       </c>
       <c r="R198" t="inlineStr">
         <is>
+          <t>079 FRANCISCO BOLOGNESI CERVANTES</t>
+        </is>
+      </c>
+      <c r="S198" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T198" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -17100,6 +19072,16 @@
       </c>
       <c r="R199" t="inlineStr">
         <is>
+          <t>030</t>
+        </is>
+      </c>
+      <c r="S199" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T199" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -17184,6 +19166,16 @@
       </c>
       <c r="R200" t="inlineStr">
         <is>
+          <t>088</t>
+        </is>
+      </c>
+      <c r="S200" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T200" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -17268,6 +19260,16 @@
       </c>
       <c r="R201" t="inlineStr">
         <is>
+          <t>082 DANIEL ALCIDES CARRION</t>
+        </is>
+      </c>
+      <c r="S201" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T201" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -17352,6 +19354,16 @@
       </c>
       <c r="R202" t="inlineStr">
         <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="S202" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T202" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -17436,6 +19448,16 @@
       </c>
       <c r="R203" t="inlineStr">
         <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="S203" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T203" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -17520,6 +19542,16 @@
       </c>
       <c r="R204" t="inlineStr">
         <is>
+          <t>092 VIRGEN DEL ROSARIO</t>
+        </is>
+      </c>
+      <c r="S204" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T204" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -17604,6 +19636,16 @@
       </c>
       <c r="R205" t="inlineStr">
         <is>
+          <t>032</t>
+        </is>
+      </c>
+      <c r="S205" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T205" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -17688,6 +19730,16 @@
       </c>
       <c r="R206" t="inlineStr">
         <is>
+          <t>105 JUAN VELASCO ALVARADO</t>
+        </is>
+      </c>
+      <c r="S206" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T206" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -17772,6 +19824,16 @@
       </c>
       <c r="R207" t="inlineStr">
         <is>
+          <t>82815</t>
+        </is>
+      </c>
+      <c r="S207" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T207" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -17856,6 +19918,16 @@
       </c>
       <c r="R208" t="inlineStr">
         <is>
+          <t>82815</t>
+        </is>
+      </c>
+      <c r="S208" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T208" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -17940,6 +20012,16 @@
       </c>
       <c r="R209" t="inlineStr">
         <is>
+          <t>18001</t>
+        </is>
+      </c>
+      <c r="S209" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T209" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -18024,6 +20106,16 @@
       </c>
       <c r="R210" t="inlineStr">
         <is>
+          <t>1121</t>
+        </is>
+      </c>
+      <c r="S210" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T210" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -18108,6 +20200,16 @@
       </c>
       <c r="R211" t="inlineStr">
         <is>
+          <t>1121</t>
+        </is>
+      </c>
+      <c r="S211" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T211" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -18192,6 +20294,16 @@
       </c>
       <c r="R212" t="inlineStr">
         <is>
+          <t>2241</t>
+        </is>
+      </c>
+      <c r="S212" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T212" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -18276,6 +20388,16 @@
       </c>
       <c r="R213" t="inlineStr">
         <is>
+          <t>14454/14454</t>
+        </is>
+      </c>
+      <c r="S213" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T213" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -18360,6 +20482,16 @@
       </c>
       <c r="R214" t="inlineStr">
         <is>
+          <t>14454/14454</t>
+        </is>
+      </c>
+      <c r="S214" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T214" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -18444,6 +20576,16 @@
       </c>
       <c r="R215" t="inlineStr">
         <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="S215" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T215" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -18528,6 +20670,16 @@
       </c>
       <c r="R216" t="inlineStr">
         <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="S216" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T216" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -18612,6 +20764,16 @@
       </c>
       <c r="R217" t="inlineStr">
         <is>
+          <t>14191 SAN MARTIN DE PORRAS/14191 SAN MARTIN DE PORRAS</t>
+        </is>
+      </c>
+      <c r="S217" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T217" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -18696,6 +20858,16 @@
       </c>
       <c r="R218" t="inlineStr">
         <is>
+          <t>14191 SAN MARTIN DE PORRAS/14191 SAN MARTIN DE PORRAS</t>
+        </is>
+      </c>
+      <c r="S218" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T218" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -18780,6 +20952,16 @@
       </c>
       <c r="R219" t="inlineStr">
         <is>
+          <t>075 TEODOSIO TARAZONA VIDAL</t>
+        </is>
+      </c>
+      <c r="S219" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T219" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -18864,6 +21046,16 @@
       </c>
       <c r="R220" t="inlineStr">
         <is>
+          <t>075 TEODOSIO TARAZONA VIDAL</t>
+        </is>
+      </c>
+      <c r="S220" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T220" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -18948,6 +21140,16 @@
       </c>
       <c r="R221" t="inlineStr">
         <is>
+          <t>1583</t>
+        </is>
+      </c>
+      <c r="S221" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T221" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -19032,6 +21234,16 @@
       </c>
       <c r="R222" t="inlineStr">
         <is>
+          <t>1273</t>
+        </is>
+      </c>
+      <c r="S222" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T222" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -19116,6 +21328,16 @@
       </c>
       <c r="R223" t="inlineStr">
         <is>
+          <t>1289</t>
+        </is>
+      </c>
+      <c r="S223" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T223" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -19200,6 +21422,16 @@
       </c>
       <c r="R224" t="inlineStr">
         <is>
+          <t>1469</t>
+        </is>
+      </c>
+      <c r="S224" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T224" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -19284,6 +21516,16 @@
       </c>
       <c r="R225" t="inlineStr">
         <is>
+          <t>1470</t>
+        </is>
+      </c>
+      <c r="S225" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T225" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -19368,6 +21610,16 @@
       </c>
       <c r="R226" t="inlineStr">
         <is>
+          <t>1476</t>
+        </is>
+      </c>
+      <c r="S226" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T226" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -19452,6 +21704,16 @@
       </c>
       <c r="R227" t="inlineStr">
         <is>
+          <t>390</t>
+        </is>
+      </c>
+      <c r="S227" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T227" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -19536,6 +21798,16 @@
       </c>
       <c r="R228" t="inlineStr">
         <is>
+          <t>390</t>
+        </is>
+      </c>
+      <c r="S228" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T228" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -19620,6 +21892,16 @@
       </c>
       <c r="R229" t="inlineStr">
         <is>
+          <t>86589 SAN MARTIN DE PORRES</t>
+        </is>
+      </c>
+      <c r="S229" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T229" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -19704,6 +21986,16 @@
       </c>
       <c r="R230" t="inlineStr">
         <is>
+          <t>86589 SAN MARTIN DE PORRES</t>
+        </is>
+      </c>
+      <c r="S230" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T230" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -19788,6 +22080,16 @@
       </c>
       <c r="R231" t="inlineStr">
         <is>
+          <t>86615/86615</t>
+        </is>
+      </c>
+      <c r="S231" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T231" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -19872,6 +22174,16 @@
       </c>
       <c r="R232" t="inlineStr">
         <is>
+          <t>86615/86615</t>
+        </is>
+      </c>
+      <c r="S232" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T232" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -19956,6 +22268,16 @@
       </c>
       <c r="R233" t="inlineStr">
         <is>
+          <t>87508 DON MIGUEL DE CERVANTES SAAVEDRA</t>
+        </is>
+      </c>
+      <c r="S233" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T233" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -20040,6 +22362,16 @@
       </c>
       <c r="R234" t="inlineStr">
         <is>
+          <t>87508 DON MIGUEL DE CERVANTES SAAVEDRA</t>
+        </is>
+      </c>
+      <c r="S234" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T234" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -20124,6 +22456,16 @@
       </c>
       <c r="R235" t="inlineStr">
         <is>
+          <t>041</t>
+        </is>
+      </c>
+      <c r="S235" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T235" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -20208,6 +22550,16 @@
       </c>
       <c r="R236" t="inlineStr">
         <is>
+          <t>88074</t>
+        </is>
+      </c>
+      <c r="S236" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T236" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -20292,6 +22644,16 @@
       </c>
       <c r="R237" t="inlineStr">
         <is>
+          <t>88074</t>
+        </is>
+      </c>
+      <c r="S237" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T237" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -20376,6 +22738,16 @@
       </c>
       <c r="R238" t="inlineStr">
         <is>
+          <t>86969</t>
+        </is>
+      </c>
+      <c r="S238" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T238" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -20460,6 +22832,16 @@
       </c>
       <c r="R239" t="inlineStr">
         <is>
+          <t>86969</t>
+        </is>
+      </c>
+      <c r="S239" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T239" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -20544,6 +22926,16 @@
       </c>
       <c r="R240" t="inlineStr">
         <is>
+          <t>486</t>
+        </is>
+      </c>
+      <c r="S240" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T240" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -20628,6 +23020,16 @@
       </c>
       <c r="R241" t="inlineStr">
         <is>
+          <t>501</t>
+        </is>
+      </c>
+      <c r="S241" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T241" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -20712,6 +23114,16 @@
       </c>
       <c r="R242" t="inlineStr">
         <is>
+          <t>501</t>
+        </is>
+      </c>
+      <c r="S242" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T242" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -20796,6 +23208,16 @@
       </c>
       <c r="R243" t="inlineStr">
         <is>
+          <t>15445</t>
+        </is>
+      </c>
+      <c r="S243" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T243" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -20880,6 +23302,16 @@
       </c>
       <c r="R244" t="inlineStr">
         <is>
+          <t>15445</t>
+        </is>
+      </c>
+      <c r="S244" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T244" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -20964,6 +23396,16 @@
       </c>
       <c r="R245" t="inlineStr">
         <is>
+          <t>15189</t>
+        </is>
+      </c>
+      <c r="S245" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T245" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -21048,6 +23490,16 @@
       </c>
       <c r="R246" t="inlineStr">
         <is>
+          <t>1001 LA RINCONADA</t>
+        </is>
+      </c>
+      <c r="S246" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T246" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -21132,6 +23584,16 @@
       </c>
       <c r="R247" t="inlineStr">
         <is>
+          <t>86963</t>
+        </is>
+      </c>
+      <c r="S247" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T247" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -21216,6 +23678,16 @@
       </c>
       <c r="R248" t="inlineStr">
         <is>
+          <t>86510 PEDRO PABLO ATUSPARIA</t>
+        </is>
+      </c>
+      <c r="S248" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T248" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -21300,6 +23772,16 @@
       </c>
       <c r="R249" t="inlineStr">
         <is>
+          <t>86529 ALFONSO UGARTE</t>
+        </is>
+      </c>
+      <c r="S249" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T249" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -21384,6 +23866,16 @@
       </c>
       <c r="R250" t="inlineStr">
         <is>
+          <t>86529 ALFONSO UGARTE</t>
+        </is>
+      </c>
+      <c r="S250" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T250" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -21468,6 +23960,16 @@
       </c>
       <c r="R251" t="inlineStr">
         <is>
+          <t>88371</t>
+        </is>
+      </c>
+      <c r="S251" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T251" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -21552,6 +24054,16 @@
       </c>
       <c r="R252" t="inlineStr">
         <is>
+          <t>88371</t>
+        </is>
+      </c>
+      <c r="S252" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T252" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -21636,6 +24148,16 @@
       </c>
       <c r="R253" t="inlineStr">
         <is>
+          <t>20485</t>
+        </is>
+      </c>
+      <c r="S253" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T253" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -21720,6 +24242,16 @@
       </c>
       <c r="R254" t="inlineStr">
         <is>
+          <t>20485</t>
+        </is>
+      </c>
+      <c r="S254" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T254" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -21804,6 +24336,16 @@
       </c>
       <c r="R255" t="inlineStr">
         <is>
+          <t>413</t>
+        </is>
+      </c>
+      <c r="S255" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T255" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -21888,6 +24430,16 @@
       </c>
       <c r="R256" t="inlineStr">
         <is>
+          <t>84037</t>
+        </is>
+      </c>
+      <c r="S256" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T256" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -21972,6 +24524,16 @@
       </c>
       <c r="R257" t="inlineStr">
         <is>
+          <t>84037</t>
+        </is>
+      </c>
+      <c r="S257" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T257" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -22056,6 +24618,16 @@
       </c>
       <c r="R258" t="inlineStr">
         <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="S258" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T258" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -22140,6 +24712,16 @@
       </c>
       <c r="R259" t="inlineStr">
         <is>
+          <t>653</t>
+        </is>
+      </c>
+      <c r="S259" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T259" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -22224,6 +24806,16 @@
       </c>
       <c r="R260" t="inlineStr">
         <is>
+          <t>653</t>
+        </is>
+      </c>
+      <c r="S260" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T260" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -22308,6 +24900,16 @@
       </c>
       <c r="R261" t="inlineStr">
         <is>
+          <t>2635</t>
+        </is>
+      </c>
+      <c r="S261" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T261" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -22392,6 +24994,16 @@
       </c>
       <c r="R262" t="inlineStr">
         <is>
+          <t>2635</t>
+        </is>
+      </c>
+      <c r="S262" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T262" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -22476,6 +25088,16 @@
       </c>
       <c r="R263" t="inlineStr">
         <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="S263" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T263" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -22560,6 +25182,16 @@
       </c>
       <c r="R264" t="inlineStr">
         <is>
+          <t>20511</t>
+        </is>
+      </c>
+      <c r="S264" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T264" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -22644,6 +25276,16 @@
       </c>
       <c r="R265" t="inlineStr">
         <is>
+          <t>1657</t>
+        </is>
+      </c>
+      <c r="S265" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T265" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -22728,6 +25370,16 @@
       </c>
       <c r="R266" t="inlineStr">
         <is>
+          <t>1657</t>
+        </is>
+      </c>
+      <c r="S266" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T266" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -22808,6 +25460,16 @@
       </c>
       <c r="R267" t="inlineStr">
         <is>
+          <t>84152 ULISES LLANOS OLIVEROS</t>
+        </is>
+      </c>
+      <c r="S267" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T267" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -22888,6 +25550,16 @@
       </c>
       <c r="R268" t="inlineStr">
         <is>
+          <t>84152 ULISES LLANOS OLIVEROS</t>
+        </is>
+      </c>
+      <c r="S268" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T268" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -22972,6 +25644,16 @@
       </c>
       <c r="R269" t="inlineStr">
         <is>
+          <t>2626</t>
+        </is>
+      </c>
+      <c r="S269" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T269" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -23056,6 +25738,16 @@
       </c>
       <c r="R270" t="inlineStr">
         <is>
+          <t>029-1 CORDERITOS DE JESUS</t>
+        </is>
+      </c>
+      <c r="S270" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T270" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -23140,6 +25832,16 @@
       </c>
       <c r="R271" t="inlineStr">
         <is>
+          <t>029-1 CORDERITOS DE JESUS</t>
+        </is>
+      </c>
+      <c r="S271" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T271" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -23224,6 +25926,16 @@
       </c>
       <c r="R272" t="inlineStr">
         <is>
+          <t>86570 SANTO DOMINGO DE COMPINA</t>
+        </is>
+      </c>
+      <c r="S272" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T272" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -23308,6 +26020,16 @@
       </c>
       <c r="R273" t="inlineStr">
         <is>
+          <t>86570 SANTO DOMINGO DE COMPINA</t>
+        </is>
+      </c>
+      <c r="S273" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T273" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -23392,6 +26114,16 @@
       </c>
       <c r="R274" t="inlineStr">
         <is>
+          <t>708</t>
+        </is>
+      </c>
+      <c r="S274" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T274" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -23476,6 +26208,16 @@
       </c>
       <c r="R275" t="inlineStr">
         <is>
+          <t>657</t>
+        </is>
+      </c>
+      <c r="S275" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T275" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -23560,6 +26302,16 @@
       </c>
       <c r="R276" t="inlineStr">
         <is>
+          <t>657</t>
+        </is>
+      </c>
+      <c r="S276" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T276" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -23644,6 +26396,16 @@
       </c>
       <c r="R277" t="inlineStr">
         <is>
+          <t>521</t>
+        </is>
+      </c>
+      <c r="S277" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T277" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -23728,6 +26490,16 @@
       </c>
       <c r="R278" t="inlineStr">
         <is>
+          <t>703</t>
+        </is>
+      </c>
+      <c r="S278" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T278" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -23812,6 +26584,16 @@
       </c>
       <c r="R279" t="inlineStr">
         <is>
+          <t>401</t>
+        </is>
+      </c>
+      <c r="S279" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T279" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -23896,6 +26678,16 @@
       </c>
       <c r="R280" t="inlineStr">
         <is>
+          <t>401</t>
+        </is>
+      </c>
+      <c r="S280" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T280" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -23980,6 +26772,16 @@
       </c>
       <c r="R281" t="inlineStr">
         <is>
+          <t>LLANCA</t>
+        </is>
+      </c>
+      <c r="S281" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T281" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -24064,6 +26866,16 @@
       </c>
       <c r="R282" t="inlineStr">
         <is>
+          <t>LLANCA</t>
+        </is>
+      </c>
+      <c r="S282" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T282" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -24148,6 +26960,16 @@
       </c>
       <c r="R283" t="inlineStr">
         <is>
+          <t>20053</t>
+        </is>
+      </c>
+      <c r="S283" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T283" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -24232,6 +27054,16 @@
       </c>
       <c r="R284" t="inlineStr">
         <is>
+          <t>14639</t>
+        </is>
+      </c>
+      <c r="S284" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T284" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -24316,6 +27148,16 @@
       </c>
       <c r="R285" t="inlineStr">
         <is>
+          <t>1298</t>
+        </is>
+      </c>
+      <c r="S285" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T285" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -24400,6 +27242,16 @@
       </c>
       <c r="R286" t="inlineStr">
         <is>
+          <t>20656</t>
+        </is>
+      </c>
+      <c r="S286" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T286" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -24484,6 +27336,16 @@
       </c>
       <c r="R287" t="inlineStr">
         <is>
+          <t>20656</t>
+        </is>
+      </c>
+      <c r="S287" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T287" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -24568,6 +27430,16 @@
       </c>
       <c r="R288" t="inlineStr">
         <is>
+          <t>1250</t>
+        </is>
+      </c>
+      <c r="S288" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T288" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -24652,6 +27524,16 @@
       </c>
       <c r="R289" t="inlineStr">
         <is>
+          <t>1250</t>
+        </is>
+      </c>
+      <c r="S289" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T289" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -24736,6 +27618,16 @@
       </c>
       <c r="R290" t="inlineStr">
         <is>
+          <t>1266</t>
+        </is>
+      </c>
+      <c r="S290" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T290" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -24820,6 +27712,16 @@
       </c>
       <c r="R291" t="inlineStr">
         <is>
+          <t>1266</t>
+        </is>
+      </c>
+      <c r="S291" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T291" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -24904,6 +27806,16 @@
       </c>
       <c r="R292" t="inlineStr">
         <is>
+          <t>1288</t>
+        </is>
+      </c>
+      <c r="S292" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T292" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -24988,6 +27900,16 @@
       </c>
       <c r="R293" t="inlineStr">
         <is>
+          <t>1288</t>
+        </is>
+      </c>
+      <c r="S293" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T293" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -25072,6 +27994,16 @@
       </c>
       <c r="R294" t="inlineStr">
         <is>
+          <t>988</t>
+        </is>
+      </c>
+      <c r="S294" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T294" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -25156,6 +28088,16 @@
       </c>
       <c r="R295" t="inlineStr">
         <is>
+          <t>988</t>
+        </is>
+      </c>
+      <c r="S295" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T295" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -25240,6 +28182,16 @@
       </c>
       <c r="R296" t="inlineStr">
         <is>
+          <t>1293</t>
+        </is>
+      </c>
+      <c r="S296" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T296" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -25324,6 +28276,16 @@
       </c>
       <c r="R297" t="inlineStr">
         <is>
+          <t>1193</t>
+        </is>
+      </c>
+      <c r="S297" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T297" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -25408,6 +28370,16 @@
       </c>
       <c r="R298" t="inlineStr">
         <is>
+          <t>925 NIÑO JESUS</t>
+        </is>
+      </c>
+      <c r="S298" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T298" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -25492,6 +28464,16 @@
       </c>
       <c r="R299" t="inlineStr">
         <is>
+          <t>1248</t>
+        </is>
+      </c>
+      <c r="S299" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T299" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -25576,6 +28558,16 @@
       </c>
       <c r="R300" t="inlineStr">
         <is>
+          <t>1248</t>
+        </is>
+      </c>
+      <c r="S300" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T300" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -25660,6 +28652,16 @@
       </c>
       <c r="R301" t="inlineStr">
         <is>
+          <t>1251</t>
+        </is>
+      </c>
+      <c r="S301" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T301" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -25744,6 +28746,16 @@
       </c>
       <c r="R302" t="inlineStr">
         <is>
+          <t>1251</t>
+        </is>
+      </c>
+      <c r="S302" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T302" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -25828,6 +28840,16 @@
       </c>
       <c r="R303" t="inlineStr">
         <is>
+          <t>476</t>
+        </is>
+      </c>
+      <c r="S303" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T303" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -25912,6 +28934,16 @@
       </c>
       <c r="R304" t="inlineStr">
         <is>
+          <t>1286</t>
+        </is>
+      </c>
+      <c r="S304" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T304" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -25996,6 +29028,16 @@
       </c>
       <c r="R305" t="inlineStr">
         <is>
+          <t>1286</t>
+        </is>
+      </c>
+      <c r="S305" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T305" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -26080,6 +29122,16 @@
       </c>
       <c r="R306" t="inlineStr">
         <is>
+          <t>1270</t>
+        </is>
+      </c>
+      <c r="S306" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T306" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -26164,6 +29216,16 @@
       </c>
       <c r="R307" t="inlineStr">
         <is>
+          <t>1270</t>
+        </is>
+      </c>
+      <c r="S307" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T307" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -26248,6 +29310,16 @@
       </c>
       <c r="R308" t="inlineStr">
         <is>
+          <t>14492</t>
+        </is>
+      </c>
+      <c r="S308" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T308" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -26332,6 +29404,16 @@
       </c>
       <c r="R309" t="inlineStr">
         <is>
+          <t>88194</t>
+        </is>
+      </c>
+      <c r="S309" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T309" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -26416,6 +29498,16 @@
       </c>
       <c r="R310" t="inlineStr">
         <is>
+          <t>88194</t>
+        </is>
+      </c>
+      <c r="S310" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T310" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -26500,6 +29592,16 @@
       </c>
       <c r="R311" t="inlineStr">
         <is>
+          <t>84139 CIRILO CALIXTO FELIPE</t>
+        </is>
+      </c>
+      <c r="S311" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T311" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -26584,6 +29686,16 @@
       </c>
       <c r="R312" t="inlineStr">
         <is>
+          <t>84139 CIRILO CALIXTO FELIPE</t>
+        </is>
+      </c>
+      <c r="S312" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T312" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -26668,6 +29780,16 @@
       </c>
       <c r="R313" t="inlineStr">
         <is>
+          <t>1091</t>
+        </is>
+      </c>
+      <c r="S313" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T313" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -26752,6 +29874,16 @@
       </c>
       <c r="R314" t="inlineStr">
         <is>
+          <t>1091</t>
+        </is>
+      </c>
+      <c r="S314" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T314" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -26836,6 +29968,16 @@
       </c>
       <c r="R315" t="inlineStr">
         <is>
+          <t>15083</t>
+        </is>
+      </c>
+      <c r="S315" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T315" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -26920,6 +30062,16 @@
       </c>
       <c r="R316" t="inlineStr">
         <is>
+          <t>15083</t>
+        </is>
+      </c>
+      <c r="S316" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T316" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -27004,6 +30156,16 @@
       </c>
       <c r="R317" t="inlineStr">
         <is>
+          <t>1019</t>
+        </is>
+      </c>
+      <c r="S317" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T317" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -27088,6 +30250,16 @@
       </c>
       <c r="R318" t="inlineStr">
         <is>
+          <t>15243</t>
+        </is>
+      </c>
+      <c r="S318" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T318" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -27172,6 +30344,16 @@
       </c>
       <c r="R319" t="inlineStr">
         <is>
+          <t>15243</t>
+        </is>
+      </c>
+      <c r="S319" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T319" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -27256,6 +30438,16 @@
       </c>
       <c r="R320" t="inlineStr">
         <is>
+          <t>2315</t>
+        </is>
+      </c>
+      <c r="S320" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T320" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -27340,6 +30532,16 @@
       </c>
       <c r="R321" t="inlineStr">
         <is>
+          <t>2315</t>
+        </is>
+      </c>
+      <c r="S321" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T321" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -27424,6 +30626,16 @@
       </c>
       <c r="R322" t="inlineStr">
         <is>
+          <t>80093 JOSE OLAYA/80093 JOSE OLAYA</t>
+        </is>
+      </c>
+      <c r="S322" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T322" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -27508,6 +30720,16 @@
       </c>
       <c r="R323" t="inlineStr">
         <is>
+          <t>80395/80395</t>
+        </is>
+      </c>
+      <c r="S323" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T323" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -27592,6 +30814,16 @@
       </c>
       <c r="R324" t="inlineStr">
         <is>
+          <t>80395/80395</t>
+        </is>
+      </c>
+      <c r="S324" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T324" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -27676,6 +30908,16 @@
       </c>
       <c r="R325" t="inlineStr">
         <is>
+          <t>82208 MARQUEZ DE TORRE TAGLE/82208 MARQUEZ DE TORRE TAGLE/82208 MARQUEZ DE TORRE TAGLE</t>
+        </is>
+      </c>
+      <c r="S325" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T325" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -27760,6 +31002,16 @@
       </c>
       <c r="R326" t="inlineStr">
         <is>
+          <t>2343</t>
+        </is>
+      </c>
+      <c r="S326" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T326" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -27844,6 +31096,16 @@
       </c>
       <c r="R327" t="inlineStr">
         <is>
+          <t>2343</t>
+        </is>
+      </c>
+      <c r="S327" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T327" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -27928,6 +31190,16 @@
       </c>
       <c r="R328" t="inlineStr">
         <is>
+          <t>372</t>
+        </is>
+      </c>
+      <c r="S328" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T328" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -28012,6 +31284,16 @@
       </c>
       <c r="R329" t="inlineStr">
         <is>
+          <t>372</t>
+        </is>
+      </c>
+      <c r="S329" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T329" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -28096,6 +31378,16 @@
       </c>
       <c r="R330" t="inlineStr">
         <is>
+          <t>484</t>
+        </is>
+      </c>
+      <c r="S330" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T330" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -28180,6 +31472,16 @@
       </c>
       <c r="R331" t="inlineStr">
         <is>
+          <t>388</t>
+        </is>
+      </c>
+      <c r="S331" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T331" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -28264,6 +31566,16 @@
       </c>
       <c r="R332" t="inlineStr">
         <is>
+          <t>389</t>
+        </is>
+      </c>
+      <c r="S332" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T332" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -28348,6 +31660,16 @@
       </c>
       <c r="R333" t="inlineStr">
         <is>
+          <t>1825</t>
+        </is>
+      </c>
+      <c r="S333" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T333" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -28432,6 +31754,16 @@
       </c>
       <c r="R334" t="inlineStr">
         <is>
+          <t>2192</t>
+        </is>
+      </c>
+      <c r="S334" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T334" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -28516,6 +31848,16 @@
       </c>
       <c r="R335" t="inlineStr">
         <is>
+          <t>2192</t>
+        </is>
+      </c>
+      <c r="S335" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T335" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -28600,6 +31942,16 @@
       </c>
       <c r="R336" t="inlineStr">
         <is>
+          <t>81719</t>
+        </is>
+      </c>
+      <c r="S336" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T336" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -28684,6 +32036,16 @@
       </c>
       <c r="R337" t="inlineStr">
         <is>
+          <t>501</t>
+        </is>
+      </c>
+      <c r="S337" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T337" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -28768,6 +32130,16 @@
       </c>
       <c r="R338" t="inlineStr">
         <is>
+          <t>JUAN BASILIO VILLALOBOS/JUAN BASILIO VILLALOBOS</t>
+        </is>
+      </c>
+      <c r="S338" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T338" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -28852,6 +32224,16 @@
       </c>
       <c r="R339" t="inlineStr">
         <is>
+          <t>MACABI BAJO</t>
+        </is>
+      </c>
+      <c r="S339" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T339" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -28936,6 +32318,16 @@
       </c>
       <c r="R340" t="inlineStr">
         <is>
+          <t>10241</t>
+        </is>
+      </c>
+      <c r="S340" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T340" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -29020,6 +32412,16 @@
       </c>
       <c r="R341" t="inlineStr">
         <is>
+          <t>10998 SANTISIMA TRINIDAD</t>
+        </is>
+      </c>
+      <c r="S341" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T341" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -29104,6 +32506,16 @@
       </c>
       <c r="R342" t="inlineStr">
         <is>
+          <t>997</t>
+        </is>
+      </c>
+      <c r="S342" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T342" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -29188,6 +32600,16 @@
       </c>
       <c r="R343" t="inlineStr">
         <is>
+          <t>1109</t>
+        </is>
+      </c>
+      <c r="S343" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T343" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -29272,6 +32694,16 @@
       </c>
       <c r="R344" t="inlineStr">
         <is>
+          <t>319</t>
+        </is>
+      </c>
+      <c r="S344" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T344" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -29356,6 +32788,16 @@
       </c>
       <c r="R345" t="inlineStr">
         <is>
+          <t>895</t>
+        </is>
+      </c>
+      <c r="S345" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T345" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -29440,6 +32882,16 @@
       </c>
       <c r="R346" t="inlineStr">
         <is>
+          <t>80913</t>
+        </is>
+      </c>
+      <c r="S346" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T346" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -29524,6 +32976,16 @@
       </c>
       <c r="R347" t="inlineStr">
         <is>
+          <t>2305</t>
+        </is>
+      </c>
+      <c r="S347" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T347" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -29608,6 +33070,16 @@
       </c>
       <c r="R348" t="inlineStr">
         <is>
+          <t>82613</t>
+        </is>
+      </c>
+      <c r="S348" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T348" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -29692,6 +33164,16 @@
       </c>
       <c r="R349" t="inlineStr">
         <is>
+          <t>80083</t>
+        </is>
+      </c>
+      <c r="S349" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T349" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -29776,6 +33258,16 @@
       </c>
       <c r="R350" t="inlineStr">
         <is>
+          <t>122 PEDRO DIAZ VERGARA</t>
+        </is>
+      </c>
+      <c r="S350" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T350" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -29860,6 +33352,16 @@
       </c>
       <c r="R351" t="inlineStr">
         <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="S351" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T351" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -29944,6 +33446,16 @@
       </c>
       <c r="R352" t="inlineStr">
         <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="S352" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T352" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -30028,6 +33540,16 @@
       </c>
       <c r="R353" t="inlineStr">
         <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="S353" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T353" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -30112,6 +33634,16 @@
       </c>
       <c r="R354" t="inlineStr">
         <is>
+          <t>2310</t>
+        </is>
+      </c>
+      <c r="S354" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T354" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -30196,6 +33728,16 @@
       </c>
       <c r="R355" t="inlineStr">
         <is>
+          <t>2310</t>
+        </is>
+      </c>
+      <c r="S355" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T355" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -30280,6 +33822,16 @@
       </c>
       <c r="R356" t="inlineStr">
         <is>
+          <t>2175</t>
+        </is>
+      </c>
+      <c r="S356" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T356" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -30364,6 +33916,16 @@
       </c>
       <c r="R357" t="inlineStr">
         <is>
+          <t>2289</t>
+        </is>
+      </c>
+      <c r="S357" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T357" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -30448,6 +34010,16 @@
       </c>
       <c r="R358" t="inlineStr">
         <is>
+          <t>10779 GENERAL OSCAR RAIMUNDO BENAVIDES LARREA</t>
+        </is>
+      </c>
+      <c r="S358" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T358" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -30532,6 +34104,16 @@
       </c>
       <c r="R359" t="inlineStr">
         <is>
+          <t>11590 JUAN PABLO II</t>
+        </is>
+      </c>
+      <c r="S359" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T359" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -30616,6 +34198,16 @@
       </c>
       <c r="R360" t="inlineStr">
         <is>
+          <t>377</t>
+        </is>
+      </c>
+      <c r="S360" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T360" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -30700,6 +34292,16 @@
       </c>
       <c r="R361" t="inlineStr">
         <is>
+          <t>384</t>
+        </is>
+      </c>
+      <c r="S361" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T361" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -30784,6 +34386,16 @@
       </c>
       <c r="R362" t="inlineStr">
         <is>
+          <t>384</t>
+        </is>
+      </c>
+      <c r="S362" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T362" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -30868,6 +34480,16 @@
       </c>
       <c r="R363" t="inlineStr">
         <is>
+          <t>384</t>
+        </is>
+      </c>
+      <c r="S363" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T363" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -30952,6 +34574,16 @@
       </c>
       <c r="R364" t="inlineStr">
         <is>
+          <t>510 BLANCA VALERA GONZALES</t>
+        </is>
+      </c>
+      <c r="S364" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T364" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -31036,6 +34668,16 @@
       </c>
       <c r="R365" t="inlineStr">
         <is>
+          <t>510 BLANCA VALERA GONZALES</t>
+        </is>
+      </c>
+      <c r="S365" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T365" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -31120,6 +34762,16 @@
       </c>
       <c r="R366" t="inlineStr">
         <is>
+          <t>11238</t>
+        </is>
+      </c>
+      <c r="S366" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T366" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -31204,6 +34856,16 @@
       </c>
       <c r="R367" t="inlineStr">
         <is>
+          <t>11243</t>
+        </is>
+      </c>
+      <c r="S367" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T367" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -31288,6 +34950,16 @@
       </c>
       <c r="R368" t="inlineStr">
         <is>
+          <t>86232</t>
+        </is>
+      </c>
+      <c r="S368" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T368" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -31372,6 +35044,16 @@
       </c>
       <c r="R369" t="inlineStr">
         <is>
+          <t>1652</t>
+        </is>
+      </c>
+      <c r="S369" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T369" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -31456,6 +35138,16 @@
       </c>
       <c r="R370" t="inlineStr">
         <is>
+          <t>026</t>
+        </is>
+      </c>
+      <c r="S370" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T370" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -31540,6 +35232,16 @@
       </c>
       <c r="R371" t="inlineStr">
         <is>
+          <t>026</t>
+        </is>
+      </c>
+      <c r="S371" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T371" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -31624,6 +35326,16 @@
       </c>
       <c r="R372" t="inlineStr">
         <is>
+          <t>424</t>
+        </is>
+      </c>
+      <c r="S372" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T372" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -31708,6 +35420,16 @@
       </c>
       <c r="R373" t="inlineStr">
         <is>
+          <t>424</t>
+        </is>
+      </c>
+      <c r="S373" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T373" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -31792,6 +35514,16 @@
       </c>
       <c r="R374" t="inlineStr">
         <is>
+          <t>88339</t>
+        </is>
+      </c>
+      <c r="S374" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T374" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -31876,6 +35608,16 @@
       </c>
       <c r="R375" t="inlineStr">
         <is>
+          <t>315</t>
+        </is>
+      </c>
+      <c r="S375" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T375" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -31960,6 +35702,16 @@
       </c>
       <c r="R376" t="inlineStr">
         <is>
+          <t>453</t>
+        </is>
+      </c>
+      <c r="S376" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T376" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -32044,6 +35796,16 @@
       </c>
       <c r="R377" t="inlineStr">
         <is>
+          <t>453</t>
+        </is>
+      </c>
+      <c r="S377" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T377" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -32128,6 +35890,16 @@
       </c>
       <c r="R378" t="inlineStr">
         <is>
+          <t>86237 JOSE ANDRES RAZURI/86237 JOSE ANDRES RAZURI</t>
+        </is>
+      </c>
+      <c r="S378" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T378" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -32212,6 +35984,16 @@
       </c>
       <c r="R379" t="inlineStr">
         <is>
+          <t>86307 TEOFILO CASTILLO</t>
+        </is>
+      </c>
+      <c r="S379" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T379" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -32296,6 +36078,16 @@
       </c>
       <c r="R380" t="inlineStr">
         <is>
+          <t>88249 RAMON CASTILLA</t>
+        </is>
+      </c>
+      <c r="S380" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T380" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -32380,6 +36172,16 @@
       </c>
       <c r="R381" t="inlineStr">
         <is>
+          <t>86053</t>
+        </is>
+      </c>
+      <c r="S381" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T381" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -32464,6 +36266,16 @@
       </c>
       <c r="R382" t="inlineStr">
         <is>
+          <t>620</t>
+        </is>
+      </c>
+      <c r="S382" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T382" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -32548,6 +36360,16 @@
       </c>
       <c r="R383" t="inlineStr">
         <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="S383" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T383" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -32632,6 +36454,16 @@
       </c>
       <c r="R384" t="inlineStr">
         <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="S384" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T384" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -32716,6 +36548,16 @@
       </c>
       <c r="R385" t="inlineStr">
         <is>
+          <t>86105</t>
+        </is>
+      </c>
+      <c r="S385" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T385" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -32800,6 +36642,16 @@
       </c>
       <c r="R386" t="inlineStr">
         <is>
+          <t>431</t>
+        </is>
+      </c>
+      <c r="S386" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T386" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -32884,6 +36736,16 @@
       </c>
       <c r="R387" t="inlineStr">
         <is>
+          <t>442</t>
+        </is>
+      </c>
+      <c r="S387" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T387" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -32968,6 +36830,16 @@
       </c>
       <c r="R388" t="inlineStr">
         <is>
+          <t>2605</t>
+        </is>
+      </c>
+      <c r="S388" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T388" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -33052,6 +36924,16 @@
       </c>
       <c r="R389" t="inlineStr">
         <is>
+          <t>396</t>
+        </is>
+      </c>
+      <c r="S389" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T389" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -33136,6 +37018,16 @@
       </c>
       <c r="R390" t="inlineStr">
         <is>
+          <t>396</t>
+        </is>
+      </c>
+      <c r="S390" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T390" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -33220,6 +37112,16 @@
       </c>
       <c r="R391" t="inlineStr">
         <is>
+          <t>422</t>
+        </is>
+      </c>
+      <c r="S391" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T391" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -33304,6 +37206,16 @@
       </c>
       <c r="R392" t="inlineStr">
         <is>
+          <t>86852</t>
+        </is>
+      </c>
+      <c r="S392" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T392" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -33388,6 +37300,16 @@
       </c>
       <c r="R393" t="inlineStr">
         <is>
+          <t>86933</t>
+        </is>
+      </c>
+      <c r="S393" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T393" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -33472,6 +37394,16 @@
       </c>
       <c r="R394" t="inlineStr">
         <is>
+          <t>86311/86311</t>
+        </is>
+      </c>
+      <c r="S394" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T394" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -33556,6 +37488,16 @@
       </c>
       <c r="R395" t="inlineStr">
         <is>
+          <t>86311/86311</t>
+        </is>
+      </c>
+      <c r="S395" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T395" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -33640,6 +37582,16 @@
       </c>
       <c r="R396" t="inlineStr">
         <is>
+          <t>86311/86311</t>
+        </is>
+      </c>
+      <c r="S396" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T396" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -33724,6 +37676,16 @@
       </c>
       <c r="R397" t="inlineStr">
         <is>
+          <t>1122</t>
+        </is>
+      </c>
+      <c r="S397" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T397" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -33808,6 +37770,16 @@
       </c>
       <c r="R398" t="inlineStr">
         <is>
+          <t>1122</t>
+        </is>
+      </c>
+      <c r="S398" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T398" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -33892,6 +37864,16 @@
       </c>
       <c r="R399" t="inlineStr">
         <is>
+          <t>1122</t>
+        </is>
+      </c>
+      <c r="S399" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T399" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -33976,6 +37958,16 @@
       </c>
       <c r="R400" t="inlineStr">
         <is>
+          <t>1554</t>
+        </is>
+      </c>
+      <c r="S400" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T400" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -34060,6 +38052,16 @@
       </c>
       <c r="R401" t="inlineStr">
         <is>
+          <t>1554</t>
+        </is>
+      </c>
+      <c r="S401" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T401" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -34144,6 +38146,16 @@
       </c>
       <c r="R402" t="inlineStr">
         <is>
+          <t>JABONILLAL</t>
+        </is>
+      </c>
+      <c r="S402" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T402" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -34228,6 +38240,16 @@
       </c>
       <c r="R403" t="inlineStr">
         <is>
+          <t>1148</t>
+        </is>
+      </c>
+      <c r="S403" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T403" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -34312,6 +38334,16 @@
       </c>
       <c r="R404" t="inlineStr">
         <is>
+          <t>1596</t>
+        </is>
+      </c>
+      <c r="S404" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T404" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -34396,6 +38428,16 @@
       </c>
       <c r="R405" t="inlineStr">
         <is>
+          <t>1596</t>
+        </is>
+      </c>
+      <c r="S405" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T405" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -34479,6 +38521,16 @@
         </is>
       </c>
       <c r="R406" t="inlineStr">
+        <is>
+          <t>1596</t>
+        </is>
+      </c>
+      <c r="S406" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T406" t="inlineStr">
         <is>
           <t>UGRD</t>
         </is>
@@ -34534,7 +38586,9 @@
       <c r="O407" t="inlineStr"/>
       <c r="P407" t="inlineStr"/>
       <c r="Q407" t="inlineStr"/>
-      <c r="R407" t="inlineStr">
+      <c r="R407" t="inlineStr"/>
+      <c r="S407" t="inlineStr"/>
+      <c r="T407" t="inlineStr">
         <is>
           <t>UGRD</t>
         </is>
@@ -34620,6 +38674,16 @@
       </c>
       <c r="R408" t="inlineStr">
         <is>
+          <t>486</t>
+        </is>
+      </c>
+      <c r="S408" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T408" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -34704,6 +38768,16 @@
       </c>
       <c r="R409" t="inlineStr">
         <is>
+          <t>358</t>
+        </is>
+      </c>
+      <c r="S409" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T409" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -34788,6 +38862,16 @@
       </c>
       <c r="R410" t="inlineStr">
         <is>
+          <t>077</t>
+        </is>
+      </c>
+      <c r="S410" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T410" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -34872,6 +38956,16 @@
       </c>
       <c r="R411" t="inlineStr">
         <is>
+          <t>1349</t>
+        </is>
+      </c>
+      <c r="S411" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T411" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -34956,6 +39050,16 @@
       </c>
       <c r="R412" t="inlineStr">
         <is>
+          <t>1432</t>
+        </is>
+      </c>
+      <c r="S412" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T412" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -35040,6 +39144,16 @@
       </c>
       <c r="R413" t="inlineStr">
         <is>
+          <t>1432</t>
+        </is>
+      </c>
+      <c r="S413" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T413" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -35124,6 +39238,16 @@
       </c>
       <c r="R414" t="inlineStr">
         <is>
+          <t>1432</t>
+        </is>
+      </c>
+      <c r="S414" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T414" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -35208,6 +39332,16 @@
       </c>
       <c r="R415" t="inlineStr">
         <is>
+          <t>1154</t>
+        </is>
+      </c>
+      <c r="S415" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T415" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -35292,6 +39426,16 @@
       </c>
       <c r="R416" t="inlineStr">
         <is>
+          <t>074 HILARIO MONTOYA SALDARRIAGA</t>
+        </is>
+      </c>
+      <c r="S416" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T416" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -35376,6 +39520,16 @@
       </c>
       <c r="R417" t="inlineStr">
         <is>
+          <t>794</t>
+        </is>
+      </c>
+      <c r="S417" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T417" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -35460,6 +39614,16 @@
       </c>
       <c r="R418" t="inlineStr">
         <is>
+          <t>VIRGEN DEL ROSARIO</t>
+        </is>
+      </c>
+      <c r="S418" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T418" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -35544,6 +39708,16 @@
       </c>
       <c r="R419" t="inlineStr">
         <is>
+          <t>543</t>
+        </is>
+      </c>
+      <c r="S419" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T419" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -35628,6 +39802,16 @@
       </c>
       <c r="R420" t="inlineStr">
         <is>
+          <t>20955-20 PATRON SAN LORENZO</t>
+        </is>
+      </c>
+      <c r="S420" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T420" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -35712,6 +39896,16 @@
       </c>
       <c r="R421" t="inlineStr">
         <is>
+          <t>20888 ALFONSO UGARTE</t>
+        </is>
+      </c>
+      <c r="S421" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T421" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -35796,6 +39990,16 @@
       </c>
       <c r="R422" t="inlineStr">
         <is>
+          <t>1335</t>
+        </is>
+      </c>
+      <c r="S422" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T422" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -35880,6 +40084,16 @@
       </c>
       <c r="R423" t="inlineStr">
         <is>
+          <t>1336</t>
+        </is>
+      </c>
+      <c r="S423" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T423" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -35964,6 +40178,16 @@
       </c>
       <c r="R424" t="inlineStr">
         <is>
+          <t>1512</t>
+        </is>
+      </c>
+      <c r="S424" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T424" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -36048,6 +40272,16 @@
       </c>
       <c r="R425" t="inlineStr">
         <is>
+          <t>1520</t>
+        </is>
+      </c>
+      <c r="S425" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T425" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -36132,6 +40366,16 @@
       </c>
       <c r="R426" t="inlineStr">
         <is>
+          <t>1339</t>
+        </is>
+      </c>
+      <c r="S426" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T426" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -36216,6 +40460,16 @@
       </c>
       <c r="R427" t="inlineStr">
         <is>
+          <t>20234</t>
+        </is>
+      </c>
+      <c r="S427" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T427" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -36300,6 +40554,16 @@
       </c>
       <c r="R428" t="inlineStr">
         <is>
+          <t>20234</t>
+        </is>
+      </c>
+      <c r="S428" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T428" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -36384,6 +40648,16 @@
       </c>
       <c r="R429" t="inlineStr">
         <is>
+          <t>20177</t>
+        </is>
+      </c>
+      <c r="S429" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T429" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -36468,6 +40742,16 @@
       </c>
       <c r="R430" t="inlineStr">
         <is>
+          <t>20140</t>
+        </is>
+      </c>
+      <c r="S430" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T430" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -36552,6 +40836,16 @@
       </c>
       <c r="R431" t="inlineStr">
         <is>
+          <t>1382</t>
+        </is>
+      </c>
+      <c r="S431" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T431" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -36636,6 +40930,16 @@
       </c>
       <c r="R432" t="inlineStr">
         <is>
+          <t>1382</t>
+        </is>
+      </c>
+      <c r="S432" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T432" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -36720,6 +41024,16 @@
       </c>
       <c r="R433" t="inlineStr">
         <is>
+          <t>15219</t>
+        </is>
+      </c>
+      <c r="S433" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T433" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -36804,6 +41118,16 @@
       </c>
       <c r="R434" t="inlineStr">
         <is>
+          <t>15219</t>
+        </is>
+      </c>
+      <c r="S434" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T434" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -36888,6 +41212,16 @@
       </c>
       <c r="R435" t="inlineStr">
         <is>
+          <t>1445</t>
+        </is>
+      </c>
+      <c r="S435" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T435" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -36972,6 +41306,16 @@
       </c>
       <c r="R436" t="inlineStr">
         <is>
+          <t>1445</t>
+        </is>
+      </c>
+      <c r="S436" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T436" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -37056,6 +41400,16 @@
       </c>
       <c r="R437" t="inlineStr">
         <is>
+          <t>20232/20232</t>
+        </is>
+      </c>
+      <c r="S437" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T437" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -37140,6 +41494,16 @@
       </c>
       <c r="R438" t="inlineStr">
         <is>
+          <t>1451</t>
+        </is>
+      </c>
+      <c r="S438" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T438" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -37224,6 +41588,16 @@
       </c>
       <c r="R439" t="inlineStr">
         <is>
+          <t>1399</t>
+        </is>
+      </c>
+      <c r="S439" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T439" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -37308,6 +41682,16 @@
       </c>
       <c r="R440" t="inlineStr">
         <is>
+          <t>15220</t>
+        </is>
+      </c>
+      <c r="S440" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T440" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -37392,6 +41776,16 @@
       </c>
       <c r="R441" t="inlineStr">
         <is>
+          <t>1369</t>
+        </is>
+      </c>
+      <c r="S441" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T441" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -37476,6 +41870,16 @@
       </c>
       <c r="R442" t="inlineStr">
         <is>
+          <t>1369</t>
+        </is>
+      </c>
+      <c r="S442" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T442" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -37560,6 +41964,16 @@
       </c>
       <c r="R443" t="inlineStr">
         <is>
+          <t>1381</t>
+        </is>
+      </c>
+      <c r="S443" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T443" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -37644,6 +42058,16 @@
       </c>
       <c r="R444" t="inlineStr">
         <is>
+          <t>068 MARIA MUÑOZ DE MEDINA</t>
+        </is>
+      </c>
+      <c r="S444" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T444" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -37728,6 +42152,16 @@
       </c>
       <c r="R445" t="inlineStr">
         <is>
+          <t>030</t>
+        </is>
+      </c>
+      <c r="S445" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T445" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -37812,6 +42246,16 @@
       </c>
       <c r="R446" t="inlineStr">
         <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="S446" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T446" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -37896,6 +42340,16 @@
       </c>
       <c r="R447" t="inlineStr">
         <is>
+          <t>032</t>
+        </is>
+      </c>
+      <c r="S447" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T447" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -37980,6 +42434,16 @@
       </c>
       <c r="R448" t="inlineStr">
         <is>
+          <t>14454/14454</t>
+        </is>
+      </c>
+      <c r="S448" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T448" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -38064,6 +42528,16 @@
       </c>
       <c r="R449" t="inlineStr">
         <is>
+          <t>075 TEODOSIO TARAZONA VIDAL</t>
+        </is>
+      </c>
+      <c r="S449" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T449" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -38148,6 +42622,16 @@
       </c>
       <c r="R450" t="inlineStr">
         <is>
+          <t>1583</t>
+        </is>
+      </c>
+      <c r="S450" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T450" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -38232,6 +42716,16 @@
       </c>
       <c r="R451" t="inlineStr">
         <is>
+          <t>1583</t>
+        </is>
+      </c>
+      <c r="S451" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T451" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -38316,6 +42810,16 @@
       </c>
       <c r="R452" t="inlineStr">
         <is>
+          <t>88040</t>
+        </is>
+      </c>
+      <c r="S452" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T452" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -38400,6 +42904,16 @@
       </c>
       <c r="R453" t="inlineStr">
         <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="S453" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T453" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -38484,6 +42998,16 @@
       </c>
       <c r="R454" t="inlineStr">
         <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="S454" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T454" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -38568,6 +43092,16 @@
       </c>
       <c r="R455" t="inlineStr">
         <is>
+          <t>1273</t>
+        </is>
+      </c>
+      <c r="S455" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T455" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -38652,6 +43186,16 @@
       </c>
       <c r="R456" t="inlineStr">
         <is>
+          <t>1273</t>
+        </is>
+      </c>
+      <c r="S456" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T456" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -38736,6 +43280,16 @@
       </c>
       <c r="R457" t="inlineStr">
         <is>
+          <t>1289</t>
+        </is>
+      </c>
+      <c r="S457" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T457" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -38820,6 +43374,16 @@
       </c>
       <c r="R458" t="inlineStr">
         <is>
+          <t>1469</t>
+        </is>
+      </c>
+      <c r="S458" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T458" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -38904,6 +43468,16 @@
       </c>
       <c r="R459" t="inlineStr">
         <is>
+          <t>1470</t>
+        </is>
+      </c>
+      <c r="S459" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T459" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -38988,6 +43562,16 @@
       </c>
       <c r="R460" t="inlineStr">
         <is>
+          <t>1470</t>
+        </is>
+      </c>
+      <c r="S460" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T460" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -39072,6 +43656,16 @@
       </c>
       <c r="R461" t="inlineStr">
         <is>
+          <t>1476</t>
+        </is>
+      </c>
+      <c r="S461" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T461" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -39156,6 +43750,16 @@
       </c>
       <c r="R462" t="inlineStr">
         <is>
+          <t>390</t>
+        </is>
+      </c>
+      <c r="S462" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T462" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -39240,6 +43844,16 @@
       </c>
       <c r="R463" t="inlineStr">
         <is>
+          <t>041</t>
+        </is>
+      </c>
+      <c r="S463" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T463" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -39324,6 +43938,16 @@
       </c>
       <c r="R464" t="inlineStr">
         <is>
+          <t>88074</t>
+        </is>
+      </c>
+      <c r="S464" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T464" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -39408,6 +44032,16 @@
       </c>
       <c r="R465" t="inlineStr">
         <is>
+          <t>86969</t>
+        </is>
+      </c>
+      <c r="S465" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T465" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -39492,6 +44126,16 @@
       </c>
       <c r="R466" t="inlineStr">
         <is>
+          <t>486</t>
+        </is>
+      </c>
+      <c r="S466" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T466" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -39576,6 +44220,16 @@
       </c>
       <c r="R467" t="inlineStr">
         <is>
+          <t>501</t>
+        </is>
+      </c>
+      <c r="S467" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T467" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -39660,6 +44314,16 @@
       </c>
       <c r="R468" t="inlineStr">
         <is>
+          <t>501</t>
+        </is>
+      </c>
+      <c r="S468" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T468" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -39744,6 +44408,16 @@
       </c>
       <c r="R469" t="inlineStr">
         <is>
+          <t>1285</t>
+        </is>
+      </c>
+      <c r="S469" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T469" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -39828,6 +44502,16 @@
       </c>
       <c r="R470" t="inlineStr">
         <is>
+          <t>15189</t>
+        </is>
+      </c>
+      <c r="S470" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T470" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -39912,6 +44596,16 @@
       </c>
       <c r="R471" t="inlineStr">
         <is>
+          <t>482</t>
+        </is>
+      </c>
+      <c r="S471" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T471" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -39996,6 +44690,16 @@
       </c>
       <c r="R472" t="inlineStr">
         <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="S472" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T472" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -40080,6 +44784,16 @@
       </c>
       <c r="R473" t="inlineStr">
         <is>
+          <t>22432/22432</t>
+        </is>
+      </c>
+      <c r="S473" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T473" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -40164,6 +44878,16 @@
       </c>
       <c r="R474" t="inlineStr">
         <is>
+          <t>86529 ALFONSO UGARTE</t>
+        </is>
+      </c>
+      <c r="S474" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T474" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -40248,6 +44972,16 @@
       </c>
       <c r="R475" t="inlineStr">
         <is>
+          <t>88371</t>
+        </is>
+      </c>
+      <c r="S475" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T475" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -40332,6 +45066,16 @@
       </c>
       <c r="R476" t="inlineStr">
         <is>
+          <t>20485</t>
+        </is>
+      </c>
+      <c r="S476" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T476" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -40416,6 +45160,16 @@
       </c>
       <c r="R477" t="inlineStr">
         <is>
+          <t>84037</t>
+        </is>
+      </c>
+      <c r="S477" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T477" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -40500,6 +45254,16 @@
       </c>
       <c r="R478" t="inlineStr">
         <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="S478" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T478" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -40584,6 +45348,16 @@
       </c>
       <c r="R479" t="inlineStr">
         <is>
+          <t>653</t>
+        </is>
+      </c>
+      <c r="S479" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T479" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -40668,6 +45442,16 @@
       </c>
       <c r="R480" t="inlineStr">
         <is>
+          <t>653</t>
+        </is>
+      </c>
+      <c r="S480" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T480" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -40752,6 +45536,16 @@
       </c>
       <c r="R481" t="inlineStr">
         <is>
+          <t>2635</t>
+        </is>
+      </c>
+      <c r="S481" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T481" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -40836,6 +45630,16 @@
       </c>
       <c r="R482" t="inlineStr">
         <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="S482" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T482" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -40920,6 +45724,16 @@
       </c>
       <c r="R483" t="inlineStr">
         <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="S483" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T483" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -41000,6 +45814,16 @@
       </c>
       <c r="R484" t="inlineStr">
         <is>
+          <t>84152 ULISES LLANOS OLIVEROS</t>
+        </is>
+      </c>
+      <c r="S484" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T484" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -41084,6 +45908,16 @@
       </c>
       <c r="R485" t="inlineStr">
         <is>
+          <t>2626</t>
+        </is>
+      </c>
+      <c r="S485" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T485" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -41168,6 +46002,16 @@
       </c>
       <c r="R486" t="inlineStr">
         <is>
+          <t>708</t>
+        </is>
+      </c>
+      <c r="S486" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T486" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -41252,6 +46096,16 @@
       </c>
       <c r="R487" t="inlineStr">
         <is>
+          <t>657</t>
+        </is>
+      </c>
+      <c r="S487" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T487" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -41336,6 +46190,16 @@
       </c>
       <c r="R488" t="inlineStr">
         <is>
+          <t>657</t>
+        </is>
+      </c>
+      <c r="S488" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T488" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -41420,6 +46284,16 @@
       </c>
       <c r="R489" t="inlineStr">
         <is>
+          <t>657</t>
+        </is>
+      </c>
+      <c r="S489" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T489" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -41504,6 +46378,16 @@
       </c>
       <c r="R490" t="inlineStr">
         <is>
+          <t>343</t>
+        </is>
+      </c>
+      <c r="S490" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T490" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -41588,6 +46472,16 @@
       </c>
       <c r="R491" t="inlineStr">
         <is>
+          <t>521</t>
+        </is>
+      </c>
+      <c r="S491" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T491" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -41672,6 +46566,16 @@
       </c>
       <c r="R492" t="inlineStr">
         <is>
+          <t>703</t>
+        </is>
+      </c>
+      <c r="S492" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T492" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -41756,6 +46660,16 @@
       </c>
       <c r="R493" t="inlineStr">
         <is>
+          <t>401</t>
+        </is>
+      </c>
+      <c r="S493" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T493" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -41840,6 +46754,16 @@
       </c>
       <c r="R494" t="inlineStr">
         <is>
+          <t>14639</t>
+        </is>
+      </c>
+      <c r="S494" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T494" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -41924,6 +46848,16 @@
       </c>
       <c r="R495" t="inlineStr">
         <is>
+          <t>1298</t>
+        </is>
+      </c>
+      <c r="S495" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T495" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -42008,6 +46942,16 @@
       </c>
       <c r="R496" t="inlineStr">
         <is>
+          <t>1298</t>
+        </is>
+      </c>
+      <c r="S496" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T496" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -42092,6 +47036,16 @@
       </c>
       <c r="R497" t="inlineStr">
         <is>
+          <t>1266</t>
+        </is>
+      </c>
+      <c r="S497" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T497" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -42176,6 +47130,16 @@
       </c>
       <c r="R498" t="inlineStr">
         <is>
+          <t>1288</t>
+        </is>
+      </c>
+      <c r="S498" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T498" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -42260,6 +47224,16 @@
       </c>
       <c r="R499" t="inlineStr">
         <is>
+          <t>1193</t>
+        </is>
+      </c>
+      <c r="S499" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T499" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -42344,6 +47318,16 @@
       </c>
       <c r="R500" t="inlineStr">
         <is>
+          <t>925 NIÑO JESUS</t>
+        </is>
+      </c>
+      <c r="S500" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T500" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -42428,6 +47412,16 @@
       </c>
       <c r="R501" t="inlineStr">
         <is>
+          <t>1251</t>
+        </is>
+      </c>
+      <c r="S501" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T501" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -42512,6 +47506,16 @@
       </c>
       <c r="R502" t="inlineStr">
         <is>
+          <t>1286</t>
+        </is>
+      </c>
+      <c r="S502" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T502" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -42596,6 +47600,16 @@
       </c>
       <c r="R503" t="inlineStr">
         <is>
+          <t>88194</t>
+        </is>
+      </c>
+      <c r="S503" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T503" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -42680,6 +47694,16 @@
       </c>
       <c r="R504" t="inlineStr">
         <is>
+          <t>84139 CIRILO CALIXTO FELIPE</t>
+        </is>
+      </c>
+      <c r="S504" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T504" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -42764,6 +47788,16 @@
       </c>
       <c r="R505" t="inlineStr">
         <is>
+          <t>1091</t>
+        </is>
+      </c>
+      <c r="S505" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T505" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -42848,6 +47882,16 @@
       </c>
       <c r="R506" t="inlineStr">
         <is>
+          <t>1650</t>
+        </is>
+      </c>
+      <c r="S506" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T506" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -42932,6 +47976,16 @@
       </c>
       <c r="R507" t="inlineStr">
         <is>
+          <t>81718</t>
+        </is>
+      </c>
+      <c r="S507" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T507" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -43016,6 +48070,16 @@
       </c>
       <c r="R508" t="inlineStr">
         <is>
+          <t>86053</t>
+        </is>
+      </c>
+      <c r="S508" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T508" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -43100,6 +48164,16 @@
       </c>
       <c r="R509" t="inlineStr">
         <is>
+          <t>422</t>
+        </is>
+      </c>
+      <c r="S509" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T509" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -43184,6 +48258,16 @@
       </c>
       <c r="R510" t="inlineStr">
         <is>
+          <t>88113/88113</t>
+        </is>
+      </c>
+      <c r="S510" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T510" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -43268,6 +48352,16 @@
       </c>
       <c r="R511" t="inlineStr">
         <is>
+          <t>86105</t>
+        </is>
+      </c>
+      <c r="S511" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T511" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -43352,6 +48446,16 @@
       </c>
       <c r="R512" t="inlineStr">
         <is>
+          <t>030</t>
+        </is>
+      </c>
+      <c r="S512" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T512" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -43436,6 +48540,16 @@
       </c>
       <c r="R513" t="inlineStr">
         <is>
+          <t>1583</t>
+        </is>
+      </c>
+      <c r="S513" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T513" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -43520,6 +48634,16 @@
       </c>
       <c r="R514" t="inlineStr">
         <is>
+          <t>15435 DIEGO FERRE</t>
+        </is>
+      </c>
+      <c r="S514" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T514" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -43604,6 +48728,16 @@
       </c>
       <c r="R515" t="inlineStr">
         <is>
+          <t>15435 DIEGO FERRE</t>
+        </is>
+      </c>
+      <c r="S515" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T515" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -43692,6 +48826,16 @@
       </c>
       <c r="R516" t="inlineStr">
         <is>
+          <t>82000</t>
+        </is>
+      </c>
+      <c r="S516" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T516" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -43780,6 +48924,16 @@
       </c>
       <c r="R517" t="inlineStr">
         <is>
+          <t>2241</t>
+        </is>
+      </c>
+      <c r="S517" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T517" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -43867,6 +49021,16 @@
         </is>
       </c>
       <c r="R518" t="inlineStr">
+        <is>
+          <t>1288</t>
+        </is>
+      </c>
+      <c r="S518" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T518" t="inlineStr">
         <is>
           <t>UGRD</t>
         </is>

--- a/output/bases_limpias/Grupo_03_MODULOS/df_ugrd_me.xlsx
+++ b/output/bases_limpias/Grupo_03_MODULOS/df_ugrd_me.xlsx
@@ -13995,11 +13995,27 @@
         </is>
       </c>
       <c r="J145" t="inlineStr"/>
-      <c r="K145" t="inlineStr"/>
-      <c r="L145" t="inlineStr"/>
-      <c r="M145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>HUARAZ</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>HUANCHAY</t>
+        </is>
+      </c>
       <c r="N145" t="inlineStr"/>
-      <c r="O145" t="inlineStr"/>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>020104</t>
+        </is>
+      </c>
       <c r="P145" t="inlineStr"/>
       <c r="Q145" t="inlineStr"/>
       <c r="R145" t="inlineStr"/>
@@ -38579,11 +38595,27 @@
         </is>
       </c>
       <c r="J407" t="inlineStr"/>
-      <c r="K407" t="inlineStr"/>
-      <c r="L407" t="inlineStr"/>
-      <c r="M407" t="inlineStr"/>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="L407" t="inlineStr">
+        <is>
+          <t>SECHURA</t>
+        </is>
+      </c>
+      <c r="M407" t="inlineStr">
+        <is>
+          <t>SECHURA</t>
+        </is>
+      </c>
       <c r="N407" t="inlineStr"/>
-      <c r="O407" t="inlineStr"/>
+      <c r="O407" t="inlineStr">
+        <is>
+          <t>200801</t>
+        </is>
+      </c>
       <c r="P407" t="inlineStr"/>
       <c r="Q407" t="inlineStr"/>
       <c r="R407" t="inlineStr"/>

--- a/output/bases_limpias/Grupo_03_MODULOS/df_ugrd_me.xlsx
+++ b/output/bases_limpias/Grupo_03_MODULOS/df_ugrd_me.xlsx
@@ -419,52 +419,52 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>N°</t>
+          <t>n</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>CUI</t>
+          <t>cui</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Código Local</t>
+          <t>cod_local</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Componente (Edificación y Obras Complementarias, Baño, Cerco Perimétrico o Losa Recreativa, etc.)</t>
+          <t>componente_edificacion_y_obras_complementarias_bano_cerco_pe</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Monto de inversión del componente (S/)</t>
+          <t>monto_de_inversion_del_componente_s</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Fase del componente</t>
+          <t>fase_del_componente</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Etapa del componente</t>
+          <t>etapa_del_componente</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Fecha de recepción (o estimada)</t>
+          <t>fecha_de_recepcion_o_estimada</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Fecha de entrega (o estimada)</t>
+          <t>fecha_de_entrega_o_estimada</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Comentarios</t>
+          <t>comentario</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
